--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView activeTab="2"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" r:id="rId3" sheetId="1"/>
@@ -11,15 +11,17 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Theme view" r:id="rId8" sheetId="6"/>
-    <sheet name="Sector view" r:id="rId9" sheetId="7"/>
-    <sheet name="Speaker view" r:id="rId10" sheetId="8"/>
+    <sheet name="Room view" r:id="rId8" sheetId="6"/>
+    <sheet name="Speaker view" r:id="rId9" sheetId="7"/>
+    <sheet name="Theme view" r:id="rId10" sheetId="8"/>
+    <sheet name="Sector view" r:id="rId11" sheetId="9"/>
+    <sheet name="Content view" r:id="rId12" sheetId="10"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6028" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6296" uniqueCount="474">
   <si>
     <t>Conference name</t>
   </si>
@@ -1428,13 +1430,19 @@
     <t>Building deep learning Angular</t>
   </si>
   <si>
+    <t>Speaker</t>
+  </si>
+  <si>
     <t>Theme tag</t>
   </si>
   <si>
     <t>Sector tag</t>
   </si>
   <si>
-    <t>Speaker</t>
+    <t>Content tag</t>
+  </si>
+  <si>
+    <t>(1) S028</t>
   </si>
 </sst>
 </file>
@@ -1666,6 +1674,186 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="11.78515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3"/>
+      <c r="C3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+    </row>
+  </sheetData>
+  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -16424,6 +16612,5154 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
+    <col min="1" max="1" width="6.44921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" t="s">
+        <v>32</v>
+      </c>
+      <c r="S8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" t="s">
+        <v>32</v>
+      </c>
+      <c r="S11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="11.75390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" t="s">
+        <v>32</v>
+      </c>
+      <c r="S8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" t="s">
+        <v>32</v>
+      </c>
+      <c r="S11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" t="s">
+        <v>32</v>
+      </c>
+      <c r="S13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" t="s">
+        <v>32</v>
+      </c>
+      <c r="S14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" t="s">
+        <v>32</v>
+      </c>
+      <c r="S15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" t="s">
+        <v>32</v>
+      </c>
+      <c r="O16" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" t="s">
+        <v>32</v>
+      </c>
+      <c r="S16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" t="s">
+        <v>32</v>
+      </c>
+      <c r="N17" t="s">
+        <v>32</v>
+      </c>
+      <c r="O17" t="s">
+        <v>32</v>
+      </c>
+      <c r="P17" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" t="s">
+        <v>32</v>
+      </c>
+      <c r="S17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" t="s">
+        <v>32</v>
+      </c>
+      <c r="N18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" t="s">
+        <v>32</v>
+      </c>
+      <c r="S18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" t="s">
+        <v>32</v>
+      </c>
+      <c r="S19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" t="s">
+        <v>32</v>
+      </c>
+      <c r="O20" t="s">
+        <v>32</v>
+      </c>
+      <c r="P20" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" t="s">
+        <v>32</v>
+      </c>
+      <c r="O21" t="s">
+        <v>32</v>
+      </c>
+      <c r="P21" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" t="s">
+        <v>32</v>
+      </c>
+      <c r="S21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" t="s">
+        <v>32</v>
+      </c>
+      <c r="O22" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" t="s">
+        <v>32</v>
+      </c>
+      <c r="P23" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" t="s">
+        <v>32</v>
+      </c>
+      <c r="S23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" t="s">
+        <v>32</v>
+      </c>
+      <c r="O24" t="s">
+        <v>32</v>
+      </c>
+      <c r="P24" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" t="s">
+        <v>32</v>
+      </c>
+      <c r="S24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" t="s">
+        <v>32</v>
+      </c>
+      <c r="N25" t="s">
+        <v>32</v>
+      </c>
+      <c r="O25" t="s">
+        <v>32</v>
+      </c>
+      <c r="P25" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>32</v>
+      </c>
+      <c r="R25" t="s">
+        <v>32</v>
+      </c>
+      <c r="S25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" t="s">
+        <v>32</v>
+      </c>
+      <c r="N26" t="s">
+        <v>32</v>
+      </c>
+      <c r="O26" t="s">
+        <v>32</v>
+      </c>
+      <c r="P26" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>32</v>
+      </c>
+      <c r="R26" t="s">
+        <v>32</v>
+      </c>
+      <c r="S26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" t="s">
+        <v>32</v>
+      </c>
+      <c r="M27" t="s">
+        <v>32</v>
+      </c>
+      <c r="N27" t="s">
+        <v>32</v>
+      </c>
+      <c r="O27" t="s">
+        <v>32</v>
+      </c>
+      <c r="P27" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>32</v>
+      </c>
+      <c r="R27" t="s">
+        <v>32</v>
+      </c>
+      <c r="S27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" t="s">
+        <v>32</v>
+      </c>
+      <c r="O28" t="s">
+        <v>32</v>
+      </c>
+      <c r="P28" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" t="s">
+        <v>32</v>
+      </c>
+      <c r="S28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" t="s">
+        <v>32</v>
+      </c>
+      <c r="O29" t="s">
+        <v>32</v>
+      </c>
+      <c r="P29" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>32</v>
+      </c>
+      <c r="R29" t="s">
+        <v>32</v>
+      </c>
+      <c r="S29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" t="s">
+        <v>32</v>
+      </c>
+      <c r="H30" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" t="s">
+        <v>32</v>
+      </c>
+      <c r="M30" t="s">
+        <v>32</v>
+      </c>
+      <c r="N30" t="s">
+        <v>32</v>
+      </c>
+      <c r="O30" t="s">
+        <v>32</v>
+      </c>
+      <c r="P30" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>32</v>
+      </c>
+      <c r="R30" t="s">
+        <v>32</v>
+      </c>
+      <c r="S30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" t="s">
+        <v>32</v>
+      </c>
+      <c r="K31" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" t="s">
+        <v>32</v>
+      </c>
+      <c r="M31" t="s">
+        <v>32</v>
+      </c>
+      <c r="N31" t="s">
+        <v>32</v>
+      </c>
+      <c r="O31" t="s">
+        <v>32</v>
+      </c>
+      <c r="P31" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" t="s">
+        <v>32</v>
+      </c>
+      <c r="S31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H32" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" t="s">
+        <v>32</v>
+      </c>
+      <c r="J32" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M32" t="s">
+        <v>32</v>
+      </c>
+      <c r="N32" t="s">
+        <v>32</v>
+      </c>
+      <c r="O32" t="s">
+        <v>32</v>
+      </c>
+      <c r="P32" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>32</v>
+      </c>
+      <c r="R32" t="s">
+        <v>32</v>
+      </c>
+      <c r="S32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" t="s">
+        <v>32</v>
+      </c>
+      <c r="K33" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" t="s">
+        <v>32</v>
+      </c>
+      <c r="N33" t="s">
+        <v>32</v>
+      </c>
+      <c r="O33" t="s">
+        <v>32</v>
+      </c>
+      <c r="P33" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>32</v>
+      </c>
+      <c r="R33" t="s">
+        <v>32</v>
+      </c>
+      <c r="S33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" t="s">
+        <v>32</v>
+      </c>
+      <c r="J34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M34" t="s">
+        <v>32</v>
+      </c>
+      <c r="N34" t="s">
+        <v>32</v>
+      </c>
+      <c r="O34" t="s">
+        <v>32</v>
+      </c>
+      <c r="P34" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>32</v>
+      </c>
+      <c r="R34" t="s">
+        <v>32</v>
+      </c>
+      <c r="S34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" t="s">
+        <v>32</v>
+      </c>
+      <c r="M35" t="s">
+        <v>32</v>
+      </c>
+      <c r="N35" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" t="s">
+        <v>32</v>
+      </c>
+      <c r="P35" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>32</v>
+      </c>
+      <c r="R35" t="s">
+        <v>32</v>
+      </c>
+      <c r="S35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" t="s">
+        <v>32</v>
+      </c>
+      <c r="J36" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" t="s">
+        <v>32</v>
+      </c>
+      <c r="M36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N36" t="s">
+        <v>32</v>
+      </c>
+      <c r="O36" t="s">
+        <v>32</v>
+      </c>
+      <c r="P36" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>32</v>
+      </c>
+      <c r="R36" t="s">
+        <v>32</v>
+      </c>
+      <c r="S36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G37" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" t="s">
+        <v>32</v>
+      </c>
+      <c r="M37" t="s">
+        <v>32</v>
+      </c>
+      <c r="N37" t="s">
+        <v>32</v>
+      </c>
+      <c r="O37" t="s">
+        <v>32</v>
+      </c>
+      <c r="P37" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>32</v>
+      </c>
+      <c r="R37" t="s">
+        <v>32</v>
+      </c>
+      <c r="S37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" t="s">
+        <v>32</v>
+      </c>
+      <c r="G38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" t="s">
+        <v>32</v>
+      </c>
+      <c r="K38" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38" t="s">
+        <v>32</v>
+      </c>
+      <c r="M38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N38" t="s">
+        <v>32</v>
+      </c>
+      <c r="O38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P38" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>32</v>
+      </c>
+      <c r="R38" t="s">
+        <v>32</v>
+      </c>
+      <c r="S38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" t="s">
+        <v>32</v>
+      </c>
+      <c r="K39" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" t="s">
+        <v>32</v>
+      </c>
+      <c r="M39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N39" t="s">
+        <v>32</v>
+      </c>
+      <c r="O39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P39" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>32</v>
+      </c>
+      <c r="R39" t="s">
+        <v>32</v>
+      </c>
+      <c r="S39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G40" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" t="s">
+        <v>32</v>
+      </c>
+      <c r="M40" t="s">
+        <v>32</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>32</v>
+      </c>
+      <c r="R40" t="s">
+        <v>32</v>
+      </c>
+      <c r="S40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G41" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" t="s">
+        <v>32</v>
+      </c>
+      <c r="J41" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" t="s">
+        <v>32</v>
+      </c>
+      <c r="L41" t="s">
+        <v>32</v>
+      </c>
+      <c r="M41" t="s">
+        <v>32</v>
+      </c>
+      <c r="N41" t="s">
+        <v>32</v>
+      </c>
+      <c r="O41" t="s">
+        <v>32</v>
+      </c>
+      <c r="P41" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>32</v>
+      </c>
+      <c r="R41" t="s">
+        <v>32</v>
+      </c>
+      <c r="S41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" t="s">
+        <v>32</v>
+      </c>
+      <c r="H42" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" t="s">
+        <v>32</v>
+      </c>
+      <c r="M42" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42" t="s">
+        <v>32</v>
+      </c>
+      <c r="O42" t="s">
+        <v>32</v>
+      </c>
+      <c r="P42" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>32</v>
+      </c>
+      <c r="R42" t="s">
+        <v>32</v>
+      </c>
+      <c r="S42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" t="s">
+        <v>32</v>
+      </c>
+      <c r="G43" t="s">
+        <v>32</v>
+      </c>
+      <c r="H43" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" t="s">
+        <v>32</v>
+      </c>
+      <c r="J43" t="s">
+        <v>32</v>
+      </c>
+      <c r="K43" t="s">
+        <v>32</v>
+      </c>
+      <c r="L43" t="s">
+        <v>32</v>
+      </c>
+      <c r="M43" t="s">
+        <v>32</v>
+      </c>
+      <c r="N43" t="s">
+        <v>32</v>
+      </c>
+      <c r="O43" t="s">
+        <v>32</v>
+      </c>
+      <c r="P43" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>32</v>
+      </c>
+      <c r="R43" t="s">
+        <v>32</v>
+      </c>
+      <c r="S43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" t="s">
+        <v>32</v>
+      </c>
+      <c r="H44" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" t="s">
+        <v>32</v>
+      </c>
+      <c r="J44" t="s">
+        <v>32</v>
+      </c>
+      <c r="K44" t="s">
+        <v>32</v>
+      </c>
+      <c r="L44" t="s">
+        <v>32</v>
+      </c>
+      <c r="M44" t="s">
+        <v>32</v>
+      </c>
+      <c r="N44" t="s">
+        <v>32</v>
+      </c>
+      <c r="O44" t="s">
+        <v>32</v>
+      </c>
+      <c r="P44" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>32</v>
+      </c>
+      <c r="R44" t="s">
+        <v>32</v>
+      </c>
+      <c r="S44" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" t="s">
+        <v>32</v>
+      </c>
+      <c r="G45" t="s">
+        <v>32</v>
+      </c>
+      <c r="H45" t="s">
+        <v>32</v>
+      </c>
+      <c r="I45" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45" t="s">
+        <v>32</v>
+      </c>
+      <c r="M45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45" t="s">
+        <v>32</v>
+      </c>
+      <c r="O45" t="s">
+        <v>32</v>
+      </c>
+      <c r="P45" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>32</v>
+      </c>
+      <c r="R45" t="s">
+        <v>32</v>
+      </c>
+      <c r="S45" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" t="s">
+        <v>32</v>
+      </c>
+      <c r="E46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" t="s">
+        <v>32</v>
+      </c>
+      <c r="G46" t="s">
+        <v>32</v>
+      </c>
+      <c r="H46" t="s">
+        <v>32</v>
+      </c>
+      <c r="I46" t="s">
+        <v>32</v>
+      </c>
+      <c r="J46" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" t="s">
+        <v>32</v>
+      </c>
+      <c r="L46" t="s">
+        <v>32</v>
+      </c>
+      <c r="M46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N46" t="s">
+        <v>32</v>
+      </c>
+      <c r="O46" t="s">
+        <v>32</v>
+      </c>
+      <c r="P46" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>32</v>
+      </c>
+      <c r="R46" t="s">
+        <v>32</v>
+      </c>
+      <c r="S46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J47" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" t="s">
+        <v>32</v>
+      </c>
+      <c r="L47" t="s">
+        <v>32</v>
+      </c>
+      <c r="M47" t="s">
+        <v>32</v>
+      </c>
+      <c r="N47" t="s">
+        <v>32</v>
+      </c>
+      <c r="O47" t="s">
+        <v>32</v>
+      </c>
+      <c r="P47" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>32</v>
+      </c>
+      <c r="R47" t="s">
+        <v>32</v>
+      </c>
+      <c r="S47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" t="s">
+        <v>32</v>
+      </c>
+      <c r="K48" t="s">
+        <v>32</v>
+      </c>
+      <c r="L48" t="s">
+        <v>32</v>
+      </c>
+      <c r="M48" t="s">
+        <v>32</v>
+      </c>
+      <c r="N48" t="s">
+        <v>32</v>
+      </c>
+      <c r="O48" t="s">
+        <v>32</v>
+      </c>
+      <c r="P48" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>32</v>
+      </c>
+      <c r="R48" t="s">
+        <v>32</v>
+      </c>
+      <c r="S48" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>120</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" t="s">
+        <v>32</v>
+      </c>
+      <c r="I49" t="s">
+        <v>32</v>
+      </c>
+      <c r="J49" t="s">
+        <v>32</v>
+      </c>
+      <c r="K49" t="s">
+        <v>32</v>
+      </c>
+      <c r="L49" t="s">
+        <v>32</v>
+      </c>
+      <c r="M49" t="s">
+        <v>32</v>
+      </c>
+      <c r="N49" t="s">
+        <v>32</v>
+      </c>
+      <c r="O49" t="s">
+        <v>32</v>
+      </c>
+      <c r="P49" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>32</v>
+      </c>
+      <c r="R49" t="s">
+        <v>32</v>
+      </c>
+      <c r="S49" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" t="s">
+        <v>32</v>
+      </c>
+      <c r="J50" t="s">
+        <v>32</v>
+      </c>
+      <c r="K50" t="s">
+        <v>32</v>
+      </c>
+      <c r="L50" t="s">
+        <v>32</v>
+      </c>
+      <c r="M50" t="s">
+        <v>32</v>
+      </c>
+      <c r="N50" t="s">
+        <v>32</v>
+      </c>
+      <c r="O50" t="s">
+        <v>32</v>
+      </c>
+      <c r="P50" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>32</v>
+      </c>
+      <c r="R50" t="s">
+        <v>32</v>
+      </c>
+      <c r="S50" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K51" t="s">
+        <v>32</v>
+      </c>
+      <c r="L51" t="s">
+        <v>32</v>
+      </c>
+      <c r="M51" t="s">
+        <v>32</v>
+      </c>
+      <c r="N51" t="s">
+        <v>32</v>
+      </c>
+      <c r="O51" t="s">
+        <v>32</v>
+      </c>
+      <c r="P51" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>32</v>
+      </c>
+      <c r="R51" t="s">
+        <v>32</v>
+      </c>
+      <c r="S51" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" t="s">
+        <v>32</v>
+      </c>
+      <c r="E52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52" t="s">
+        <v>32</v>
+      </c>
+      <c r="G52" t="s">
+        <v>32</v>
+      </c>
+      <c r="H52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" t="s">
+        <v>32</v>
+      </c>
+      <c r="J52" t="s">
+        <v>32</v>
+      </c>
+      <c r="K52" t="s">
+        <v>32</v>
+      </c>
+      <c r="L52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M52" t="s">
+        <v>32</v>
+      </c>
+      <c r="N52" t="s">
+        <v>32</v>
+      </c>
+      <c r="O52" t="s">
+        <v>32</v>
+      </c>
+      <c r="P52" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>32</v>
+      </c>
+      <c r="R52" t="s">
+        <v>32</v>
+      </c>
+      <c r="S52" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G53" t="s">
+        <v>32</v>
+      </c>
+      <c r="H53" t="s">
+        <v>32</v>
+      </c>
+      <c r="I53" t="s">
+        <v>32</v>
+      </c>
+      <c r="J53" t="s">
+        <v>32</v>
+      </c>
+      <c r="K53" t="s">
+        <v>32</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M53" t="s">
+        <v>32</v>
+      </c>
+      <c r="N53" t="s">
+        <v>32</v>
+      </c>
+      <c r="O53" t="s">
+        <v>32</v>
+      </c>
+      <c r="P53" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>32</v>
+      </c>
+      <c r="R53" t="s">
+        <v>32</v>
+      </c>
+      <c r="S53" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" t="s">
+        <v>32</v>
+      </c>
+      <c r="E54" t="s">
+        <v>32</v>
+      </c>
+      <c r="F54" t="s">
+        <v>32</v>
+      </c>
+      <c r="G54" t="s">
+        <v>32</v>
+      </c>
+      <c r="H54" t="s">
+        <v>32</v>
+      </c>
+      <c r="I54" t="s">
+        <v>32</v>
+      </c>
+      <c r="J54" t="s">
+        <v>32</v>
+      </c>
+      <c r="K54" t="s">
+        <v>32</v>
+      </c>
+      <c r="L54" t="s">
+        <v>32</v>
+      </c>
+      <c r="M54" t="s">
+        <v>32</v>
+      </c>
+      <c r="N54" t="s">
+        <v>32</v>
+      </c>
+      <c r="O54" t="s">
+        <v>32</v>
+      </c>
+      <c r="P54" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>32</v>
+      </c>
+      <c r="R54" t="s">
+        <v>32</v>
+      </c>
+      <c r="S54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" t="s">
+        <v>32</v>
+      </c>
+      <c r="E55" t="s">
+        <v>32</v>
+      </c>
+      <c r="F55" t="s">
+        <v>32</v>
+      </c>
+      <c r="G55" t="s">
+        <v>32</v>
+      </c>
+      <c r="H55" t="s">
+        <v>32</v>
+      </c>
+      <c r="I55" t="s">
+        <v>32</v>
+      </c>
+      <c r="J55" t="s">
+        <v>32</v>
+      </c>
+      <c r="K55" t="s">
+        <v>32</v>
+      </c>
+      <c r="L55" t="s">
+        <v>32</v>
+      </c>
+      <c r="M55" t="s">
+        <v>32</v>
+      </c>
+      <c r="N55" t="s">
+        <v>32</v>
+      </c>
+      <c r="O55" t="s">
+        <v>32</v>
+      </c>
+      <c r="P55" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>32</v>
+      </c>
+      <c r="R55" t="s">
+        <v>32</v>
+      </c>
+      <c r="S55" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" t="s">
+        <v>32</v>
+      </c>
+      <c r="E56" t="s">
+        <v>32</v>
+      </c>
+      <c r="F56" t="s">
+        <v>32</v>
+      </c>
+      <c r="G56" t="s">
+        <v>32</v>
+      </c>
+      <c r="H56" t="s">
+        <v>32</v>
+      </c>
+      <c r="I56" t="s">
+        <v>32</v>
+      </c>
+      <c r="J56" t="s">
+        <v>32</v>
+      </c>
+      <c r="K56" t="s">
+        <v>32</v>
+      </c>
+      <c r="L56" t="s">
+        <v>32</v>
+      </c>
+      <c r="M56" t="s">
+        <v>32</v>
+      </c>
+      <c r="N56" t="s">
+        <v>32</v>
+      </c>
+      <c r="O56" t="s">
+        <v>32</v>
+      </c>
+      <c r="P56" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>32</v>
+      </c>
+      <c r="R56" t="s">
+        <v>32</v>
+      </c>
+      <c r="S56" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" t="s">
+        <v>32</v>
+      </c>
+      <c r="E57" t="s">
+        <v>32</v>
+      </c>
+      <c r="F57" t="s">
+        <v>32</v>
+      </c>
+      <c r="G57" t="s">
+        <v>32</v>
+      </c>
+      <c r="H57" t="s">
+        <v>32</v>
+      </c>
+      <c r="I57" t="s">
+        <v>32</v>
+      </c>
+      <c r="J57" t="s">
+        <v>32</v>
+      </c>
+      <c r="K57" t="s">
+        <v>32</v>
+      </c>
+      <c r="L57" t="s">
+        <v>32</v>
+      </c>
+      <c r="M57" t="s">
+        <v>32</v>
+      </c>
+      <c r="N57" t="s">
+        <v>32</v>
+      </c>
+      <c r="O57" t="s">
+        <v>32</v>
+      </c>
+      <c r="P57" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>32</v>
+      </c>
+      <c r="R57" t="s">
+        <v>32</v>
+      </c>
+      <c r="S57" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" t="s">
+        <v>32</v>
+      </c>
+      <c r="E58" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" t="s">
+        <v>32</v>
+      </c>
+      <c r="G58" t="s">
+        <v>32</v>
+      </c>
+      <c r="H58" t="s">
+        <v>32</v>
+      </c>
+      <c r="I58" t="s">
+        <v>32</v>
+      </c>
+      <c r="J58" t="s">
+        <v>32</v>
+      </c>
+      <c r="K58" t="s">
+        <v>32</v>
+      </c>
+      <c r="L58" t="s">
+        <v>32</v>
+      </c>
+      <c r="M58" t="s">
+        <v>32</v>
+      </c>
+      <c r="N58" t="s">
+        <v>32</v>
+      </c>
+      <c r="O58" t="s">
+        <v>32</v>
+      </c>
+      <c r="P58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>32</v>
+      </c>
+      <c r="R58" t="s">
+        <v>32</v>
+      </c>
+      <c r="S58" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" t="s">
+        <v>32</v>
+      </c>
+      <c r="E59" t="s">
+        <v>32</v>
+      </c>
+      <c r="F59" t="s">
+        <v>32</v>
+      </c>
+      <c r="G59" t="s">
+        <v>32</v>
+      </c>
+      <c r="H59" t="s">
+        <v>32</v>
+      </c>
+      <c r="I59" t="s">
+        <v>32</v>
+      </c>
+      <c r="J59" t="s">
+        <v>32</v>
+      </c>
+      <c r="K59" t="s">
+        <v>32</v>
+      </c>
+      <c r="L59" t="s">
+        <v>32</v>
+      </c>
+      <c r="M59" t="s">
+        <v>32</v>
+      </c>
+      <c r="N59" t="s">
+        <v>32</v>
+      </c>
+      <c r="O59" t="s">
+        <v>32</v>
+      </c>
+      <c r="P59" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>32</v>
+      </c>
+      <c r="R59" t="s">
+        <v>32</v>
+      </c>
+      <c r="S59" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" t="s">
+        <v>32</v>
+      </c>
+      <c r="E60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60" t="s">
+        <v>32</v>
+      </c>
+      <c r="G60" t="s">
+        <v>32</v>
+      </c>
+      <c r="H60" t="s">
+        <v>32</v>
+      </c>
+      <c r="I60" t="s">
+        <v>32</v>
+      </c>
+      <c r="J60" t="s">
+        <v>32</v>
+      </c>
+      <c r="K60" t="s">
+        <v>32</v>
+      </c>
+      <c r="L60" t="s">
+        <v>32</v>
+      </c>
+      <c r="M60" t="s">
+        <v>32</v>
+      </c>
+      <c r="N60" t="s">
+        <v>32</v>
+      </c>
+      <c r="O60" t="s">
+        <v>32</v>
+      </c>
+      <c r="P60" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>32</v>
+      </c>
+      <c r="R60" t="s">
+        <v>32</v>
+      </c>
+      <c r="S60" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B61" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" t="s">
+        <v>32</v>
+      </c>
+      <c r="E61" t="s">
+        <v>32</v>
+      </c>
+      <c r="F61" t="s">
+        <v>32</v>
+      </c>
+      <c r="G61" t="s">
+        <v>32</v>
+      </c>
+      <c r="H61" t="s">
+        <v>32</v>
+      </c>
+      <c r="I61" t="s">
+        <v>32</v>
+      </c>
+      <c r="J61" t="s">
+        <v>32</v>
+      </c>
+      <c r="K61" t="s">
+        <v>32</v>
+      </c>
+      <c r="L61" t="s">
+        <v>32</v>
+      </c>
+      <c r="M61" t="s">
+        <v>32</v>
+      </c>
+      <c r="N61" t="s">
+        <v>32</v>
+      </c>
+      <c r="O61" t="s">
+        <v>32</v>
+      </c>
+      <c r="P61" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>32</v>
+      </c>
+      <c r="R61" t="s">
+        <v>32</v>
+      </c>
+      <c r="S61" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" t="s">
+        <v>32</v>
+      </c>
+      <c r="E62" t="s">
+        <v>32</v>
+      </c>
+      <c r="F62" t="s">
+        <v>32</v>
+      </c>
+      <c r="G62" t="s">
+        <v>32</v>
+      </c>
+      <c r="H62" t="s">
+        <v>32</v>
+      </c>
+      <c r="I62" t="s">
+        <v>32</v>
+      </c>
+      <c r="J62" t="s">
+        <v>32</v>
+      </c>
+      <c r="K62" t="s">
+        <v>32</v>
+      </c>
+      <c r="L62" t="s">
+        <v>32</v>
+      </c>
+      <c r="M62" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62" t="s">
+        <v>32</v>
+      </c>
+      <c r="O62" t="s">
+        <v>32</v>
+      </c>
+      <c r="P62" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>32</v>
+      </c>
+      <c r="R62" t="s">
+        <v>32</v>
+      </c>
+      <c r="S62" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>134</v>
+      </c>
+      <c r="B63" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" t="s">
+        <v>32</v>
+      </c>
+      <c r="E63" t="s">
+        <v>32</v>
+      </c>
+      <c r="F63" t="s">
+        <v>32</v>
+      </c>
+      <c r="G63" t="s">
+        <v>32</v>
+      </c>
+      <c r="H63" t="s">
+        <v>32</v>
+      </c>
+      <c r="I63" t="s">
+        <v>32</v>
+      </c>
+      <c r="J63" t="s">
+        <v>32</v>
+      </c>
+      <c r="K63" t="s">
+        <v>32</v>
+      </c>
+      <c r="L63" t="s">
+        <v>32</v>
+      </c>
+      <c r="M63" t="s">
+        <v>32</v>
+      </c>
+      <c r="N63" t="s">
+        <v>32</v>
+      </c>
+      <c r="O63" t="s">
+        <v>32</v>
+      </c>
+      <c r="P63" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>32</v>
+      </c>
+      <c r="R63" t="s">
+        <v>32</v>
+      </c>
+      <c r="S63" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" t="s">
+        <v>32</v>
+      </c>
+      <c r="E64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F64" t="s">
+        <v>32</v>
+      </c>
+      <c r="G64" t="s">
+        <v>32</v>
+      </c>
+      <c r="H64" t="s">
+        <v>32</v>
+      </c>
+      <c r="I64" t="s">
+        <v>32</v>
+      </c>
+      <c r="J64" t="s">
+        <v>32</v>
+      </c>
+      <c r="K64" t="s">
+        <v>32</v>
+      </c>
+      <c r="L64" t="s">
+        <v>32</v>
+      </c>
+      <c r="M64" t="s">
+        <v>32</v>
+      </c>
+      <c r="N64" t="s">
+        <v>32</v>
+      </c>
+      <c r="O64" t="s">
+        <v>32</v>
+      </c>
+      <c r="P64" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>32</v>
+      </c>
+      <c r="R64" t="s">
+        <v>32</v>
+      </c>
+      <c r="S64" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" t="s">
+        <v>32</v>
+      </c>
+      <c r="D65" t="s">
+        <v>32</v>
+      </c>
+      <c r="E65" t="s">
+        <v>32</v>
+      </c>
+      <c r="F65" t="s">
+        <v>32</v>
+      </c>
+      <c r="G65" t="s">
+        <v>32</v>
+      </c>
+      <c r="H65" t="s">
+        <v>32</v>
+      </c>
+      <c r="I65" t="s">
+        <v>32</v>
+      </c>
+      <c r="J65" t="s">
+        <v>32</v>
+      </c>
+      <c r="K65" t="s">
+        <v>32</v>
+      </c>
+      <c r="L65" t="s">
+        <v>32</v>
+      </c>
+      <c r="M65" t="s">
+        <v>32</v>
+      </c>
+      <c r="N65" t="s">
+        <v>32</v>
+      </c>
+      <c r="O65" t="s">
+        <v>32</v>
+      </c>
+      <c r="P65" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>32</v>
+      </c>
+      <c r="R65" t="s">
+        <v>32</v>
+      </c>
+      <c r="S65" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>137</v>
+      </c>
+      <c r="B66" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" t="s">
+        <v>32</v>
+      </c>
+      <c r="E66" t="s">
+        <v>32</v>
+      </c>
+      <c r="F66" t="s">
+        <v>32</v>
+      </c>
+      <c r="G66" t="s">
+        <v>32</v>
+      </c>
+      <c r="H66" t="s">
+        <v>32</v>
+      </c>
+      <c r="I66" t="s">
+        <v>32</v>
+      </c>
+      <c r="J66" t="s">
+        <v>32</v>
+      </c>
+      <c r="K66" t="s">
+        <v>32</v>
+      </c>
+      <c r="L66" t="s">
+        <v>32</v>
+      </c>
+      <c r="M66" t="s">
+        <v>32</v>
+      </c>
+      <c r="N66" t="s">
+        <v>32</v>
+      </c>
+      <c r="O66" t="s">
+        <v>32</v>
+      </c>
+      <c r="P66" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>32</v>
+      </c>
+      <c r="R66" t="s">
+        <v>32</v>
+      </c>
+      <c r="S66" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>138</v>
+      </c>
+      <c r="B67" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67" t="s">
+        <v>32</v>
+      </c>
+      <c r="E67" t="s">
+        <v>32</v>
+      </c>
+      <c r="F67" t="s">
+        <v>32</v>
+      </c>
+      <c r="G67" t="s">
+        <v>32</v>
+      </c>
+      <c r="H67" t="s">
+        <v>32</v>
+      </c>
+      <c r="I67" t="s">
+        <v>32</v>
+      </c>
+      <c r="J67" t="s">
+        <v>32</v>
+      </c>
+      <c r="K67" t="s">
+        <v>32</v>
+      </c>
+      <c r="L67" t="s">
+        <v>32</v>
+      </c>
+      <c r="M67" t="s">
+        <v>32</v>
+      </c>
+      <c r="N67" t="s">
+        <v>32</v>
+      </c>
+      <c r="O67" t="s">
+        <v>32</v>
+      </c>
+      <c r="P67" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>32</v>
+      </c>
+      <c r="R67" t="s">
+        <v>32</v>
+      </c>
+      <c r="S67" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>139</v>
+      </c>
+      <c r="B68" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E68" t="s">
+        <v>32</v>
+      </c>
+      <c r="F68" t="s">
+        <v>32</v>
+      </c>
+      <c r="G68" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68" t="s">
+        <v>32</v>
+      </c>
+      <c r="I68" t="s">
+        <v>32</v>
+      </c>
+      <c r="J68" t="s">
+        <v>32</v>
+      </c>
+      <c r="K68" t="s">
+        <v>32</v>
+      </c>
+      <c r="L68" t="s">
+        <v>32</v>
+      </c>
+      <c r="M68" t="s">
+        <v>32</v>
+      </c>
+      <c r="N68" t="s">
+        <v>32</v>
+      </c>
+      <c r="O68" t="s">
+        <v>32</v>
+      </c>
+      <c r="P68" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>32</v>
+      </c>
+      <c r="R68" t="s">
+        <v>32</v>
+      </c>
+      <c r="S68" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>140</v>
+      </c>
+      <c r="B69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69" t="s">
+        <v>32</v>
+      </c>
+      <c r="E69" t="s">
+        <v>32</v>
+      </c>
+      <c r="F69" t="s">
+        <v>32</v>
+      </c>
+      <c r="G69" t="s">
+        <v>32</v>
+      </c>
+      <c r="H69" t="s">
+        <v>32</v>
+      </c>
+      <c r="I69" t="s">
+        <v>32</v>
+      </c>
+      <c r="J69" t="s">
+        <v>32</v>
+      </c>
+      <c r="K69" t="s">
+        <v>32</v>
+      </c>
+      <c r="L69" t="s">
+        <v>32</v>
+      </c>
+      <c r="M69" t="s">
+        <v>32</v>
+      </c>
+      <c r="N69" t="s">
+        <v>32</v>
+      </c>
+      <c r="O69" t="s">
+        <v>32</v>
+      </c>
+      <c r="P69" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>32</v>
+      </c>
+      <c r="R69" t="s">
+        <v>32</v>
+      </c>
+      <c r="S69" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" t="s">
+        <v>32</v>
+      </c>
+      <c r="D70" t="s">
+        <v>32</v>
+      </c>
+      <c r="E70" t="s">
+        <v>32</v>
+      </c>
+      <c r="F70" t="s">
+        <v>32</v>
+      </c>
+      <c r="G70" t="s">
+        <v>32</v>
+      </c>
+      <c r="H70" t="s">
+        <v>32</v>
+      </c>
+      <c r="I70" t="s">
+        <v>32</v>
+      </c>
+      <c r="J70" t="s">
+        <v>32</v>
+      </c>
+      <c r="K70" t="s">
+        <v>32</v>
+      </c>
+      <c r="L70" t="s">
+        <v>32</v>
+      </c>
+      <c r="M70" t="s">
+        <v>32</v>
+      </c>
+      <c r="N70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O70" t="s">
+        <v>32</v>
+      </c>
+      <c r="P70" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>32</v>
+      </c>
+      <c r="R70" t="s">
+        <v>32</v>
+      </c>
+      <c r="S70" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>142</v>
+      </c>
+      <c r="B71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" t="s">
+        <v>32</v>
+      </c>
+      <c r="D71" t="s">
+        <v>32</v>
+      </c>
+      <c r="E71" t="s">
+        <v>32</v>
+      </c>
+      <c r="F71" t="s">
+        <v>32</v>
+      </c>
+      <c r="G71" t="s">
+        <v>32</v>
+      </c>
+      <c r="H71" t="s">
+        <v>32</v>
+      </c>
+      <c r="I71" t="s">
+        <v>32</v>
+      </c>
+      <c r="J71" t="s">
+        <v>32</v>
+      </c>
+      <c r="K71" t="s">
+        <v>32</v>
+      </c>
+      <c r="L71" t="s">
+        <v>32</v>
+      </c>
+      <c r="M71" t="s">
+        <v>32</v>
+      </c>
+      <c r="N71" t="s">
+        <v>32</v>
+      </c>
+      <c r="O71" t="s">
+        <v>32</v>
+      </c>
+      <c r="P71" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>32</v>
+      </c>
+      <c r="R71" t="s">
+        <v>32</v>
+      </c>
+      <c r="S71" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72" t="s">
+        <v>32</v>
+      </c>
+      <c r="E72" t="s">
+        <v>32</v>
+      </c>
+      <c r="F72" t="s">
+        <v>32</v>
+      </c>
+      <c r="G72" t="s">
+        <v>32</v>
+      </c>
+      <c r="H72" t="s">
+        <v>32</v>
+      </c>
+      <c r="I72" t="s">
+        <v>32</v>
+      </c>
+      <c r="J72" t="s">
+        <v>32</v>
+      </c>
+      <c r="K72" t="s">
+        <v>32</v>
+      </c>
+      <c r="L72" t="s">
+        <v>32</v>
+      </c>
+      <c r="M72" t="s">
+        <v>32</v>
+      </c>
+      <c r="N72" t="s">
+        <v>32</v>
+      </c>
+      <c r="O72" t="s">
+        <v>32</v>
+      </c>
+      <c r="P72" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>32</v>
+      </c>
+      <c r="R72" t="s">
+        <v>32</v>
+      </c>
+      <c r="S72" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" t="s">
+        <v>32</v>
+      </c>
+      <c r="E73" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" t="s">
+        <v>32</v>
+      </c>
+      <c r="G73" t="s">
+        <v>32</v>
+      </c>
+      <c r="H73" t="s">
+        <v>32</v>
+      </c>
+      <c r="I73" t="s">
+        <v>32</v>
+      </c>
+      <c r="J73" t="s">
+        <v>32</v>
+      </c>
+      <c r="K73" t="s">
+        <v>32</v>
+      </c>
+      <c r="L73" t="s">
+        <v>32</v>
+      </c>
+      <c r="M73" t="s">
+        <v>32</v>
+      </c>
+      <c r="N73" t="s">
+        <v>32</v>
+      </c>
+      <c r="O73" t="s">
+        <v>32</v>
+      </c>
+      <c r="P73" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>32</v>
+      </c>
+      <c r="R73" t="s">
+        <v>32</v>
+      </c>
+      <c r="S73" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74" t="s">
+        <v>32</v>
+      </c>
+      <c r="E74" t="s">
+        <v>32</v>
+      </c>
+      <c r="F74" t="s">
+        <v>32</v>
+      </c>
+      <c r="G74" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" t="s">
+        <v>32</v>
+      </c>
+      <c r="I74" t="s">
+        <v>32</v>
+      </c>
+      <c r="J74" t="s">
+        <v>32</v>
+      </c>
+      <c r="K74" t="s">
+        <v>32</v>
+      </c>
+      <c r="L74" t="s">
+        <v>32</v>
+      </c>
+      <c r="M74" t="s">
+        <v>32</v>
+      </c>
+      <c r="N74" t="s">
+        <v>32</v>
+      </c>
+      <c r="O74" t="s">
+        <v>32</v>
+      </c>
+      <c r="P74" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>32</v>
+      </c>
+      <c r="R74" t="s">
+        <v>32</v>
+      </c>
+      <c r="S74" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
     <col min="1" max="1" width="10.71875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -16506,7 +21842,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>45</v>
@@ -16624,7 +21960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -16711,7 +22047,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>45</v>
@@ -16766,4409 +22102,6 @@
       </c>
       <c r="S2" s="1" t="s">
         <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection password="D4D4" sheet="true" scenarios="true" objects="true"/>
-  <mergeCells>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:S1"/>
-  </mergeCells>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="11.75390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" t="s">
-        <v>32</v>
-      </c>
-      <c r="S3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" t="s">
-        <v>32</v>
-      </c>
-      <c r="P5" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" t="s">
-        <v>32</v>
-      </c>
-      <c r="S5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6" t="s">
-        <v>32</v>
-      </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O6" t="s">
-        <v>32</v>
-      </c>
-      <c r="P6" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" t="s">
-        <v>32</v>
-      </c>
-      <c r="S6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" t="s">
-        <v>32</v>
-      </c>
-      <c r="P7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R7" t="s">
-        <v>32</v>
-      </c>
-      <c r="S7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" t="s">
-        <v>32</v>
-      </c>
-      <c r="O8" t="s">
-        <v>32</v>
-      </c>
-      <c r="P8" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R8" t="s">
-        <v>32</v>
-      </c>
-      <c r="S8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>32</v>
-      </c>
-      <c r="R9" t="s">
-        <v>32</v>
-      </c>
-      <c r="S9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" t="s">
-        <v>32</v>
-      </c>
-      <c r="N10" t="s">
-        <v>32</v>
-      </c>
-      <c r="O10" t="s">
-        <v>32</v>
-      </c>
-      <c r="P10" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R10" t="s">
-        <v>32</v>
-      </c>
-      <c r="S10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" t="s">
-        <v>32</v>
-      </c>
-      <c r="N11" t="s">
-        <v>32</v>
-      </c>
-      <c r="O11" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>32</v>
-      </c>
-      <c r="R11" t="s">
-        <v>32</v>
-      </c>
-      <c r="S11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12" t="s">
-        <v>32</v>
-      </c>
-      <c r="N12" t="s">
-        <v>32</v>
-      </c>
-      <c r="O12" t="s">
-        <v>32</v>
-      </c>
-      <c r="P12" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>32</v>
-      </c>
-      <c r="R12" t="s">
-        <v>32</v>
-      </c>
-      <c r="S12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" t="s">
-        <v>32</v>
-      </c>
-      <c r="M13" t="s">
-        <v>32</v>
-      </c>
-      <c r="N13" t="s">
-        <v>32</v>
-      </c>
-      <c r="O13" t="s">
-        <v>32</v>
-      </c>
-      <c r="P13" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>32</v>
-      </c>
-      <c r="R13" t="s">
-        <v>32</v>
-      </c>
-      <c r="S13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" t="s">
-        <v>32</v>
-      </c>
-      <c r="M14" t="s">
-        <v>32</v>
-      </c>
-      <c r="N14" t="s">
-        <v>32</v>
-      </c>
-      <c r="O14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P14" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>32</v>
-      </c>
-      <c r="R14" t="s">
-        <v>32</v>
-      </c>
-      <c r="S14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" t="s">
-        <v>32</v>
-      </c>
-      <c r="M15" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" t="s">
-        <v>32</v>
-      </c>
-      <c r="O15" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>32</v>
-      </c>
-      <c r="R15" t="s">
-        <v>32</v>
-      </c>
-      <c r="S15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" t="s">
-        <v>32</v>
-      </c>
-      <c r="L16" t="s">
-        <v>32</v>
-      </c>
-      <c r="M16" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" t="s">
-        <v>32</v>
-      </c>
-      <c r="O16" t="s">
-        <v>32</v>
-      </c>
-      <c r="P16" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>32</v>
-      </c>
-      <c r="R16" t="s">
-        <v>32</v>
-      </c>
-      <c r="S16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17" t="s">
-        <v>32</v>
-      </c>
-      <c r="L17" t="s">
-        <v>32</v>
-      </c>
-      <c r="M17" t="s">
-        <v>32</v>
-      </c>
-      <c r="N17" t="s">
-        <v>32</v>
-      </c>
-      <c r="O17" t="s">
-        <v>32</v>
-      </c>
-      <c r="P17" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>32</v>
-      </c>
-      <c r="R17" t="s">
-        <v>32</v>
-      </c>
-      <c r="S17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H18" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" t="s">
-        <v>32</v>
-      </c>
-      <c r="M18" t="s">
-        <v>32</v>
-      </c>
-      <c r="N18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O18" t="s">
-        <v>32</v>
-      </c>
-      <c r="P18" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>32</v>
-      </c>
-      <c r="R18" t="s">
-        <v>32</v>
-      </c>
-      <c r="S18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" t="s">
-        <v>32</v>
-      </c>
-      <c r="L19" t="s">
-        <v>32</v>
-      </c>
-      <c r="M19" t="s">
-        <v>32</v>
-      </c>
-      <c r="N19" t="s">
-        <v>32</v>
-      </c>
-      <c r="O19" t="s">
-        <v>32</v>
-      </c>
-      <c r="P19" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>32</v>
-      </c>
-      <c r="R19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" t="s">
-        <v>32</v>
-      </c>
-      <c r="K20" t="s">
-        <v>32</v>
-      </c>
-      <c r="L20" t="s">
-        <v>32</v>
-      </c>
-      <c r="M20" t="s">
-        <v>32</v>
-      </c>
-      <c r="N20" t="s">
-        <v>32</v>
-      </c>
-      <c r="O20" t="s">
-        <v>32</v>
-      </c>
-      <c r="P20" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>32</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" t="s">
-        <v>32</v>
-      </c>
-      <c r="K21" t="s">
-        <v>32</v>
-      </c>
-      <c r="L21" t="s">
-        <v>32</v>
-      </c>
-      <c r="M21" t="s">
-        <v>32</v>
-      </c>
-      <c r="N21" t="s">
-        <v>32</v>
-      </c>
-      <c r="O21" t="s">
-        <v>32</v>
-      </c>
-      <c r="P21" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>32</v>
-      </c>
-      <c r="R21" t="s">
-        <v>32</v>
-      </c>
-      <c r="S21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" t="s">
-        <v>32</v>
-      </c>
-      <c r="K22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L22" t="s">
-        <v>32</v>
-      </c>
-      <c r="M22" t="s">
-        <v>32</v>
-      </c>
-      <c r="N22" t="s">
-        <v>32</v>
-      </c>
-      <c r="O22" t="s">
-        <v>32</v>
-      </c>
-      <c r="P22" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" t="s">
-        <v>32</v>
-      </c>
-      <c r="S22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" t="s">
-        <v>32</v>
-      </c>
-      <c r="J23" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23" t="s">
-        <v>32</v>
-      </c>
-      <c r="L23" t="s">
-        <v>32</v>
-      </c>
-      <c r="M23" t="s">
-        <v>32</v>
-      </c>
-      <c r="N23" t="s">
-        <v>32</v>
-      </c>
-      <c r="O23" t="s">
-        <v>32</v>
-      </c>
-      <c r="P23" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>32</v>
-      </c>
-      <c r="R23" t="s">
-        <v>32</v>
-      </c>
-      <c r="S23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" t="s">
-        <v>32</v>
-      </c>
-      <c r="J24" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L24" t="s">
-        <v>32</v>
-      </c>
-      <c r="M24" t="s">
-        <v>32</v>
-      </c>
-      <c r="N24" t="s">
-        <v>32</v>
-      </c>
-      <c r="O24" t="s">
-        <v>32</v>
-      </c>
-      <c r="P24" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>32</v>
-      </c>
-      <c r="R24" t="s">
-        <v>32</v>
-      </c>
-      <c r="S24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" t="s">
-        <v>32</v>
-      </c>
-      <c r="J25" t="s">
-        <v>32</v>
-      </c>
-      <c r="K25" t="s">
-        <v>32</v>
-      </c>
-      <c r="L25" t="s">
-        <v>32</v>
-      </c>
-      <c r="M25" t="s">
-        <v>32</v>
-      </c>
-      <c r="N25" t="s">
-        <v>32</v>
-      </c>
-      <c r="O25" t="s">
-        <v>32</v>
-      </c>
-      <c r="P25" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>32</v>
-      </c>
-      <c r="R25" t="s">
-        <v>32</v>
-      </c>
-      <c r="S25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" t="s">
-        <v>32</v>
-      </c>
-      <c r="H26" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J26" t="s">
-        <v>32</v>
-      </c>
-      <c r="K26" t="s">
-        <v>32</v>
-      </c>
-      <c r="L26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N26" t="s">
-        <v>32</v>
-      </c>
-      <c r="O26" t="s">
-        <v>32</v>
-      </c>
-      <c r="P26" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>32</v>
-      </c>
-      <c r="R26" t="s">
-        <v>32</v>
-      </c>
-      <c r="S26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>98</v>
-      </c>
-      <c r="B27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" t="s">
-        <v>32</v>
-      </c>
-      <c r="H27" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27" t="s">
-        <v>32</v>
-      </c>
-      <c r="K27" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" t="s">
-        <v>32</v>
-      </c>
-      <c r="M27" t="s">
-        <v>32</v>
-      </c>
-      <c r="N27" t="s">
-        <v>32</v>
-      </c>
-      <c r="O27" t="s">
-        <v>32</v>
-      </c>
-      <c r="P27" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>32</v>
-      </c>
-      <c r="R27" t="s">
-        <v>32</v>
-      </c>
-      <c r="S27" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>99</v>
-      </c>
-      <c r="B28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" t="s">
-        <v>32</v>
-      </c>
-      <c r="H28" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" t="s">
-        <v>32</v>
-      </c>
-      <c r="K28" t="s">
-        <v>32</v>
-      </c>
-      <c r="L28" t="s">
-        <v>32</v>
-      </c>
-      <c r="M28" t="s">
-        <v>32</v>
-      </c>
-      <c r="N28" t="s">
-        <v>32</v>
-      </c>
-      <c r="O28" t="s">
-        <v>32</v>
-      </c>
-      <c r="P28" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>32</v>
-      </c>
-      <c r="R28" t="s">
-        <v>32</v>
-      </c>
-      <c r="S28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>100</v>
-      </c>
-      <c r="B29" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" t="s">
-        <v>32</v>
-      </c>
-      <c r="H29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" t="s">
-        <v>32</v>
-      </c>
-      <c r="J29" t="s">
-        <v>32</v>
-      </c>
-      <c r="K29" t="s">
-        <v>32</v>
-      </c>
-      <c r="L29" t="s">
-        <v>32</v>
-      </c>
-      <c r="M29" t="s">
-        <v>32</v>
-      </c>
-      <c r="N29" t="s">
-        <v>32</v>
-      </c>
-      <c r="O29" t="s">
-        <v>32</v>
-      </c>
-      <c r="P29" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>32</v>
-      </c>
-      <c r="R29" t="s">
-        <v>32</v>
-      </c>
-      <c r="S29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B30" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" t="s">
-        <v>32</v>
-      </c>
-      <c r="H30" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" t="s">
-        <v>32</v>
-      </c>
-      <c r="J30" t="s">
-        <v>32</v>
-      </c>
-      <c r="K30" t="s">
-        <v>32</v>
-      </c>
-      <c r="L30" t="s">
-        <v>32</v>
-      </c>
-      <c r="M30" t="s">
-        <v>32</v>
-      </c>
-      <c r="N30" t="s">
-        <v>32</v>
-      </c>
-      <c r="O30" t="s">
-        <v>32</v>
-      </c>
-      <c r="P30" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>32</v>
-      </c>
-      <c r="R30" t="s">
-        <v>32</v>
-      </c>
-      <c r="S30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>102</v>
-      </c>
-      <c r="B31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" t="s">
-        <v>32</v>
-      </c>
-      <c r="H31" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" t="s">
-        <v>32</v>
-      </c>
-      <c r="J31" t="s">
-        <v>32</v>
-      </c>
-      <c r="K31" t="s">
-        <v>32</v>
-      </c>
-      <c r="L31" t="s">
-        <v>32</v>
-      </c>
-      <c r="M31" t="s">
-        <v>32</v>
-      </c>
-      <c r="N31" t="s">
-        <v>32</v>
-      </c>
-      <c r="O31" t="s">
-        <v>32</v>
-      </c>
-      <c r="P31" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>32</v>
-      </c>
-      <c r="R31" t="s">
-        <v>32</v>
-      </c>
-      <c r="S31" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>103</v>
-      </c>
-      <c r="B32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G32" t="s">
-        <v>32</v>
-      </c>
-      <c r="H32" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" t="s">
-        <v>32</v>
-      </c>
-      <c r="J32" t="s">
-        <v>32</v>
-      </c>
-      <c r="K32" t="s">
-        <v>32</v>
-      </c>
-      <c r="L32" t="s">
-        <v>32</v>
-      </c>
-      <c r="M32" t="s">
-        <v>32</v>
-      </c>
-      <c r="N32" t="s">
-        <v>32</v>
-      </c>
-      <c r="O32" t="s">
-        <v>32</v>
-      </c>
-      <c r="P32" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>32</v>
-      </c>
-      <c r="R32" t="s">
-        <v>32</v>
-      </c>
-      <c r="S32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" t="s">
-        <v>32</v>
-      </c>
-      <c r="F33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G33" t="s">
-        <v>32</v>
-      </c>
-      <c r="H33" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" t="s">
-        <v>32</v>
-      </c>
-      <c r="J33" t="s">
-        <v>32</v>
-      </c>
-      <c r="K33" t="s">
-        <v>32</v>
-      </c>
-      <c r="L33" t="s">
-        <v>32</v>
-      </c>
-      <c r="M33" t="s">
-        <v>32</v>
-      </c>
-      <c r="N33" t="s">
-        <v>32</v>
-      </c>
-      <c r="O33" t="s">
-        <v>32</v>
-      </c>
-      <c r="P33" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>32</v>
-      </c>
-      <c r="R33" t="s">
-        <v>32</v>
-      </c>
-      <c r="S33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" t="s">
-        <v>32</v>
-      </c>
-      <c r="E34" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" t="s">
-        <v>32</v>
-      </c>
-      <c r="H34" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" t="s">
-        <v>32</v>
-      </c>
-      <c r="J34" t="s">
-        <v>32</v>
-      </c>
-      <c r="K34" t="s">
-        <v>32</v>
-      </c>
-      <c r="L34" t="s">
-        <v>32</v>
-      </c>
-      <c r="M34" t="s">
-        <v>32</v>
-      </c>
-      <c r="N34" t="s">
-        <v>32</v>
-      </c>
-      <c r="O34" t="s">
-        <v>32</v>
-      </c>
-      <c r="P34" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>32</v>
-      </c>
-      <c r="R34" t="s">
-        <v>32</v>
-      </c>
-      <c r="S34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>106</v>
-      </c>
-      <c r="B35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" t="s">
-        <v>32</v>
-      </c>
-      <c r="F35" t="s">
-        <v>32</v>
-      </c>
-      <c r="G35" t="s">
-        <v>32</v>
-      </c>
-      <c r="H35" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" t="s">
-        <v>32</v>
-      </c>
-      <c r="J35" t="s">
-        <v>32</v>
-      </c>
-      <c r="K35" t="s">
-        <v>32</v>
-      </c>
-      <c r="L35" t="s">
-        <v>32</v>
-      </c>
-      <c r="M35" t="s">
-        <v>32</v>
-      </c>
-      <c r="N35" t="s">
-        <v>32</v>
-      </c>
-      <c r="O35" t="s">
-        <v>32</v>
-      </c>
-      <c r="P35" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>32</v>
-      </c>
-      <c r="R35" t="s">
-        <v>32</v>
-      </c>
-      <c r="S35" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>107</v>
-      </c>
-      <c r="B36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" t="s">
-        <v>32</v>
-      </c>
-      <c r="F36" t="s">
-        <v>32</v>
-      </c>
-      <c r="G36" t="s">
-        <v>32</v>
-      </c>
-      <c r="H36" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" t="s">
-        <v>32</v>
-      </c>
-      <c r="J36" t="s">
-        <v>32</v>
-      </c>
-      <c r="K36" t="s">
-        <v>32</v>
-      </c>
-      <c r="L36" t="s">
-        <v>32</v>
-      </c>
-      <c r="M36" t="s">
-        <v>32</v>
-      </c>
-      <c r="N36" t="s">
-        <v>32</v>
-      </c>
-      <c r="O36" t="s">
-        <v>32</v>
-      </c>
-      <c r="P36" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>32</v>
-      </c>
-      <c r="R36" t="s">
-        <v>32</v>
-      </c>
-      <c r="S36" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>108</v>
-      </c>
-      <c r="B37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E37" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
-        <v>32</v>
-      </c>
-      <c r="H37" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" t="s">
-        <v>32</v>
-      </c>
-      <c r="J37" t="s">
-        <v>32</v>
-      </c>
-      <c r="K37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L37" t="s">
-        <v>32</v>
-      </c>
-      <c r="M37" t="s">
-        <v>32</v>
-      </c>
-      <c r="N37" t="s">
-        <v>32</v>
-      </c>
-      <c r="O37" t="s">
-        <v>32</v>
-      </c>
-      <c r="P37" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>32</v>
-      </c>
-      <c r="R37" t="s">
-        <v>32</v>
-      </c>
-      <c r="S37" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>109</v>
-      </c>
-      <c r="B38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" t="s">
-        <v>32</v>
-      </c>
-      <c r="E38" t="s">
-        <v>32</v>
-      </c>
-      <c r="F38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H38" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" t="s">
-        <v>32</v>
-      </c>
-      <c r="J38" t="s">
-        <v>32</v>
-      </c>
-      <c r="K38" t="s">
-        <v>32</v>
-      </c>
-      <c r="L38" t="s">
-        <v>32</v>
-      </c>
-      <c r="M38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N38" t="s">
-        <v>32</v>
-      </c>
-      <c r="O38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P38" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>32</v>
-      </c>
-      <c r="R38" t="s">
-        <v>32</v>
-      </c>
-      <c r="S38" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>110</v>
-      </c>
-      <c r="B39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" t="s">
-        <v>32</v>
-      </c>
-      <c r="F39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
-        <v>32</v>
-      </c>
-      <c r="H39" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" t="s">
-        <v>32</v>
-      </c>
-      <c r="J39" t="s">
-        <v>32</v>
-      </c>
-      <c r="K39" t="s">
-        <v>32</v>
-      </c>
-      <c r="L39" t="s">
-        <v>32</v>
-      </c>
-      <c r="M39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N39" t="s">
-        <v>32</v>
-      </c>
-      <c r="O39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P39" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>32</v>
-      </c>
-      <c r="R39" t="s">
-        <v>32</v>
-      </c>
-      <c r="S39" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>111</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E40" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" t="s">
-        <v>32</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K40" t="s">
-        <v>32</v>
-      </c>
-      <c r="L40" t="s">
-        <v>32</v>
-      </c>
-      <c r="M40" t="s">
-        <v>32</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>32</v>
-      </c>
-      <c r="R40" t="s">
-        <v>32</v>
-      </c>
-      <c r="S40" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>112</v>
-      </c>
-      <c r="B41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G41" t="s">
-        <v>32</v>
-      </c>
-      <c r="H41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I41" t="s">
-        <v>32</v>
-      </c>
-      <c r="J41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L41" t="s">
-        <v>32</v>
-      </c>
-      <c r="M41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N41" t="s">
-        <v>32</v>
-      </c>
-      <c r="O41" t="s">
-        <v>32</v>
-      </c>
-      <c r="P41" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>32</v>
-      </c>
-      <c r="R41" t="s">
-        <v>32</v>
-      </c>
-      <c r="S41" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>113</v>
-      </c>
-      <c r="B42" t="s">
-        <v>32</v>
-      </c>
-      <c r="C42" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F42" t="s">
-        <v>32</v>
-      </c>
-      <c r="G42" t="s">
-        <v>32</v>
-      </c>
-      <c r="H42" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" t="s">
-        <v>32</v>
-      </c>
-      <c r="J42" t="s">
-        <v>32</v>
-      </c>
-      <c r="K42" t="s">
-        <v>32</v>
-      </c>
-      <c r="L42" t="s">
-        <v>32</v>
-      </c>
-      <c r="M42" t="s">
-        <v>32</v>
-      </c>
-      <c r="N42" t="s">
-        <v>32</v>
-      </c>
-      <c r="O42" t="s">
-        <v>32</v>
-      </c>
-      <c r="P42" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>32</v>
-      </c>
-      <c r="R42" t="s">
-        <v>32</v>
-      </c>
-      <c r="S42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B43" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" t="s">
-        <v>32</v>
-      </c>
-      <c r="D43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E43" t="s">
-        <v>32</v>
-      </c>
-      <c r="F43" t="s">
-        <v>32</v>
-      </c>
-      <c r="G43" t="s">
-        <v>32</v>
-      </c>
-      <c r="H43" t="s">
-        <v>32</v>
-      </c>
-      <c r="I43" t="s">
-        <v>32</v>
-      </c>
-      <c r="J43" t="s">
-        <v>32</v>
-      </c>
-      <c r="K43" t="s">
-        <v>32</v>
-      </c>
-      <c r="L43" t="s">
-        <v>32</v>
-      </c>
-      <c r="M43" t="s">
-        <v>32</v>
-      </c>
-      <c r="N43" t="s">
-        <v>32</v>
-      </c>
-      <c r="O43" t="s">
-        <v>32</v>
-      </c>
-      <c r="P43" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>32</v>
-      </c>
-      <c r="R43" t="s">
-        <v>32</v>
-      </c>
-      <c r="S43" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>115</v>
-      </c>
-      <c r="B44" t="s">
-        <v>32</v>
-      </c>
-      <c r="C44" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" t="s">
-        <v>32</v>
-      </c>
-      <c r="E44" t="s">
-        <v>32</v>
-      </c>
-      <c r="F44" t="s">
-        <v>32</v>
-      </c>
-      <c r="G44" t="s">
-        <v>32</v>
-      </c>
-      <c r="H44" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" t="s">
-        <v>32</v>
-      </c>
-      <c r="J44" t="s">
-        <v>32</v>
-      </c>
-      <c r="K44" t="s">
-        <v>32</v>
-      </c>
-      <c r="L44" t="s">
-        <v>32</v>
-      </c>
-      <c r="M44" t="s">
-        <v>32</v>
-      </c>
-      <c r="N44" t="s">
-        <v>32</v>
-      </c>
-      <c r="O44" t="s">
-        <v>32</v>
-      </c>
-      <c r="P44" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>32</v>
-      </c>
-      <c r="R44" t="s">
-        <v>32</v>
-      </c>
-      <c r="S44" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>116</v>
-      </c>
-      <c r="B45" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" t="s">
-        <v>32</v>
-      </c>
-      <c r="E45" t="s">
-        <v>32</v>
-      </c>
-      <c r="F45" t="s">
-        <v>32</v>
-      </c>
-      <c r="G45" t="s">
-        <v>32</v>
-      </c>
-      <c r="H45" t="s">
-        <v>32</v>
-      </c>
-      <c r="I45" t="s">
-        <v>32</v>
-      </c>
-      <c r="J45" t="s">
-        <v>32</v>
-      </c>
-      <c r="K45" t="s">
-        <v>32</v>
-      </c>
-      <c r="L45" t="s">
-        <v>32</v>
-      </c>
-      <c r="M45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N45" t="s">
-        <v>32</v>
-      </c>
-      <c r="O45" t="s">
-        <v>32</v>
-      </c>
-      <c r="P45" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>32</v>
-      </c>
-      <c r="R45" t="s">
-        <v>32</v>
-      </c>
-      <c r="S45" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>117</v>
-      </c>
-      <c r="B46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" t="s">
-        <v>32</v>
-      </c>
-      <c r="E46" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" t="s">
-        <v>32</v>
-      </c>
-      <c r="G46" t="s">
-        <v>32</v>
-      </c>
-      <c r="H46" t="s">
-        <v>32</v>
-      </c>
-      <c r="I46" t="s">
-        <v>32</v>
-      </c>
-      <c r="J46" t="s">
-        <v>32</v>
-      </c>
-      <c r="K46" t="s">
-        <v>32</v>
-      </c>
-      <c r="L46" t="s">
-        <v>32</v>
-      </c>
-      <c r="M46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N46" t="s">
-        <v>32</v>
-      </c>
-      <c r="O46" t="s">
-        <v>32</v>
-      </c>
-      <c r="P46" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>32</v>
-      </c>
-      <c r="R46" t="s">
-        <v>32</v>
-      </c>
-      <c r="S46" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>118</v>
-      </c>
-      <c r="B47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" t="s">
-        <v>32</v>
-      </c>
-      <c r="D47" t="s">
-        <v>32</v>
-      </c>
-      <c r="E47" t="s">
-        <v>32</v>
-      </c>
-      <c r="F47" t="s">
-        <v>32</v>
-      </c>
-      <c r="G47" t="s">
-        <v>32</v>
-      </c>
-      <c r="H47" t="s">
-        <v>32</v>
-      </c>
-      <c r="I47" t="s">
-        <v>32</v>
-      </c>
-      <c r="J47" t="s">
-        <v>32</v>
-      </c>
-      <c r="K47" t="s">
-        <v>32</v>
-      </c>
-      <c r="L47" t="s">
-        <v>32</v>
-      </c>
-      <c r="M47" t="s">
-        <v>32</v>
-      </c>
-      <c r="N47" t="s">
-        <v>32</v>
-      </c>
-      <c r="O47" t="s">
-        <v>32</v>
-      </c>
-      <c r="P47" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>32</v>
-      </c>
-      <c r="R47" t="s">
-        <v>32</v>
-      </c>
-      <c r="S47" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>119</v>
-      </c>
-      <c r="B48" t="s">
-        <v>32</v>
-      </c>
-      <c r="C48" t="s">
-        <v>32</v>
-      </c>
-      <c r="D48" t="s">
-        <v>32</v>
-      </c>
-      <c r="E48" t="s">
-        <v>32</v>
-      </c>
-      <c r="F48" t="s">
-        <v>32</v>
-      </c>
-      <c r="G48" t="s">
-        <v>32</v>
-      </c>
-      <c r="H48" t="s">
-        <v>32</v>
-      </c>
-      <c r="I48" t="s">
-        <v>32</v>
-      </c>
-      <c r="J48" t="s">
-        <v>32</v>
-      </c>
-      <c r="K48" t="s">
-        <v>32</v>
-      </c>
-      <c r="L48" t="s">
-        <v>32</v>
-      </c>
-      <c r="M48" t="s">
-        <v>32</v>
-      </c>
-      <c r="N48" t="s">
-        <v>32</v>
-      </c>
-      <c r="O48" t="s">
-        <v>32</v>
-      </c>
-      <c r="P48" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R48" t="s">
-        <v>32</v>
-      </c>
-      <c r="S48" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>120</v>
-      </c>
-      <c r="B49" t="s">
-        <v>32</v>
-      </c>
-      <c r="C49" t="s">
-        <v>32</v>
-      </c>
-      <c r="D49" t="s">
-        <v>32</v>
-      </c>
-      <c r="E49" t="s">
-        <v>32</v>
-      </c>
-      <c r="F49" t="s">
-        <v>32</v>
-      </c>
-      <c r="G49" t="s">
-        <v>32</v>
-      </c>
-      <c r="H49" t="s">
-        <v>32</v>
-      </c>
-      <c r="I49" t="s">
-        <v>32</v>
-      </c>
-      <c r="J49" t="s">
-        <v>32</v>
-      </c>
-      <c r="K49" t="s">
-        <v>32</v>
-      </c>
-      <c r="L49" t="s">
-        <v>32</v>
-      </c>
-      <c r="M49" t="s">
-        <v>32</v>
-      </c>
-      <c r="N49" t="s">
-        <v>32</v>
-      </c>
-      <c r="O49" t="s">
-        <v>32</v>
-      </c>
-      <c r="P49" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>32</v>
-      </c>
-      <c r="R49" t="s">
-        <v>32</v>
-      </c>
-      <c r="S49" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>121</v>
-      </c>
-      <c r="B50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" t="s">
-        <v>32</v>
-      </c>
-      <c r="D50" t="s">
-        <v>32</v>
-      </c>
-      <c r="E50" t="s">
-        <v>32</v>
-      </c>
-      <c r="F50" t="s">
-        <v>32</v>
-      </c>
-      <c r="G50" t="s">
-        <v>32</v>
-      </c>
-      <c r="H50" t="s">
-        <v>32</v>
-      </c>
-      <c r="I50" t="s">
-        <v>32</v>
-      </c>
-      <c r="J50" t="s">
-        <v>32</v>
-      </c>
-      <c r="K50" t="s">
-        <v>32</v>
-      </c>
-      <c r="L50" t="s">
-        <v>32</v>
-      </c>
-      <c r="M50" t="s">
-        <v>32</v>
-      </c>
-      <c r="N50" t="s">
-        <v>32</v>
-      </c>
-      <c r="O50" t="s">
-        <v>32</v>
-      </c>
-      <c r="P50" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>32</v>
-      </c>
-      <c r="R50" t="s">
-        <v>32</v>
-      </c>
-      <c r="S50" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>122</v>
-      </c>
-      <c r="B51" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" t="s">
-        <v>32</v>
-      </c>
-      <c r="D51" t="s">
-        <v>32</v>
-      </c>
-      <c r="E51" t="s">
-        <v>32</v>
-      </c>
-      <c r="F51" t="s">
-        <v>32</v>
-      </c>
-      <c r="G51" t="s">
-        <v>32</v>
-      </c>
-      <c r="H51" t="s">
-        <v>32</v>
-      </c>
-      <c r="I51" t="s">
-        <v>32</v>
-      </c>
-      <c r="J51" t="s">
-        <v>32</v>
-      </c>
-      <c r="K51" t="s">
-        <v>32</v>
-      </c>
-      <c r="L51" t="s">
-        <v>32</v>
-      </c>
-      <c r="M51" t="s">
-        <v>32</v>
-      </c>
-      <c r="N51" t="s">
-        <v>32</v>
-      </c>
-      <c r="O51" t="s">
-        <v>32</v>
-      </c>
-      <c r="P51" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>32</v>
-      </c>
-      <c r="R51" t="s">
-        <v>32</v>
-      </c>
-      <c r="S51" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>123</v>
-      </c>
-      <c r="B52" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" t="s">
-        <v>32</v>
-      </c>
-      <c r="E52" t="s">
-        <v>32</v>
-      </c>
-      <c r="F52" t="s">
-        <v>32</v>
-      </c>
-      <c r="G52" t="s">
-        <v>32</v>
-      </c>
-      <c r="H52" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" t="s">
-        <v>32</v>
-      </c>
-      <c r="J52" t="s">
-        <v>32</v>
-      </c>
-      <c r="K52" t="s">
-        <v>32</v>
-      </c>
-      <c r="L52" t="s">
-        <v>32</v>
-      </c>
-      <c r="M52" t="s">
-        <v>32</v>
-      </c>
-      <c r="N52" t="s">
-        <v>32</v>
-      </c>
-      <c r="O52" t="s">
-        <v>32</v>
-      </c>
-      <c r="P52" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>32</v>
-      </c>
-      <c r="R52" t="s">
-        <v>32</v>
-      </c>
-      <c r="S52" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>124</v>
-      </c>
-      <c r="B53" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" t="s">
-        <v>32</v>
-      </c>
-      <c r="E53" t="s">
-        <v>32</v>
-      </c>
-      <c r="F53" t="s">
-        <v>32</v>
-      </c>
-      <c r="G53" t="s">
-        <v>32</v>
-      </c>
-      <c r="H53" t="s">
-        <v>32</v>
-      </c>
-      <c r="I53" t="s">
-        <v>32</v>
-      </c>
-      <c r="J53" t="s">
-        <v>32</v>
-      </c>
-      <c r="K53" t="s">
-        <v>32</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M53" t="s">
-        <v>32</v>
-      </c>
-      <c r="N53" t="s">
-        <v>32</v>
-      </c>
-      <c r="O53" t="s">
-        <v>32</v>
-      </c>
-      <c r="P53" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>32</v>
-      </c>
-      <c r="R53" t="s">
-        <v>32</v>
-      </c>
-      <c r="S53" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>125</v>
-      </c>
-      <c r="B54" t="s">
-        <v>32</v>
-      </c>
-      <c r="C54" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" t="s">
-        <v>32</v>
-      </c>
-      <c r="E54" t="s">
-        <v>32</v>
-      </c>
-      <c r="F54" t="s">
-        <v>32</v>
-      </c>
-      <c r="G54" t="s">
-        <v>32</v>
-      </c>
-      <c r="H54" t="s">
-        <v>32</v>
-      </c>
-      <c r="I54" t="s">
-        <v>32</v>
-      </c>
-      <c r="J54" t="s">
-        <v>32</v>
-      </c>
-      <c r="K54" t="s">
-        <v>32</v>
-      </c>
-      <c r="L54" t="s">
-        <v>32</v>
-      </c>
-      <c r="M54" t="s">
-        <v>32</v>
-      </c>
-      <c r="N54" t="s">
-        <v>32</v>
-      </c>
-      <c r="O54" t="s">
-        <v>32</v>
-      </c>
-      <c r="P54" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>32</v>
-      </c>
-      <c r="R54" t="s">
-        <v>32</v>
-      </c>
-      <c r="S54" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>126</v>
-      </c>
-      <c r="B55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" t="s">
-        <v>32</v>
-      </c>
-      <c r="D55" t="s">
-        <v>32</v>
-      </c>
-      <c r="E55" t="s">
-        <v>32</v>
-      </c>
-      <c r="F55" t="s">
-        <v>32</v>
-      </c>
-      <c r="G55" t="s">
-        <v>32</v>
-      </c>
-      <c r="H55" t="s">
-        <v>32</v>
-      </c>
-      <c r="I55" t="s">
-        <v>32</v>
-      </c>
-      <c r="J55" t="s">
-        <v>32</v>
-      </c>
-      <c r="K55" t="s">
-        <v>32</v>
-      </c>
-      <c r="L55" t="s">
-        <v>32</v>
-      </c>
-      <c r="M55" t="s">
-        <v>32</v>
-      </c>
-      <c r="N55" t="s">
-        <v>32</v>
-      </c>
-      <c r="O55" t="s">
-        <v>32</v>
-      </c>
-      <c r="P55" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>32</v>
-      </c>
-      <c r="R55" t="s">
-        <v>32</v>
-      </c>
-      <c r="S55" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>127</v>
-      </c>
-      <c r="B56" t="s">
-        <v>32</v>
-      </c>
-      <c r="C56" t="s">
-        <v>32</v>
-      </c>
-      <c r="D56" t="s">
-        <v>32</v>
-      </c>
-      <c r="E56" t="s">
-        <v>32</v>
-      </c>
-      <c r="F56" t="s">
-        <v>32</v>
-      </c>
-      <c r="G56" t="s">
-        <v>32</v>
-      </c>
-      <c r="H56" t="s">
-        <v>32</v>
-      </c>
-      <c r="I56" t="s">
-        <v>32</v>
-      </c>
-      <c r="J56" t="s">
-        <v>32</v>
-      </c>
-      <c r="K56" t="s">
-        <v>32</v>
-      </c>
-      <c r="L56" t="s">
-        <v>32</v>
-      </c>
-      <c r="M56" t="s">
-        <v>32</v>
-      </c>
-      <c r="N56" t="s">
-        <v>32</v>
-      </c>
-      <c r="O56" t="s">
-        <v>32</v>
-      </c>
-      <c r="P56" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>32</v>
-      </c>
-      <c r="R56" t="s">
-        <v>32</v>
-      </c>
-      <c r="S56" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>128</v>
-      </c>
-      <c r="B57" t="s">
-        <v>32</v>
-      </c>
-      <c r="C57" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" t="s">
-        <v>32</v>
-      </c>
-      <c r="E57" t="s">
-        <v>32</v>
-      </c>
-      <c r="F57" t="s">
-        <v>32</v>
-      </c>
-      <c r="G57" t="s">
-        <v>32</v>
-      </c>
-      <c r="H57" t="s">
-        <v>32</v>
-      </c>
-      <c r="I57" t="s">
-        <v>32</v>
-      </c>
-      <c r="J57" t="s">
-        <v>32</v>
-      </c>
-      <c r="K57" t="s">
-        <v>32</v>
-      </c>
-      <c r="L57" t="s">
-        <v>32</v>
-      </c>
-      <c r="M57" t="s">
-        <v>32</v>
-      </c>
-      <c r="N57" t="s">
-        <v>32</v>
-      </c>
-      <c r="O57" t="s">
-        <v>32</v>
-      </c>
-      <c r="P57" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>32</v>
-      </c>
-      <c r="R57" t="s">
-        <v>32</v>
-      </c>
-      <c r="S57" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>129</v>
-      </c>
-      <c r="B58" t="s">
-        <v>32</v>
-      </c>
-      <c r="C58" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" t="s">
-        <v>32</v>
-      </c>
-      <c r="E58" t="s">
-        <v>32</v>
-      </c>
-      <c r="F58" t="s">
-        <v>32</v>
-      </c>
-      <c r="G58" t="s">
-        <v>32</v>
-      </c>
-      <c r="H58" t="s">
-        <v>32</v>
-      </c>
-      <c r="I58" t="s">
-        <v>32</v>
-      </c>
-      <c r="J58" t="s">
-        <v>32</v>
-      </c>
-      <c r="K58" t="s">
-        <v>32</v>
-      </c>
-      <c r="L58" t="s">
-        <v>32</v>
-      </c>
-      <c r="M58" t="s">
-        <v>32</v>
-      </c>
-      <c r="N58" t="s">
-        <v>32</v>
-      </c>
-      <c r="O58" t="s">
-        <v>32</v>
-      </c>
-      <c r="P58" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>32</v>
-      </c>
-      <c r="R58" t="s">
-        <v>32</v>
-      </c>
-      <c r="S58" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>130</v>
-      </c>
-      <c r="B59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C59" t="s">
-        <v>32</v>
-      </c>
-      <c r="D59" t="s">
-        <v>32</v>
-      </c>
-      <c r="E59" t="s">
-        <v>32</v>
-      </c>
-      <c r="F59" t="s">
-        <v>32</v>
-      </c>
-      <c r="G59" t="s">
-        <v>32</v>
-      </c>
-      <c r="H59" t="s">
-        <v>32</v>
-      </c>
-      <c r="I59" t="s">
-        <v>32</v>
-      </c>
-      <c r="J59" t="s">
-        <v>32</v>
-      </c>
-      <c r="K59" t="s">
-        <v>32</v>
-      </c>
-      <c r="L59" t="s">
-        <v>32</v>
-      </c>
-      <c r="M59" t="s">
-        <v>32</v>
-      </c>
-      <c r="N59" t="s">
-        <v>32</v>
-      </c>
-      <c r="O59" t="s">
-        <v>32</v>
-      </c>
-      <c r="P59" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>32</v>
-      </c>
-      <c r="R59" t="s">
-        <v>32</v>
-      </c>
-      <c r="S59" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>131</v>
-      </c>
-      <c r="B60" t="s">
-        <v>32</v>
-      </c>
-      <c r="C60" t="s">
-        <v>32</v>
-      </c>
-      <c r="D60" t="s">
-        <v>32</v>
-      </c>
-      <c r="E60" t="s">
-        <v>32</v>
-      </c>
-      <c r="F60" t="s">
-        <v>32</v>
-      </c>
-      <c r="G60" t="s">
-        <v>32</v>
-      </c>
-      <c r="H60" t="s">
-        <v>32</v>
-      </c>
-      <c r="I60" t="s">
-        <v>32</v>
-      </c>
-      <c r="J60" t="s">
-        <v>32</v>
-      </c>
-      <c r="K60" t="s">
-        <v>32</v>
-      </c>
-      <c r="L60" t="s">
-        <v>32</v>
-      </c>
-      <c r="M60" t="s">
-        <v>32</v>
-      </c>
-      <c r="N60" t="s">
-        <v>32</v>
-      </c>
-      <c r="O60" t="s">
-        <v>32</v>
-      </c>
-      <c r="P60" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>32</v>
-      </c>
-      <c r="R60" t="s">
-        <v>32</v>
-      </c>
-      <c r="S60" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>132</v>
-      </c>
-      <c r="B61" t="s">
-        <v>32</v>
-      </c>
-      <c r="C61" t="s">
-        <v>32</v>
-      </c>
-      <c r="D61" t="s">
-        <v>32</v>
-      </c>
-      <c r="E61" t="s">
-        <v>32</v>
-      </c>
-      <c r="F61" t="s">
-        <v>32</v>
-      </c>
-      <c r="G61" t="s">
-        <v>32</v>
-      </c>
-      <c r="H61" t="s">
-        <v>32</v>
-      </c>
-      <c r="I61" t="s">
-        <v>32</v>
-      </c>
-      <c r="J61" t="s">
-        <v>32</v>
-      </c>
-      <c r="K61" t="s">
-        <v>32</v>
-      </c>
-      <c r="L61" t="s">
-        <v>32</v>
-      </c>
-      <c r="M61" t="s">
-        <v>32</v>
-      </c>
-      <c r="N61" t="s">
-        <v>32</v>
-      </c>
-      <c r="O61" t="s">
-        <v>32</v>
-      </c>
-      <c r="P61" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>32</v>
-      </c>
-      <c r="R61" t="s">
-        <v>32</v>
-      </c>
-      <c r="S61" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>133</v>
-      </c>
-      <c r="B62" t="s">
-        <v>32</v>
-      </c>
-      <c r="C62" t="s">
-        <v>32</v>
-      </c>
-      <c r="D62" t="s">
-        <v>32</v>
-      </c>
-      <c r="E62" t="s">
-        <v>32</v>
-      </c>
-      <c r="F62" t="s">
-        <v>32</v>
-      </c>
-      <c r="G62" t="s">
-        <v>32</v>
-      </c>
-      <c r="H62" t="s">
-        <v>32</v>
-      </c>
-      <c r="I62" t="s">
-        <v>32</v>
-      </c>
-      <c r="J62" t="s">
-        <v>32</v>
-      </c>
-      <c r="K62" t="s">
-        <v>32</v>
-      </c>
-      <c r="L62" t="s">
-        <v>32</v>
-      </c>
-      <c r="M62" t="s">
-        <v>32</v>
-      </c>
-      <c r="N62" t="s">
-        <v>32</v>
-      </c>
-      <c r="O62" t="s">
-        <v>32</v>
-      </c>
-      <c r="P62" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>32</v>
-      </c>
-      <c r="R62" t="s">
-        <v>32</v>
-      </c>
-      <c r="S62" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>134</v>
-      </c>
-      <c r="B63" t="s">
-        <v>32</v>
-      </c>
-      <c r="C63" t="s">
-        <v>32</v>
-      </c>
-      <c r="D63" t="s">
-        <v>32</v>
-      </c>
-      <c r="E63" t="s">
-        <v>32</v>
-      </c>
-      <c r="F63" t="s">
-        <v>32</v>
-      </c>
-      <c r="G63" t="s">
-        <v>32</v>
-      </c>
-      <c r="H63" t="s">
-        <v>32</v>
-      </c>
-      <c r="I63" t="s">
-        <v>32</v>
-      </c>
-      <c r="J63" t="s">
-        <v>32</v>
-      </c>
-      <c r="K63" t="s">
-        <v>32</v>
-      </c>
-      <c r="L63" t="s">
-        <v>32</v>
-      </c>
-      <c r="M63" t="s">
-        <v>32</v>
-      </c>
-      <c r="N63" t="s">
-        <v>32</v>
-      </c>
-      <c r="O63" t="s">
-        <v>32</v>
-      </c>
-      <c r="P63" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>32</v>
-      </c>
-      <c r="R63" t="s">
-        <v>32</v>
-      </c>
-      <c r="S63" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>135</v>
-      </c>
-      <c r="B64" t="s">
-        <v>32</v>
-      </c>
-      <c r="C64" t="s">
-        <v>32</v>
-      </c>
-      <c r="D64" t="s">
-        <v>32</v>
-      </c>
-      <c r="E64" t="s">
-        <v>32</v>
-      </c>
-      <c r="F64" t="s">
-        <v>32</v>
-      </c>
-      <c r="G64" t="s">
-        <v>32</v>
-      </c>
-      <c r="H64" t="s">
-        <v>32</v>
-      </c>
-      <c r="I64" t="s">
-        <v>32</v>
-      </c>
-      <c r="J64" t="s">
-        <v>32</v>
-      </c>
-      <c r="K64" t="s">
-        <v>32</v>
-      </c>
-      <c r="L64" t="s">
-        <v>32</v>
-      </c>
-      <c r="M64" t="s">
-        <v>32</v>
-      </c>
-      <c r="N64" t="s">
-        <v>32</v>
-      </c>
-      <c r="O64" t="s">
-        <v>32</v>
-      </c>
-      <c r="P64" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>32</v>
-      </c>
-      <c r="R64" t="s">
-        <v>32</v>
-      </c>
-      <c r="S64" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>136</v>
-      </c>
-      <c r="B65" t="s">
-        <v>32</v>
-      </c>
-      <c r="C65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D65" t="s">
-        <v>32</v>
-      </c>
-      <c r="E65" t="s">
-        <v>32</v>
-      </c>
-      <c r="F65" t="s">
-        <v>32</v>
-      </c>
-      <c r="G65" t="s">
-        <v>32</v>
-      </c>
-      <c r="H65" t="s">
-        <v>32</v>
-      </c>
-      <c r="I65" t="s">
-        <v>32</v>
-      </c>
-      <c r="J65" t="s">
-        <v>32</v>
-      </c>
-      <c r="K65" t="s">
-        <v>32</v>
-      </c>
-      <c r="L65" t="s">
-        <v>32</v>
-      </c>
-      <c r="M65" t="s">
-        <v>32</v>
-      </c>
-      <c r="N65" t="s">
-        <v>32</v>
-      </c>
-      <c r="O65" t="s">
-        <v>32</v>
-      </c>
-      <c r="P65" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>32</v>
-      </c>
-      <c r="R65" t="s">
-        <v>32</v>
-      </c>
-      <c r="S65" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>137</v>
-      </c>
-      <c r="B66" t="s">
-        <v>32</v>
-      </c>
-      <c r="C66" t="s">
-        <v>32</v>
-      </c>
-      <c r="D66" t="s">
-        <v>32</v>
-      </c>
-      <c r="E66" t="s">
-        <v>32</v>
-      </c>
-      <c r="F66" t="s">
-        <v>32</v>
-      </c>
-      <c r="G66" t="s">
-        <v>32</v>
-      </c>
-      <c r="H66" t="s">
-        <v>32</v>
-      </c>
-      <c r="I66" t="s">
-        <v>32</v>
-      </c>
-      <c r="J66" t="s">
-        <v>32</v>
-      </c>
-      <c r="K66" t="s">
-        <v>32</v>
-      </c>
-      <c r="L66" t="s">
-        <v>32</v>
-      </c>
-      <c r="M66" t="s">
-        <v>32</v>
-      </c>
-      <c r="N66" t="s">
-        <v>32</v>
-      </c>
-      <c r="O66" t="s">
-        <v>32</v>
-      </c>
-      <c r="P66" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>32</v>
-      </c>
-      <c r="R66" t="s">
-        <v>32</v>
-      </c>
-      <c r="S66" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>138</v>
-      </c>
-      <c r="B67" t="s">
-        <v>32</v>
-      </c>
-      <c r="C67" t="s">
-        <v>32</v>
-      </c>
-      <c r="D67" t="s">
-        <v>32</v>
-      </c>
-      <c r="E67" t="s">
-        <v>32</v>
-      </c>
-      <c r="F67" t="s">
-        <v>32</v>
-      </c>
-      <c r="G67" t="s">
-        <v>32</v>
-      </c>
-      <c r="H67" t="s">
-        <v>32</v>
-      </c>
-      <c r="I67" t="s">
-        <v>32</v>
-      </c>
-      <c r="J67" t="s">
-        <v>32</v>
-      </c>
-      <c r="K67" t="s">
-        <v>32</v>
-      </c>
-      <c r="L67" t="s">
-        <v>32</v>
-      </c>
-      <c r="M67" t="s">
-        <v>32</v>
-      </c>
-      <c r="N67" t="s">
-        <v>32</v>
-      </c>
-      <c r="O67" t="s">
-        <v>32</v>
-      </c>
-      <c r="P67" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>32</v>
-      </c>
-      <c r="R67" t="s">
-        <v>32</v>
-      </c>
-      <c r="S67" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>139</v>
-      </c>
-      <c r="B68" t="s">
-        <v>32</v>
-      </c>
-      <c r="C68" t="s">
-        <v>32</v>
-      </c>
-      <c r="D68" t="s">
-        <v>32</v>
-      </c>
-      <c r="E68" t="s">
-        <v>32</v>
-      </c>
-      <c r="F68" t="s">
-        <v>32</v>
-      </c>
-      <c r="G68" t="s">
-        <v>32</v>
-      </c>
-      <c r="H68" t="s">
-        <v>32</v>
-      </c>
-      <c r="I68" t="s">
-        <v>32</v>
-      </c>
-      <c r="J68" t="s">
-        <v>32</v>
-      </c>
-      <c r="K68" t="s">
-        <v>32</v>
-      </c>
-      <c r="L68" t="s">
-        <v>32</v>
-      </c>
-      <c r="M68" t="s">
-        <v>32</v>
-      </c>
-      <c r="N68" t="s">
-        <v>32</v>
-      </c>
-      <c r="O68" t="s">
-        <v>32</v>
-      </c>
-      <c r="P68" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>32</v>
-      </c>
-      <c r="R68" t="s">
-        <v>32</v>
-      </c>
-      <c r="S68" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>140</v>
-      </c>
-      <c r="B69" t="s">
-        <v>32</v>
-      </c>
-      <c r="C69" t="s">
-        <v>32</v>
-      </c>
-      <c r="D69" t="s">
-        <v>32</v>
-      </c>
-      <c r="E69" t="s">
-        <v>32</v>
-      </c>
-      <c r="F69" t="s">
-        <v>32</v>
-      </c>
-      <c r="G69" t="s">
-        <v>32</v>
-      </c>
-      <c r="H69" t="s">
-        <v>32</v>
-      </c>
-      <c r="I69" t="s">
-        <v>32</v>
-      </c>
-      <c r="J69" t="s">
-        <v>32</v>
-      </c>
-      <c r="K69" t="s">
-        <v>32</v>
-      </c>
-      <c r="L69" t="s">
-        <v>32</v>
-      </c>
-      <c r="M69" t="s">
-        <v>32</v>
-      </c>
-      <c r="N69" t="s">
-        <v>32</v>
-      </c>
-      <c r="O69" t="s">
-        <v>32</v>
-      </c>
-      <c r="P69" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>32</v>
-      </c>
-      <c r="R69" t="s">
-        <v>32</v>
-      </c>
-      <c r="S69" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>141</v>
-      </c>
-      <c r="B70" t="s">
-        <v>32</v>
-      </c>
-      <c r="C70" t="s">
-        <v>32</v>
-      </c>
-      <c r="D70" t="s">
-        <v>32</v>
-      </c>
-      <c r="E70" t="s">
-        <v>32</v>
-      </c>
-      <c r="F70" t="s">
-        <v>32</v>
-      </c>
-      <c r="G70" t="s">
-        <v>32</v>
-      </c>
-      <c r="H70" t="s">
-        <v>32</v>
-      </c>
-      <c r="I70" t="s">
-        <v>32</v>
-      </c>
-      <c r="J70" t="s">
-        <v>32</v>
-      </c>
-      <c r="K70" t="s">
-        <v>32</v>
-      </c>
-      <c r="L70" t="s">
-        <v>32</v>
-      </c>
-      <c r="M70" t="s">
-        <v>32</v>
-      </c>
-      <c r="N70" t="s">
-        <v>32</v>
-      </c>
-      <c r="O70" t="s">
-        <v>32</v>
-      </c>
-      <c r="P70" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>32</v>
-      </c>
-      <c r="R70" t="s">
-        <v>32</v>
-      </c>
-      <c r="S70" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>142</v>
-      </c>
-      <c r="B71" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" t="s">
-        <v>32</v>
-      </c>
-      <c r="D71" t="s">
-        <v>32</v>
-      </c>
-      <c r="E71" t="s">
-        <v>32</v>
-      </c>
-      <c r="F71" t="s">
-        <v>32</v>
-      </c>
-      <c r="G71" t="s">
-        <v>32</v>
-      </c>
-      <c r="H71" t="s">
-        <v>32</v>
-      </c>
-      <c r="I71" t="s">
-        <v>32</v>
-      </c>
-      <c r="J71" t="s">
-        <v>32</v>
-      </c>
-      <c r="K71" t="s">
-        <v>32</v>
-      </c>
-      <c r="L71" t="s">
-        <v>32</v>
-      </c>
-      <c r="M71" t="s">
-        <v>32</v>
-      </c>
-      <c r="N71" t="s">
-        <v>32</v>
-      </c>
-      <c r="O71" t="s">
-        <v>32</v>
-      </c>
-      <c r="P71" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>32</v>
-      </c>
-      <c r="R71" t="s">
-        <v>32</v>
-      </c>
-      <c r="S71" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>143</v>
-      </c>
-      <c r="B72" t="s">
-        <v>32</v>
-      </c>
-      <c r="C72" t="s">
-        <v>32</v>
-      </c>
-      <c r="D72" t="s">
-        <v>32</v>
-      </c>
-      <c r="E72" t="s">
-        <v>32</v>
-      </c>
-      <c r="F72" t="s">
-        <v>32</v>
-      </c>
-      <c r="G72" t="s">
-        <v>32</v>
-      </c>
-      <c r="H72" t="s">
-        <v>32</v>
-      </c>
-      <c r="I72" t="s">
-        <v>32</v>
-      </c>
-      <c r="J72" t="s">
-        <v>32</v>
-      </c>
-      <c r="K72" t="s">
-        <v>32</v>
-      </c>
-      <c r="L72" t="s">
-        <v>32</v>
-      </c>
-      <c r="M72" t="s">
-        <v>32</v>
-      </c>
-      <c r="N72" t="s">
-        <v>32</v>
-      </c>
-      <c r="O72" t="s">
-        <v>32</v>
-      </c>
-      <c r="P72" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>32</v>
-      </c>
-      <c r="R72" t="s">
-        <v>32</v>
-      </c>
-      <c r="S72" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>144</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C73" t="s">
-        <v>32</v>
-      </c>
-      <c r="D73" t="s">
-        <v>32</v>
-      </c>
-      <c r="E73" t="s">
-        <v>32</v>
-      </c>
-      <c r="F73" t="s">
-        <v>32</v>
-      </c>
-      <c r="G73" t="s">
-        <v>32</v>
-      </c>
-      <c r="H73" t="s">
-        <v>32</v>
-      </c>
-      <c r="I73" t="s">
-        <v>32</v>
-      </c>
-      <c r="J73" t="s">
-        <v>32</v>
-      </c>
-      <c r="K73" t="s">
-        <v>32</v>
-      </c>
-      <c r="L73" t="s">
-        <v>32</v>
-      </c>
-      <c r="M73" t="s">
-        <v>32</v>
-      </c>
-      <c r="N73" t="s">
-        <v>32</v>
-      </c>
-      <c r="O73" t="s">
-        <v>32</v>
-      </c>
-      <c r="P73" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>32</v>
-      </c>
-      <c r="R73" t="s">
-        <v>32</v>
-      </c>
-      <c r="S73" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>145</v>
-      </c>
-      <c r="B74" t="s">
-        <v>32</v>
-      </c>
-      <c r="C74" t="s">
-        <v>32</v>
-      </c>
-      <c r="D74" t="s">
-        <v>32</v>
-      </c>
-      <c r="E74" t="s">
-        <v>32</v>
-      </c>
-      <c r="F74" t="s">
-        <v>32</v>
-      </c>
-      <c r="G74" t="s">
-        <v>32</v>
-      </c>
-      <c r="H74" t="s">
-        <v>32</v>
-      </c>
-      <c r="I74" t="s">
-        <v>32</v>
-      </c>
-      <c r="J74" t="s">
-        <v>32</v>
-      </c>
-      <c r="K74" t="s">
-        <v>32</v>
-      </c>
-      <c r="L74" t="s">
-        <v>32</v>
-      </c>
-      <c r="M74" t="s">
-        <v>32</v>
-      </c>
-      <c r="N74" t="s">
-        <v>32</v>
-      </c>
-      <c r="O74" t="s">
-        <v>32</v>
-      </c>
-      <c r="P74" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>32</v>
-      </c>
-      <c r="R74" t="s">
-        <v>32</v>
-      </c>
-      <c r="S74" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -11,11 +11,11 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Room view" r:id="rId8" sheetId="6"/>
-    <sheet name="Speaker view" r:id="rId9" sheetId="7"/>
-    <sheet name="Theme view" r:id="rId10" sheetId="8"/>
-    <sheet name="Sector view" r:id="rId11" sheetId="9"/>
-    <sheet name="Content view" r:id="rId12" sheetId="10"/>
+    <sheet name="Rooms view" r:id="rId8" sheetId="6"/>
+    <sheet name="Speakers view" r:id="rId9" sheetId="7"/>
+    <sheet name="Theme tracks view" r:id="rId10" sheetId="8"/>
+    <sheet name="Sectors view" r:id="rId11" sheetId="9"/>
+    <sheet name="Contents view" r:id="rId12" sheetId="10"/>
   </sheets>
 </workbook>
 </file>
@@ -38,10 +38,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Theme conflict</t>
-  </si>
-  <si>
-    <t>Soft penalty per common theme of 2 talks that have an overlapping timeslot</t>
+    <t>Theme track conflict</t>
+  </si>
+  <si>
+    <t>Soft penalty per common theme track of 2 talks that have an overlapping timeslot</t>
   </si>
   <si>
     <t>Sector conflict</t>
@@ -188,642 +188,642 @@
     <t>Large, Recorded</t>
   </si>
   <si>
+    <t>R 2</t>
+  </si>
+  <si>
+    <t>R 3</t>
+  </si>
+  <si>
+    <t>Recorded</t>
+  </si>
+  <si>
+    <t>R 4</t>
+  </si>
+  <si>
+    <t>R 5</t>
+  </si>
+  <si>
+    <t>Lab_room, Large, Recorded</t>
+  </si>
+  <si>
+    <t>R 6</t>
+  </si>
+  <si>
+    <t>R 7</t>
+  </si>
+  <si>
+    <t>R 8</t>
+  </si>
+  <si>
+    <t>R 9</t>
+  </si>
+  <si>
+    <t>R 10</t>
+  </si>
+  <si>
+    <t>Lab_room</t>
+  </si>
+  <si>
+    <t>Required timeslot tags</t>
+  </si>
+  <si>
+    <t>Preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Required room tags</t>
+  </si>
+  <si>
+    <t>Preferred room tags</t>
+  </si>
+  <si>
+    <t>Prohibited room tags</t>
+  </si>
+  <si>
+    <t>Undesired room tags</t>
+  </si>
+  <si>
+    <t>Amy Cole</t>
+  </si>
+  <si>
+    <t>Beth Fox</t>
+  </si>
+  <si>
+    <t>Chad Green</t>
+  </si>
+  <si>
+    <t>Dan Jones</t>
+  </si>
+  <si>
+    <t>Elsa King</t>
+  </si>
+  <si>
+    <t>Flo Li</t>
+  </si>
+  <si>
+    <t>Gus Poe</t>
+  </si>
+  <si>
+    <t>Hugo Rye</t>
+  </si>
+  <si>
+    <t>Ivy Smith</t>
+  </si>
+  <si>
+    <t>Jay Watt</t>
+  </si>
+  <si>
+    <t>Amy Fox</t>
+  </si>
+  <si>
+    <t>Beth Green</t>
+  </si>
+  <si>
+    <t>Chad Jones</t>
+  </si>
+  <si>
+    <t>Dan King</t>
+  </si>
+  <si>
+    <t>Elsa Li</t>
+  </si>
+  <si>
+    <t>Flo Poe</t>
+  </si>
+  <si>
+    <t>Gus Rye</t>
+  </si>
+  <si>
+    <t>Hugo Smith</t>
+  </si>
+  <si>
+    <t>Ivy Watt</t>
+  </si>
+  <si>
+    <t>Jay Cole</t>
+  </si>
+  <si>
+    <t>Amy Green</t>
+  </si>
+  <si>
+    <t>Beth Jones</t>
+  </si>
+  <si>
+    <t>Chad King</t>
+  </si>
+  <si>
+    <t>Dan Li</t>
+  </si>
+  <si>
+    <t>Elsa Poe</t>
+  </si>
+  <si>
+    <t>Flo Rye</t>
+  </si>
+  <si>
+    <t>Gus Smith</t>
+  </si>
+  <si>
+    <t>Hugo Watt</t>
+  </si>
+  <si>
+    <t>Ivy Cole</t>
+  </si>
+  <si>
+    <t>Jay Fox</t>
+  </si>
+  <si>
+    <t>Amy Jones</t>
+  </si>
+  <si>
+    <t>Beth King</t>
+  </si>
+  <si>
+    <t>Chad Li</t>
+  </si>
+  <si>
+    <t>Dan Poe</t>
+  </si>
+  <si>
+    <t>Elsa Rye</t>
+  </si>
+  <si>
+    <t>Flo Smith</t>
+  </si>
+  <si>
+    <t>Gus Watt</t>
+  </si>
+  <si>
+    <t>Hugo Cole</t>
+  </si>
+  <si>
+    <t>Ivy Fox</t>
+  </si>
+  <si>
+    <t>Jay Green</t>
+  </si>
+  <si>
+    <t>Amy King</t>
+  </si>
+  <si>
+    <t>Beth Li</t>
+  </si>
+  <si>
+    <t>Chad Poe</t>
+  </si>
+  <si>
+    <t>Dan Rye</t>
+  </si>
+  <si>
+    <t>Elsa Smith</t>
+  </si>
+  <si>
+    <t>Flo Watt</t>
+  </si>
+  <si>
+    <t>Gus Cole</t>
+  </si>
+  <si>
+    <t>Hugo Fox</t>
+  </si>
+  <si>
+    <t>Ivy Green</t>
+  </si>
+  <si>
+    <t>Jay Jones</t>
+  </si>
+  <si>
+    <t>Amy Li</t>
+  </si>
+  <si>
+    <t>Beth Poe</t>
+  </si>
+  <si>
+    <t>Chad Rye</t>
+  </si>
+  <si>
+    <t>Dan Smith</t>
+  </si>
+  <si>
+    <t>Elsa Watt</t>
+  </si>
+  <si>
+    <t>Flo Cole</t>
+  </si>
+  <si>
+    <t>Gus Fox</t>
+  </si>
+  <si>
+    <t>Hugo Green</t>
+  </si>
+  <si>
+    <t>Ivy Jones</t>
+  </si>
+  <si>
+    <t>Jay King</t>
+  </si>
+  <si>
+    <t>Amy Poe</t>
+  </si>
+  <si>
+    <t>Beth Rye</t>
+  </si>
+  <si>
+    <t>Chad Smith</t>
+  </si>
+  <si>
+    <t>Dan Watt</t>
+  </si>
+  <si>
+    <t>Elsa Cole</t>
+  </si>
+  <si>
+    <t>Flo Fox</t>
+  </si>
+  <si>
+    <t>Gus Green</t>
+  </si>
+  <si>
+    <t>Hugo Jones</t>
+  </si>
+  <si>
+    <t>Ivy King</t>
+  </si>
+  <si>
+    <t>Jay Li</t>
+  </si>
+  <si>
+    <t>Amy Rye</t>
+  </si>
+  <si>
+    <t>Beth Smith</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Speakers</t>
+  </si>
+  <si>
+    <t>Theme track tags</t>
+  </si>
+  <si>
+    <t>Sector tags</t>
+  </si>
+  <si>
+    <t>Audience level</t>
+  </si>
+  <si>
+    <t>Content tags</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Pinned by user</t>
+  </si>
+  <si>
+    <t>Timeslot day</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>S000</t>
+  </si>
+  <si>
+    <t>Hands on real-time OpenShift</t>
+  </si>
+  <si>
+    <t>Amy Cole, Beth Fox</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>OpenShift, Kubernetes</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>S001</t>
+  </si>
+  <si>
+    <t>Advanced containerized WildFly</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>S002</t>
+  </si>
+  <si>
+    <t>Learn virtualized Spring</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>S003</t>
+  </si>
+  <si>
+    <t>Intro to serverless Drools</t>
+  </si>
+  <si>
+    <t>Elsa King, Flo Li</t>
+  </si>
+  <si>
+    <t>Modern Web</t>
+  </si>
+  <si>
+    <t>Drools</t>
+  </si>
+  <si>
+    <t>S004</t>
+  </si>
+  <si>
+    <t>Discover AI-driven OptaPlanner</t>
+  </si>
+  <si>
+    <t>Gus Poe, Hugo Rye</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>OptaPlanner</t>
+  </si>
+  <si>
+    <t>S005</t>
+  </si>
+  <si>
+    <t>Mastering machine learning jBPM</t>
+  </si>
+  <si>
+    <t>Middleware</t>
+  </si>
+  <si>
+    <t>jBPM</t>
+  </si>
+  <si>
+    <t>S006</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven Camel</t>
+  </si>
+  <si>
+    <t>Jay Watt, Amy Fox</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>S007</t>
+  </si>
+  <si>
+    <t>Building deep learning XStream</t>
+  </si>
+  <si>
+    <t>XStream</t>
+  </si>
+  <si>
+    <t>S008</t>
+  </si>
+  <si>
+    <t>Securing scalable Docker</t>
+  </si>
+  <si>
+    <t>Chad Jones, Dan King</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>S009</t>
+  </si>
+  <si>
+    <t>Debug enterprise Hibernate</t>
+  </si>
+  <si>
+    <t>Cloud, Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Hibernate</t>
+  </si>
+  <si>
+    <t>S010</t>
+  </si>
+  <si>
+    <t>Prepare for streaming GWT</t>
+  </si>
+  <si>
+    <t>Flo Poe, Gus Rye</t>
+  </si>
+  <si>
+    <t>IoT</t>
+  </si>
+  <si>
+    <t>GWT</t>
+  </si>
+  <si>
+    <t>S011</t>
+  </si>
+  <si>
+    <t>Understand mobile Errai</t>
+  </si>
+  <si>
+    <t>Hugo Smith, Ivy Watt</t>
+  </si>
+  <si>
+    <t>Mobile, Security</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>Errai</t>
+  </si>
+  <si>
+    <t>S012</t>
+  </si>
+  <si>
+    <t>Applying modern Angular</t>
+  </si>
+  <si>
+    <t>Big Data</t>
+  </si>
+  <si>
+    <t>Angular</t>
+  </si>
+  <si>
+    <t>S013</t>
+  </si>
+  <si>
+    <t>Grok distributed Weld</t>
+  </si>
+  <si>
+    <t>Weld</t>
+  </si>
+  <si>
+    <t>S014</t>
+  </si>
+  <si>
+    <t>Troubleshooting reliable RestEasy</t>
+  </si>
+  <si>
+    <t>Telecommunications</t>
+  </si>
+  <si>
+    <t>RestEasy</t>
+  </si>
+  <si>
+    <t>S015</t>
+  </si>
+  <si>
+    <t>Using secure Android</t>
+  </si>
+  <si>
+    <t>Chad King, Dan Li</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>S016</t>
+  </si>
+  <si>
+    <t>Deliver stable Tensorflow</t>
+  </si>
+  <si>
+    <t>Tensorflow</t>
+  </si>
+  <si>
+    <t>S017</t>
+  </si>
+  <si>
+    <t>Implement platform-independent VertX</t>
+  </si>
+  <si>
+    <t>Flo Rye, Gus Smith</t>
+  </si>
+  <si>
+    <t>VertX</t>
+  </si>
+  <si>
+    <t>S018</t>
+  </si>
+  <si>
+    <t>Program flexible JUnit</t>
+  </si>
+  <si>
+    <t>Hugo Watt, Ivy Cole</t>
+  </si>
+  <si>
+    <t>JUnit</t>
+  </si>
+  <si>
+    <t>S019</t>
+  </si>
+  <si>
+    <t>Hack modularized Keycloak</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Keycloak</t>
+  </si>
+  <si>
+    <t>S020</t>
+  </si>
+  <si>
+    <t>Hands on real-time WildFly</t>
+  </si>
+  <si>
+    <t>Amy Jones, Beth King</t>
+  </si>
+  <si>
+    <t>IoT, Middleware</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>S021</t>
+  </si>
+  <si>
+    <t>Advanced containerized Spring</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Cloud</t>
+  </si>
+  <si>
+    <t>S022</t>
+  </si>
+  <si>
+    <t>Learn virtualized Drools</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Security</t>
+  </si>
+  <si>
+    <t>S023</t>
+  </si>
+  <si>
+    <t>Intro to serverless OptaPlanner</t>
+  </si>
+  <si>
+    <t>S024</t>
+  </si>
+  <si>
+    <t>Discover AI-driven jBPM</t>
+  </si>
+  <si>
+    <t>Flo Smith, Gus Watt, Hugo Cole, Ivy Fox</t>
+  </si>
+  <si>
+    <t>S025</t>
+  </si>
+  <si>
+    <t>Mastering machine learning Camel</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>S026</t>
+  </si>
+  <si>
+    <t>Tuning IOT-driven XStream</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>S027</t>
+  </si>
+  <si>
+    <t>Building deep learning Docker</t>
+  </si>
+  <si>
     <t>S028</t>
   </si>
   <si>
-    <t>R 2</t>
-  </si>
-  <si>
-    <t>R 3</t>
-  </si>
-  <si>
-    <t>Recorded</t>
-  </si>
-  <si>
-    <t>R 4</t>
-  </si>
-  <si>
-    <t>R 5</t>
-  </si>
-  <si>
-    <t>Lab_room, Large, Recorded</t>
-  </si>
-  <si>
-    <t>R 6</t>
-  </si>
-  <si>
-    <t>R 7</t>
-  </si>
-  <si>
-    <t>R 8</t>
-  </si>
-  <si>
-    <t>R 9</t>
-  </si>
-  <si>
-    <t>R 10</t>
-  </si>
-  <si>
-    <t>Lab_room</t>
-  </si>
-  <si>
-    <t>Required timeslot tags</t>
-  </si>
-  <si>
-    <t>Preferred timeslot tags</t>
-  </si>
-  <si>
-    <t>Prohibited timeslot tags</t>
-  </si>
-  <si>
-    <t>Undesired timeslot tags</t>
-  </si>
-  <si>
-    <t>Required room tags</t>
-  </si>
-  <si>
-    <t>Preferred room tags</t>
-  </si>
-  <si>
-    <t>Prohibited room tags</t>
-  </si>
-  <si>
-    <t>Undesired room tags</t>
-  </si>
-  <si>
-    <t>Amy Cole</t>
-  </si>
-  <si>
-    <t>Beth Fox</t>
-  </si>
-  <si>
-    <t>Chad Green</t>
-  </si>
-  <si>
-    <t>Dan Jones</t>
-  </si>
-  <si>
-    <t>Elsa King</t>
-  </si>
-  <si>
-    <t>Flo Li</t>
-  </si>
-  <si>
-    <t>Gus Poe</t>
-  </si>
-  <si>
-    <t>Hugo Rye</t>
-  </si>
-  <si>
-    <t>Ivy Smith</t>
-  </si>
-  <si>
-    <t>Jay Watt</t>
-  </si>
-  <si>
-    <t>Amy Fox</t>
-  </si>
-  <si>
-    <t>Beth Green</t>
-  </si>
-  <si>
-    <t>Chad Jones</t>
-  </si>
-  <si>
-    <t>Dan King</t>
-  </si>
-  <si>
-    <t>Elsa Li</t>
-  </si>
-  <si>
-    <t>Flo Poe</t>
-  </si>
-  <si>
-    <t>Gus Rye</t>
-  </si>
-  <si>
-    <t>Hugo Smith</t>
-  </si>
-  <si>
-    <t>Ivy Watt</t>
-  </si>
-  <si>
-    <t>Jay Cole</t>
-  </si>
-  <si>
-    <t>Amy Green</t>
-  </si>
-  <si>
-    <t>Beth Jones</t>
-  </si>
-  <si>
-    <t>Chad King</t>
-  </si>
-  <si>
-    <t>Dan Li</t>
-  </si>
-  <si>
-    <t>Elsa Poe</t>
-  </si>
-  <si>
-    <t>Flo Rye</t>
-  </si>
-  <si>
-    <t>Gus Smith</t>
-  </si>
-  <si>
-    <t>Hugo Watt</t>
-  </si>
-  <si>
-    <t>Ivy Cole</t>
-  </si>
-  <si>
-    <t>Jay Fox</t>
-  </si>
-  <si>
-    <t>Amy Jones</t>
-  </si>
-  <si>
-    <t>Beth King</t>
-  </si>
-  <si>
-    <t>Chad Li</t>
-  </si>
-  <si>
-    <t>Dan Poe</t>
-  </si>
-  <si>
-    <t>Elsa Rye</t>
-  </si>
-  <si>
-    <t>Flo Smith</t>
-  </si>
-  <si>
-    <t>Gus Watt</t>
-  </si>
-  <si>
-    <t>Hugo Cole</t>
-  </si>
-  <si>
-    <t>Ivy Fox</t>
-  </si>
-  <si>
-    <t>Jay Green</t>
-  </si>
-  <si>
-    <t>Amy King</t>
-  </si>
-  <si>
-    <t>Beth Li</t>
-  </si>
-  <si>
-    <t>Chad Poe</t>
-  </si>
-  <si>
-    <t>Dan Rye</t>
-  </si>
-  <si>
-    <t>Elsa Smith</t>
-  </si>
-  <si>
-    <t>Flo Watt</t>
-  </si>
-  <si>
-    <t>Gus Cole</t>
-  </si>
-  <si>
-    <t>Hugo Fox</t>
-  </si>
-  <si>
-    <t>Ivy Green</t>
-  </si>
-  <si>
-    <t>Jay Jones</t>
-  </si>
-  <si>
-    <t>Amy Li</t>
-  </si>
-  <si>
-    <t>Beth Poe</t>
-  </si>
-  <si>
-    <t>Chad Rye</t>
-  </si>
-  <si>
-    <t>Dan Smith</t>
-  </si>
-  <si>
-    <t>Elsa Watt</t>
-  </si>
-  <si>
-    <t>Flo Cole</t>
-  </si>
-  <si>
-    <t>Gus Fox</t>
-  </si>
-  <si>
-    <t>Hugo Green</t>
-  </si>
-  <si>
-    <t>Ivy Jones</t>
-  </si>
-  <si>
-    <t>Jay King</t>
-  </si>
-  <si>
-    <t>Amy Poe</t>
-  </si>
-  <si>
-    <t>Beth Rye</t>
-  </si>
-  <si>
-    <t>Chad Smith</t>
-  </si>
-  <si>
-    <t>Dan Watt</t>
-  </si>
-  <si>
-    <t>Elsa Cole</t>
-  </si>
-  <si>
-    <t>Flo Fox</t>
-  </si>
-  <si>
-    <t>Gus Green</t>
-  </si>
-  <si>
-    <t>Hugo Jones</t>
-  </si>
-  <si>
-    <t>Ivy King</t>
-  </si>
-  <si>
-    <t>Jay Li</t>
-  </si>
-  <si>
-    <t>Amy Rye</t>
-  </si>
-  <si>
-    <t>Beth Smith</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Speakers</t>
-  </si>
-  <si>
-    <t>Theme tags</t>
-  </si>
-  <si>
-    <t>Sector tags</t>
-  </si>
-  <si>
-    <t>Audience level</t>
-  </si>
-  <si>
-    <t>Content tags</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>Pinned by user</t>
-  </si>
-  <si>
-    <t>Timeslot day</t>
-  </si>
-  <si>
-    <t>Room</t>
-  </si>
-  <si>
-    <t>S000</t>
-  </si>
-  <si>
-    <t>Hands on real-time OpenShift</t>
-  </si>
-  <si>
-    <t>Amy Cole, Beth Fox</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>OpenShift, Kubernetes</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>S001</t>
-  </si>
-  <si>
-    <t>Advanced containerized WildFly</t>
-  </si>
-  <si>
-    <t>WildFly</t>
-  </si>
-  <si>
-    <t>S002</t>
-  </si>
-  <si>
-    <t>Learn virtualized Spring</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>S003</t>
-  </si>
-  <si>
-    <t>Intro to serverless Drools</t>
-  </si>
-  <si>
-    <t>Elsa King, Flo Li</t>
-  </si>
-  <si>
-    <t>Modern Web</t>
-  </si>
-  <si>
-    <t>Drools</t>
-  </si>
-  <si>
-    <t>S004</t>
-  </si>
-  <si>
-    <t>Discover AI-driven OptaPlanner</t>
-  </si>
-  <si>
-    <t>Gus Poe, Hugo Rye</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
-    <t>OptaPlanner</t>
-  </si>
-  <si>
-    <t>S005</t>
-  </si>
-  <si>
-    <t>Mastering machine learning jBPM</t>
-  </si>
-  <si>
-    <t>Middleware</t>
-  </si>
-  <si>
-    <t>jBPM</t>
-  </si>
-  <si>
-    <t>S006</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven Camel</t>
-  </si>
-  <si>
-    <t>Jay Watt, Amy Fox</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>S007</t>
-  </si>
-  <si>
-    <t>Building deep learning XStream</t>
-  </si>
-  <si>
-    <t>XStream</t>
-  </si>
-  <si>
-    <t>S008</t>
-  </si>
-  <si>
-    <t>Securing scalable Docker</t>
-  </si>
-  <si>
-    <t>Chad Jones, Dan King</t>
-  </si>
-  <si>
-    <t>Docker</t>
-  </si>
-  <si>
-    <t>S009</t>
-  </si>
-  <si>
-    <t>Debug enterprise Hibernate</t>
-  </si>
-  <si>
-    <t>Cloud, Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>Hibernate</t>
-  </si>
-  <si>
-    <t>S010</t>
-  </si>
-  <si>
-    <t>Prepare for streaming GWT</t>
-  </si>
-  <si>
-    <t>Flo Poe, Gus Rye</t>
-  </si>
-  <si>
-    <t>IoT</t>
-  </si>
-  <si>
-    <t>GWT</t>
-  </si>
-  <si>
-    <t>S011</t>
-  </si>
-  <si>
-    <t>Understand mobile Errai</t>
-  </si>
-  <si>
-    <t>Hugo Smith, Ivy Watt</t>
-  </si>
-  <si>
-    <t>Mobile, Security</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
-    <t>Errai</t>
-  </si>
-  <si>
-    <t>S012</t>
-  </si>
-  <si>
-    <t>Applying modern Angular</t>
-  </si>
-  <si>
-    <t>Big Data</t>
-  </si>
-  <si>
-    <t>Angular</t>
-  </si>
-  <si>
-    <t>S013</t>
-  </si>
-  <si>
-    <t>Grok distributed Weld</t>
-  </si>
-  <si>
-    <t>Weld</t>
-  </si>
-  <si>
-    <t>S014</t>
-  </si>
-  <si>
-    <t>Troubleshooting reliable RestEasy</t>
-  </si>
-  <si>
-    <t>Telecommunications</t>
-  </si>
-  <si>
-    <t>RestEasy</t>
-  </si>
-  <si>
-    <t>S015</t>
-  </si>
-  <si>
-    <t>Using secure Android</t>
-  </si>
-  <si>
-    <t>Chad King, Dan Li</t>
-  </si>
-  <si>
-    <t>Android</t>
-  </si>
-  <si>
-    <t>S016</t>
-  </si>
-  <si>
-    <t>Deliver stable Tensorflow</t>
-  </si>
-  <si>
-    <t>Tensorflow</t>
-  </si>
-  <si>
-    <t>S017</t>
-  </si>
-  <si>
-    <t>Implement platform-independent VertX</t>
-  </si>
-  <si>
-    <t>Flo Rye, Gus Smith</t>
-  </si>
-  <si>
-    <t>VertX</t>
-  </si>
-  <si>
-    <t>S018</t>
-  </si>
-  <si>
-    <t>Program flexible JUnit</t>
-  </si>
-  <si>
-    <t>Hugo Watt, Ivy Cole</t>
-  </si>
-  <si>
-    <t>JUnit</t>
-  </si>
-  <si>
-    <t>S019</t>
-  </si>
-  <si>
-    <t>Hack modularized Keycloak</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>Keycloak</t>
-  </si>
-  <si>
-    <t>S020</t>
-  </si>
-  <si>
-    <t>Hands on real-time WildFly</t>
-  </si>
-  <si>
-    <t>Amy Jones, Beth King</t>
-  </si>
-  <si>
-    <t>IoT, Middleware</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>S021</t>
-  </si>
-  <si>
-    <t>Advanced containerized Spring</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence, Cloud</t>
-  </si>
-  <si>
-    <t>S022</t>
-  </si>
-  <si>
-    <t>Learn virtualized Drools</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence, Security</t>
-  </si>
-  <si>
-    <t>S023</t>
-  </si>
-  <si>
-    <t>Intro to serverless OptaPlanner</t>
-  </si>
-  <si>
-    <t>S024</t>
-  </si>
-  <si>
-    <t>Discover AI-driven jBPM</t>
-  </si>
-  <si>
-    <t>Flo Smith, Gus Watt, Hugo Cole, Ivy Fox</t>
-  </si>
-  <si>
-    <t>S025</t>
-  </si>
-  <si>
-    <t>Mastering machine learning Camel</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>S026</t>
-  </si>
-  <si>
-    <t>Tuning IOT-driven XStream</t>
-  </si>
-  <si>
-    <t>Culture</t>
-  </si>
-  <si>
-    <t>S027</t>
-  </si>
-  <si>
-    <t>Building deep learning Docker</t>
-  </si>
-  <si>
     <t>Securing scalable Hibernate</t>
   </si>
   <si>
@@ -1439,7 +1439,7 @@
     <t>Speaker</t>
   </si>
   <si>
-    <t>Theme tag</t>
+    <t>Theme track tag</t>
   </si>
   <si>
     <t>Sector tag</t>
@@ -1878,7 +1878,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
@@ -2414,8 +2414,8 @@
       <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>55</v>
+      <c r="D3" t="s">
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" t="s">
         <v>57</v>
-      </c>
-      <c r="B5" t="s">
-        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>34</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>34</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
         <v>60</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>34</v>
@@ -2778,7 +2778,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>34</v>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
         <v>66</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
       </c>
       <c r="C12" t="s">
         <v>34</v>
@@ -3157,28 +3157,28 @@
         <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>47</v>
@@ -3237,7 +3237,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
@@ -3255,7 +3255,7 @@
         <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H3" t="s">
         <v>34</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -3587,7 +3587,7 @@
         <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
         <v>34</v>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
@@ -3836,7 +3836,7 @@
         <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H10" t="s">
         <v>34</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -4316,7 +4316,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -4648,7 +4648,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -4731,7 +4731,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -4897,7 +4897,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -5063,7 +5063,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -5146,7 +5146,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -5312,7 +5312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -5395,7 +5395,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
@@ -5561,7 +5561,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -5579,7 +5579,7 @@
         <v>34</v>
       </c>
       <c r="G31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H31" t="s">
         <v>34</v>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
@@ -5727,7 +5727,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
@@ -5810,7 +5810,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B34" t="s">
         <v>34</v>
@@ -5893,7 +5893,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
@@ -5976,7 +5976,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
@@ -6059,7 +6059,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
@@ -6077,7 +6077,7 @@
         <v>34</v>
       </c>
       <c r="G37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H37" t="s">
         <v>34</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
         <v>34</v>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>34</v>
@@ -6308,7 +6308,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
         <v>34</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
         <v>34</v>
@@ -6474,7 +6474,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
@@ -6492,7 +6492,7 @@
         <v>34</v>
       </c>
       <c r="G42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H42" t="s">
         <v>34</v>
@@ -6557,7 +6557,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
         <v>34</v>
@@ -6640,7 +6640,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B44" t="s">
         <v>34</v>
@@ -6723,7 +6723,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B45" t="s">
         <v>34</v>
@@ -6753,7 +6753,7 @@
         <v>34</v>
       </c>
       <c r="K45" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="L45" t="s">
         <v>34</v>
@@ -6806,7 +6806,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
         <v>34</v>
@@ -6889,7 +6889,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
         <v>34</v>
@@ -6972,7 +6972,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
         <v>34</v>
@@ -7055,7 +7055,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
         <v>34</v>
@@ -7073,7 +7073,7 @@
         <v>34</v>
       </c>
       <c r="G49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H49" t="s">
         <v>34</v>
@@ -7138,7 +7138,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s">
         <v>34</v>
@@ -7221,7 +7221,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B51" t="s">
         <v>34</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B52" t="s">
         <v>34</v>
@@ -7387,7 +7387,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
         <v>34</v>
@@ -7402,7 +7402,7 @@
         <v>34</v>
       </c>
       <c r="F53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G53" t="s">
         <v>34</v>
@@ -7470,7 +7470,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B54" t="s">
         <v>34</v>
@@ -7488,7 +7488,7 @@
         <v>34</v>
       </c>
       <c r="G54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H54" t="s">
         <v>34</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B55" t="s">
         <v>34</v>
@@ -7636,7 +7636,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B56" t="s">
         <v>34</v>
@@ -7719,7 +7719,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B57" t="s">
         <v>34</v>
@@ -7802,7 +7802,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B58" t="s">
         <v>34</v>
@@ -7885,7 +7885,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B59" t="s">
         <v>34</v>
@@ -7968,7 +7968,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B60" t="s">
         <v>34</v>
@@ -8051,7 +8051,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B61" t="s">
         <v>34</v>
@@ -8134,7 +8134,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B62" t="s">
         <v>34</v>
@@ -8217,7 +8217,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s">
         <v>34</v>
@@ -8300,7 +8300,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B64" t="s">
         <v>34</v>
@@ -8383,7 +8383,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B65" t="s">
         <v>34</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B66" t="s">
         <v>34</v>
@@ -8484,7 +8484,7 @@
         <v>34</v>
       </c>
       <c r="G66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H66" t="s">
         <v>34</v>
@@ -8549,7 +8549,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B67" t="s">
         <v>34</v>
@@ -8567,7 +8567,7 @@
         <v>34</v>
       </c>
       <c r="G67" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H67" t="s">
         <v>34</v>
@@ -8632,7 +8632,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B68" t="s">
         <v>34</v>
@@ -8715,7 +8715,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B69" t="s">
         <v>34</v>
@@ -8798,7 +8798,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B70" t="s">
         <v>34</v>
@@ -8881,7 +8881,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B71" t="s">
         <v>34</v>
@@ -8964,7 +8964,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B72" t="s">
         <v>34</v>
@@ -9047,7 +9047,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B73" t="s">
         <v>34</v>
@@ -9130,7 +9130,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B74" t="s">
         <v>34</v>
@@ -9253,61 +9253,61 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>26</v>
@@ -9316,24 +9316,24 @@
         <v>27</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" t="s">
         <v>159</v>
-      </c>
-      <c r="B2" t="s">
-        <v>160</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" t="s">
         <v>161</v>
-      </c>
-      <c r="E2" t="s">
-        <v>162</v>
       </c>
       <c r="F2" t="s">
         <v>34</v>
@@ -9342,11 +9342,11 @@
         <v>1.0</v>
       </c>
       <c r="H2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I2" t="s">
         <v>163</v>
       </c>
-      <c r="I2" t="s">
-        <v>164</v>
-      </c>
       <c r="J2" t="s">
         <v>34</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>34</v>
       </c>
       <c r="N2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O2" t="s">
         <v>34</v>
@@ -9389,19 +9389,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" t="s">
         <v>165</v>
-      </c>
-      <c r="B3" t="s">
-        <v>166</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F3" t="s">
         <v>34</v>
@@ -9410,10 +9410,10 @@
         <v>3.0</v>
       </c>
       <c r="H3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J3" t="s">
         <v>34</v>
@@ -9428,7 +9428,7 @@
         <v>34</v>
       </c>
       <c r="N3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O3" t="s">
         <v>34</v>
@@ -9457,31 +9457,31 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
         <v>168</v>
-      </c>
-      <c r="B4" t="s">
-        <v>169</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" t="s">
         <v>170</v>
-      </c>
-      <c r="F4" t="s">
-        <v>171</v>
       </c>
       <c r="G4" t="n">
         <v>1.0</v>
       </c>
       <c r="H4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J4" t="s">
         <v>34</v>
@@ -9496,7 +9496,7 @@
         <v>34</v>
       </c>
       <c r="N4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O4" t="s">
         <v>34</v>
@@ -9525,19 +9525,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" t="s">
         <v>173</v>
-      </c>
-      <c r="B5" t="s">
-        <v>174</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
       </c>
       <c r="D5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E5" t="s">
         <v>175</v>
-      </c>
-      <c r="E5" t="s">
-        <v>176</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
@@ -9546,10 +9546,10 @@
         <v>1.0</v>
       </c>
       <c r="H5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J5" t="s">
         <v>34</v>
@@ -9564,7 +9564,7 @@
         <v>34</v>
       </c>
       <c r="N5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O5" t="s">
         <v>34</v>
@@ -9593,19 +9593,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s">
         <v>178</v>
-      </c>
-      <c r="B6" t="s">
-        <v>179</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
       </c>
       <c r="D6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" t="s">
         <v>180</v>
-      </c>
-      <c r="E6" t="s">
-        <v>181</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
@@ -9614,10 +9614,10 @@
         <v>2.0</v>
       </c>
       <c r="H6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J6" t="s">
         <v>34</v>
@@ -9632,7 +9632,7 @@
         <v>34</v>
       </c>
       <c r="N6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O6" t="s">
         <v>34</v>
@@ -9661,19 +9661,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" t="s">
         <v>183</v>
-      </c>
-      <c r="B7" t="s">
-        <v>184</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F7" t="s">
         <v>34</v>
@@ -9682,10 +9682,10 @@
         <v>3.0</v>
       </c>
       <c r="H7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J7" t="s">
         <v>34</v>
@@ -9700,7 +9700,7 @@
         <v>34</v>
       </c>
       <c r="N7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O7" t="s">
         <v>34</v>
@@ -9729,19 +9729,19 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" t="s">
         <v>187</v>
-      </c>
-      <c r="B8" t="s">
-        <v>188</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -9750,10 +9750,10 @@
         <v>1.0</v>
       </c>
       <c r="H8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J8" t="s">
         <v>34</v>
@@ -9768,7 +9768,7 @@
         <v>34</v>
       </c>
       <c r="N8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O8" t="s">
         <v>34</v>
@@ -9797,19 +9797,19 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" t="s">
         <v>191</v>
-      </c>
-      <c r="B9" t="s">
-        <v>192</v>
       </c>
       <c r="C9" t="s">
         <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -9818,10 +9818,10 @@
         <v>3.0</v>
       </c>
       <c r="H9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
@@ -9836,7 +9836,7 @@
         <v>34</v>
       </c>
       <c r="N9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O9" t="s">
         <v>34</v>
@@ -9865,19 +9865,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" t="s">
         <v>194</v>
-      </c>
-      <c r="B10" t="s">
-        <v>195</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
@@ -9886,10 +9886,10 @@
         <v>1.0</v>
       </c>
       <c r="H10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J10" t="s">
         <v>34</v>
@@ -9904,7 +9904,7 @@
         <v>34</v>
       </c>
       <c r="N10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O10" t="s">
         <v>34</v>
@@ -9933,19 +9933,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" t="s">
         <v>198</v>
-      </c>
-      <c r="B11" t="s">
-        <v>199</v>
       </c>
       <c r="C11" t="s">
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F11" t="s">
         <v>34</v>
@@ -9954,10 +9954,10 @@
         <v>3.0</v>
       </c>
       <c r="H11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J11" t="s">
         <v>34</v>
@@ -9972,7 +9972,7 @@
         <v>34</v>
       </c>
       <c r="N11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O11" t="s">
         <v>34</v>
@@ -10001,19 +10001,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" t="s">
         <v>202</v>
-      </c>
-      <c r="B12" t="s">
-        <v>203</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
       </c>
       <c r="D12" t="s">
+        <v>203</v>
+      </c>
+      <c r="E12" t="s">
         <v>204</v>
-      </c>
-      <c r="E12" t="s">
-        <v>205</v>
       </c>
       <c r="F12" t="s">
         <v>34</v>
@@ -10022,10 +10022,10 @@
         <v>1.0</v>
       </c>
       <c r="H12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J12" t="s">
         <v>34</v>
@@ -10040,7 +10040,7 @@
         <v>34</v>
       </c>
       <c r="N12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O12" t="s">
         <v>34</v>
@@ -10069,31 +10069,31 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" t="s">
         <v>207</v>
-      </c>
-      <c r="B13" t="s">
-        <v>208</v>
       </c>
       <c r="C13" t="s">
         <v>33</v>
       </c>
       <c r="D13" t="s">
+        <v>208</v>
+      </c>
+      <c r="E13" t="s">
         <v>209</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>210</v>
-      </c>
-      <c r="F13" t="s">
-        <v>211</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
       </c>
       <c r="H13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J13" t="s">
         <v>34</v>
@@ -10108,7 +10108,7 @@
         <v>34</v>
       </c>
       <c r="N13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O13" t="s">
         <v>34</v>
@@ -10137,19 +10137,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" t="s">
         <v>213</v>
-      </c>
-      <c r="B14" t="s">
-        <v>214</v>
       </c>
       <c r="C14" t="s">
         <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F14" t="s">
         <v>34</v>
@@ -10158,10 +10158,10 @@
         <v>3.0</v>
       </c>
       <c r="H14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J14" t="s">
         <v>34</v>
@@ -10205,31 +10205,31 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" t="s">
         <v>217</v>
-      </c>
-      <c r="B15" t="s">
-        <v>218</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G15" t="n">
         <v>1.0</v>
       </c>
       <c r="H15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J15" t="s">
         <v>34</v>
@@ -10273,31 +10273,31 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>219</v>
+      </c>
+      <c r="B16" t="s">
         <v>220</v>
-      </c>
-      <c r="B16" t="s">
-        <v>221</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G16" t="n">
         <v>3.0</v>
       </c>
       <c r="H16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J16" t="s">
         <v>34</v>
@@ -10341,19 +10341,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" t="s">
         <v>224</v>
-      </c>
-      <c r="B17" t="s">
-        <v>225</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -10362,10 +10362,10 @@
         <v>2.0</v>
       </c>
       <c r="H17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J17" t="s">
         <v>34</v>
@@ -10409,19 +10409,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" t="s">
         <v>228</v>
-      </c>
-      <c r="B18" t="s">
-        <v>229</v>
       </c>
       <c r="C18" t="s">
         <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F18" t="s">
         <v>34</v>
@@ -10430,10 +10430,10 @@
         <v>2.0</v>
       </c>
       <c r="H18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J18" t="s">
         <v>34</v>
@@ -10477,19 +10477,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" t="s">
         <v>231</v>
-      </c>
-      <c r="B19" t="s">
-        <v>232</v>
       </c>
       <c r="C19" t="s">
         <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F19" t="s">
         <v>34</v>
@@ -10498,10 +10498,10 @@
         <v>2.0</v>
       </c>
       <c r="H19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J19" t="s">
         <v>34</v>
@@ -10545,31 +10545,31 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B20" t="s">
         <v>235</v>
-      </c>
-      <c r="B20" t="s">
-        <v>236</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G20" t="n">
         <v>2.0</v>
       </c>
       <c r="H20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J20" t="s">
         <v>34</v>
@@ -10613,19 +10613,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>238</v>
+      </c>
+      <c r="B21" t="s">
         <v>239</v>
-      </c>
-      <c r="B21" t="s">
-        <v>240</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -10634,10 +10634,10 @@
         <v>1.0</v>
       </c>
       <c r="H21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J21" t="s">
         <v>34</v>
@@ -10681,31 +10681,31 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>242</v>
+      </c>
+      <c r="B22" t="s">
         <v>243</v>
-      </c>
-      <c r="B22" t="s">
-        <v>244</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
       </c>
       <c r="D22" t="s">
+        <v>244</v>
+      </c>
+      <c r="E22" t="s">
         <v>245</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>246</v>
-      </c>
-      <c r="F22" t="s">
-        <v>247</v>
       </c>
       <c r="G22" t="n">
         <v>1.0</v>
       </c>
       <c r="H22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J22" t="s">
         <v>34</v>
@@ -10749,19 +10749,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>247</v>
+      </c>
+      <c r="B23" t="s">
         <v>248</v>
-      </c>
-      <c r="B23" t="s">
-        <v>249</v>
       </c>
       <c r="C23" t="s">
         <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
@@ -10770,10 +10770,10 @@
         <v>3.0</v>
       </c>
       <c r="H23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J23" t="s">
         <v>34</v>
@@ -10817,31 +10817,31 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>250</v>
+      </c>
+      <c r="B24" t="s">
         <v>251</v>
-      </c>
-      <c r="B24" t="s">
-        <v>252</v>
       </c>
       <c r="C24" t="s">
         <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G24" t="n">
         <v>1.0</v>
       </c>
       <c r="H24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J24" t="s">
         <v>34</v>
@@ -10885,19 +10885,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>253</v>
+      </c>
+      <c r="B25" t="s">
         <v>254</v>
-      </c>
-      <c r="B25" t="s">
-        <v>255</v>
       </c>
       <c r="C25" t="s">
         <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F25" t="s">
         <v>34</v>
@@ -10906,10 +10906,10 @@
         <v>2.0</v>
       </c>
       <c r="H25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J25" t="s">
         <v>34</v>
@@ -10953,19 +10953,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>255</v>
+      </c>
+      <c r="B26" t="s">
         <v>256</v>
-      </c>
-      <c r="B26" t="s">
-        <v>257</v>
       </c>
       <c r="C26" t="s">
         <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F26" t="s">
         <v>34</v>
@@ -10974,10 +10974,10 @@
         <v>3.0</v>
       </c>
       <c r="H26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J26" t="s">
         <v>34</v>
@@ -11021,31 +11021,31 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>258</v>
+      </c>
+      <c r="B27" t="s">
         <v>259</v>
-      </c>
-      <c r="B27" t="s">
-        <v>260</v>
       </c>
       <c r="C27" t="s">
         <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
       </c>
       <c r="H27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J27" t="s">
         <v>34</v>
@@ -11089,19 +11089,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>261</v>
+      </c>
+      <c r="B28" t="s">
         <v>262</v>
-      </c>
-      <c r="B28" t="s">
-        <v>263</v>
       </c>
       <c r="C28" t="s">
         <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F28" t="s">
         <v>34</v>
@@ -11110,10 +11110,10 @@
         <v>1.0</v>
       </c>
       <c r="H28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J28" t="s">
         <v>34</v>
@@ -11157,19 +11157,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>264</v>
+      </c>
+      <c r="B29" t="s">
         <v>265</v>
-      </c>
-      <c r="B29" t="s">
-        <v>266</v>
       </c>
       <c r="C29" t="s">
         <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -11178,10 +11178,10 @@
         <v>1.0</v>
       </c>
       <c r="H29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J29" t="s">
         <v>34</v>
@@ -11225,7 +11225,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s">
         <v>267</v>
@@ -11234,7 +11234,7 @@
         <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30" t="s">
         <v>268</v>
@@ -11246,10 +11246,10 @@
         <v>1.0</v>
       </c>
       <c r="H30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J30" t="s">
         <v>34</v>
@@ -11302,10 +11302,10 @@
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
@@ -11314,10 +11314,10 @@
         <v>1.0</v>
       </c>
       <c r="H31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J31" t="s">
         <v>34</v>
@@ -11373,7 +11373,7 @@
         <v>273</v>
       </c>
       <c r="E32" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F32" t="s">
         <v>34</v>
@@ -11382,10 +11382,10 @@
         <v>2.0</v>
       </c>
       <c r="H32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J32" t="s">
         <v>34</v>
@@ -11438,10 +11438,10 @@
         <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
@@ -11450,10 +11450,10 @@
         <v>2.0</v>
       </c>
       <c r="H33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I33" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J33" t="s">
         <v>34</v>
@@ -11506,7 +11506,7 @@
         <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E34" t="s">
         <v>278</v>
@@ -11518,10 +11518,10 @@
         <v>2.0</v>
       </c>
       <c r="H34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I34" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J34" t="s">
         <v>34</v>
@@ -11574,10 +11574,10 @@
         <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
@@ -11586,10 +11586,10 @@
         <v>1.0</v>
       </c>
       <c r="H35" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J35" t="s">
         <v>34</v>
@@ -11642,7 +11642,7 @@
         <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E36" t="s">
         <v>283</v>
@@ -11654,10 +11654,10 @@
         <v>2.0</v>
       </c>
       <c r="H36" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J36" t="s">
         <v>34</v>
@@ -11710,10 +11710,10 @@
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F37" t="s">
         <v>34</v>
@@ -11722,10 +11722,10 @@
         <v>1.0</v>
       </c>
       <c r="H37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J37" t="s">
         <v>34</v>
@@ -11778,10 +11778,10 @@
         <v>36</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F38" t="s">
         <v>34</v>
@@ -11790,10 +11790,10 @@
         <v>2.0</v>
       </c>
       <c r="H38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J38" t="s">
         <v>34</v>
@@ -11846,7 +11846,7 @@
         <v>36</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E39" t="s">
         <v>290</v>
@@ -11858,10 +11858,10 @@
         <v>3.0</v>
       </c>
       <c r="H39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I39" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J39" t="s">
         <v>34</v>
@@ -11917,7 +11917,7 @@
         <v>293</v>
       </c>
       <c r="E40" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F40" t="s">
         <v>34</v>
@@ -11926,10 +11926,10 @@
         <v>1.0</v>
       </c>
       <c r="H40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J40" t="s">
         <v>34</v>
@@ -11982,10 +11982,10 @@
         <v>36</v>
       </c>
       <c r="D41" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E41" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F41" t="s">
         <v>34</v>
@@ -11997,7 +11997,7 @@
         <v>296</v>
       </c>
       <c r="I41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J41" t="s">
         <v>34</v>
@@ -12053,7 +12053,7 @@
         <v>299</v>
       </c>
       <c r="E42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F42" t="s">
         <v>34</v>
@@ -12062,10 +12062,10 @@
         <v>1.0</v>
       </c>
       <c r="H42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I42" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J42" t="s">
         <v>34</v>
@@ -12118,10 +12118,10 @@
         <v>36</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E43" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
@@ -12130,10 +12130,10 @@
         <v>1.0</v>
       </c>
       <c r="H43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I43" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J43" t="s">
         <v>34</v>
@@ -12186,22 +12186,22 @@
         <v>36</v>
       </c>
       <c r="D44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G44" t="n">
         <v>3.0</v>
       </c>
       <c r="H44" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I44" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J44" t="s">
         <v>34</v>
@@ -12266,10 +12266,10 @@
         <v>3.0</v>
       </c>
       <c r="H45" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J45" t="s">
         <v>34</v>
@@ -12322,10 +12322,10 @@
         <v>36</v>
       </c>
       <c r="D46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E46" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
@@ -12334,10 +12334,10 @@
         <v>1.0</v>
       </c>
       <c r="H46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I46" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J46" t="s">
         <v>34</v>
@@ -12393,7 +12393,7 @@
         <v>312</v>
       </c>
       <c r="E47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F47" t="s">
         <v>313</v>
@@ -12402,10 +12402,10 @@
         <v>3.0</v>
       </c>
       <c r="H47" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I47" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J47" t="s">
         <v>34</v>
@@ -12458,10 +12458,10 @@
         <v>36</v>
       </c>
       <c r="D48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E48" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F48" t="s">
         <v>34</v>
@@ -12473,7 +12473,7 @@
         <v>316</v>
       </c>
       <c r="I48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J48" t="s">
         <v>34</v>
@@ -12529,7 +12529,7 @@
         <v>319</v>
       </c>
       <c r="E49" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
@@ -12538,10 +12538,10 @@
         <v>3.0</v>
       </c>
       <c r="H49" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I49" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J49" t="s">
         <v>34</v>
@@ -12597,7 +12597,7 @@
         <v>322</v>
       </c>
       <c r="E50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F50" t="s">
         <v>34</v>
@@ -12606,10 +12606,10 @@
         <v>3.0</v>
       </c>
       <c r="H50" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J50" t="s">
         <v>34</v>
@@ -12665,7 +12665,7 @@
         <v>325</v>
       </c>
       <c r="E51" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
@@ -12674,10 +12674,10 @@
         <v>1.0</v>
       </c>
       <c r="H51" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I51" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J51" t="s">
         <v>34</v>
@@ -12730,10 +12730,10 @@
         <v>36</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E52" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F52" t="s">
         <v>34</v>
@@ -12742,10 +12742,10 @@
         <v>3.0</v>
       </c>
       <c r="H52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I52" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J52" t="s">
         <v>34</v>
@@ -12798,10 +12798,10 @@
         <v>36</v>
       </c>
       <c r="D53" t="s">
+        <v>174</v>
+      </c>
+      <c r="E53" t="s">
         <v>175</v>
-      </c>
-      <c r="E53" t="s">
-        <v>176</v>
       </c>
       <c r="F53" t="s">
         <v>34</v>
@@ -12810,10 +12810,10 @@
         <v>3.0</v>
       </c>
       <c r="H53" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J53" t="s">
         <v>34</v>
@@ -12866,22 +12866,22 @@
         <v>36</v>
       </c>
       <c r="D54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E54" t="s">
         <v>332</v>
       </c>
       <c r="F54" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G54" t="n">
         <v>1.0</v>
       </c>
       <c r="H54" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J54" t="s">
         <v>34</v>
@@ -12937,7 +12937,7 @@
         <v>335</v>
       </c>
       <c r="E55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F55" t="s">
         <v>34</v>
@@ -12946,10 +12946,10 @@
         <v>2.0</v>
       </c>
       <c r="H55" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I55" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J55" t="s">
         <v>34</v>
@@ -13002,10 +13002,10 @@
         <v>36</v>
       </c>
       <c r="D56" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E56" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F56" t="s">
         <v>34</v>
@@ -13014,10 +13014,10 @@
         <v>1.0</v>
       </c>
       <c r="H56" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I56" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J56" t="s">
         <v>34</v>
@@ -13073,7 +13073,7 @@
         <v>340</v>
       </c>
       <c r="E57" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F57" t="s">
         <v>34</v>
@@ -13082,10 +13082,10 @@
         <v>1.0</v>
       </c>
       <c r="H57" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I57" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J57" t="s">
         <v>34</v>
@@ -13138,10 +13138,10 @@
         <v>36</v>
       </c>
       <c r="D58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E58" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F58" t="s">
         <v>34</v>
@@ -13150,10 +13150,10 @@
         <v>2.0</v>
       </c>
       <c r="H58" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I58" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J58" t="s">
         <v>34</v>
@@ -13206,22 +13206,22 @@
         <v>36</v>
       </c>
       <c r="D59" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F59" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G59" t="n">
         <v>1.0</v>
       </c>
       <c r="H59" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I59" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J59" t="s">
         <v>34</v>
@@ -13274,7 +13274,7 @@
         <v>36</v>
       </c>
       <c r="D60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E60" t="s">
         <v>347</v>
@@ -13289,7 +13289,7 @@
         <v>296</v>
       </c>
       <c r="I60" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J60" t="s">
         <v>34</v>
@@ -13342,7 +13342,7 @@
         <v>36</v>
       </c>
       <c r="D61" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E61" t="s">
         <v>350</v>
@@ -13354,10 +13354,10 @@
         <v>2.0</v>
       </c>
       <c r="H61" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I61" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J61" t="s">
         <v>34</v>
@@ -13410,10 +13410,10 @@
         <v>36</v>
       </c>
       <c r="D62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E62" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F62" t="s">
         <v>34</v>
@@ -13422,10 +13422,10 @@
         <v>2.0</v>
       </c>
       <c r="H62" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I62" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J62" t="s">
         <v>34</v>
@@ -13490,10 +13490,10 @@
         <v>3.0</v>
       </c>
       <c r="H63" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I63" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J63" t="s">
         <v>34</v>
@@ -13546,22 +13546,22 @@
         <v>36</v>
       </c>
       <c r="D64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E64" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F64" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G64" t="n">
         <v>3.0</v>
       </c>
       <c r="H64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I64" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J64" t="s">
         <v>34</v>
@@ -13614,22 +13614,22 @@
         <v>36</v>
       </c>
       <c r="D65" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F65" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G65" t="n">
         <v>1.0</v>
       </c>
       <c r="H65" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I65" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J65" t="s">
         <v>34</v>
@@ -13682,10 +13682,10 @@
         <v>36</v>
       </c>
       <c r="D66" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E66" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F66" t="s">
         <v>34</v>
@@ -13694,10 +13694,10 @@
         <v>1.0</v>
       </c>
       <c r="H66" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I66" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J66" t="s">
         <v>34</v>
@@ -13765,7 +13765,7 @@
         <v>316</v>
       </c>
       <c r="I67" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J67" t="s">
         <v>34</v>
@@ -13818,10 +13818,10 @@
         <v>36</v>
       </c>
       <c r="D68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F68" t="s">
         <v>34</v>
@@ -13830,10 +13830,10 @@
         <v>1.0</v>
       </c>
       <c r="H68" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J68" t="s">
         <v>34</v>
@@ -13886,10 +13886,10 @@
         <v>36</v>
       </c>
       <c r="D69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E69" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F69" t="s">
         <v>34</v>
@@ -13898,10 +13898,10 @@
         <v>2.0</v>
       </c>
       <c r="H69" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I69" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J69" t="s">
         <v>34</v>
@@ -13957,7 +13957,7 @@
         <v>372</v>
       </c>
       <c r="E70" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F70" t="s">
         <v>34</v>
@@ -13966,10 +13966,10 @@
         <v>2.0</v>
       </c>
       <c r="H70" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J70" t="s">
         <v>34</v>
@@ -14022,10 +14022,10 @@
         <v>36</v>
       </c>
       <c r="D71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E71" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F71" t="s">
         <v>313</v>
@@ -14034,10 +14034,10 @@
         <v>2.0</v>
       </c>
       <c r="H71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I71" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J71" t="s">
         <v>34</v>
@@ -14090,7 +14090,7 @@
         <v>36</v>
       </c>
       <c r="D72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E72" t="s">
         <v>377</v>
@@ -14102,10 +14102,10 @@
         <v>1.0</v>
       </c>
       <c r="H72" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I72" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J72" t="s">
         <v>34</v>
@@ -14161,7 +14161,7 @@
         <v>380</v>
       </c>
       <c r="E73" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F73" t="s">
         <v>34</v>
@@ -14170,10 +14170,10 @@
         <v>1.0</v>
       </c>
       <c r="H73" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I73" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J73" t="s">
         <v>34</v>
@@ -14226,10 +14226,10 @@
         <v>36</v>
       </c>
       <c r="D74" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F74" t="s">
         <v>34</v>
@@ -14238,10 +14238,10 @@
         <v>3.0</v>
       </c>
       <c r="H74" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I74" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J74" t="s">
         <v>34</v>
@@ -14297,7 +14297,7 @@
         <v>385</v>
       </c>
       <c r="E75" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F75" t="s">
         <v>34</v>
@@ -14306,10 +14306,10 @@
         <v>1.0</v>
       </c>
       <c r="H75" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I75" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J75" t="s">
         <v>34</v>
@@ -14365,7 +14365,7 @@
         <v>388</v>
       </c>
       <c r="E76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
         <v>34</v>
@@ -14374,10 +14374,10 @@
         <v>2.0</v>
       </c>
       <c r="H76" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I76" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J76" t="s">
         <v>34</v>
@@ -14430,10 +14430,10 @@
         <v>36</v>
       </c>
       <c r="D77" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E77" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F77" t="s">
         <v>34</v>
@@ -14442,10 +14442,10 @@
         <v>3.0</v>
       </c>
       <c r="H77" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I77" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J77" t="s">
         <v>34</v>
@@ -14498,10 +14498,10 @@
         <v>36</v>
       </c>
       <c r="D78" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E78" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F78" t="s">
         <v>34</v>
@@ -14510,10 +14510,10 @@
         <v>1.0</v>
       </c>
       <c r="H78" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I78" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J78" t="s">
         <v>34</v>
@@ -14569,7 +14569,7 @@
         <v>395</v>
       </c>
       <c r="E79" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F79" t="s">
         <v>34</v>
@@ -14581,7 +14581,7 @@
         <v>296</v>
       </c>
       <c r="I79" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J79" t="s">
         <v>34</v>
@@ -14637,7 +14637,7 @@
         <v>398</v>
       </c>
       <c r="E80" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F80" t="s">
         <v>313</v>
@@ -14646,10 +14646,10 @@
         <v>2.0</v>
       </c>
       <c r="H80" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I80" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J80" t="s">
         <v>34</v>
@@ -14702,10 +14702,10 @@
         <v>36</v>
       </c>
       <c r="D81" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E81" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F81" t="s">
         <v>34</v>
@@ -14714,10 +14714,10 @@
         <v>3.0</v>
       </c>
       <c r="H81" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I81" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J81" t="s">
         <v>34</v>
@@ -14770,10 +14770,10 @@
         <v>36</v>
       </c>
       <c r="D82" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E82" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F82" t="s">
         <v>34</v>
@@ -14782,10 +14782,10 @@
         <v>1.0</v>
       </c>
       <c r="H82" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I82" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J82" t="s">
         <v>34</v>
@@ -14838,7 +14838,7 @@
         <v>36</v>
       </c>
       <c r="D83" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E83" t="s">
         <v>405</v>
@@ -14850,10 +14850,10 @@
         <v>1.0</v>
       </c>
       <c r="H83" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I83" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J83" t="s">
         <v>34</v>
@@ -14909,7 +14909,7 @@
         <v>408</v>
       </c>
       <c r="E84" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F84" t="s">
         <v>34</v>
@@ -14918,10 +14918,10 @@
         <v>3.0</v>
       </c>
       <c r="H84" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I84" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J84" t="s">
         <v>34</v>
@@ -14974,10 +14974,10 @@
         <v>36</v>
       </c>
       <c r="D85" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E85" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F85" t="s">
         <v>34</v>
@@ -14986,10 +14986,10 @@
         <v>2.0</v>
       </c>
       <c r="H85" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J85" t="s">
         <v>34</v>
@@ -15042,7 +15042,7 @@
         <v>36</v>
       </c>
       <c r="D86" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E86" t="s">
         <v>413</v>
@@ -15054,10 +15054,10 @@
         <v>2.0</v>
       </c>
       <c r="H86" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I86" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J86" t="s">
         <v>34</v>
@@ -15113,7 +15113,7 @@
         <v>416</v>
       </c>
       <c r="E87" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F87" t="s">
         <v>34</v>
@@ -15122,10 +15122,10 @@
         <v>1.0</v>
       </c>
       <c r="H87" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I87" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J87" t="s">
         <v>34</v>
@@ -15181,19 +15181,19 @@
         <v>419</v>
       </c>
       <c r="E88" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F88" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G88" t="n">
         <v>3.0</v>
       </c>
       <c r="H88" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I88" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J88" t="s">
         <v>34</v>
@@ -15249,19 +15249,19 @@
         <v>299</v>
       </c>
       <c r="E89" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F89" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G89" t="n">
         <v>3.0</v>
       </c>
       <c r="H89" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I89" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J89" t="s">
         <v>34</v>
@@ -15317,19 +15317,19 @@
         <v>424</v>
       </c>
       <c r="E90" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F90" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G90" t="n">
         <v>3.0</v>
       </c>
       <c r="H90" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I90" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J90" t="s">
         <v>34</v>
@@ -15382,22 +15382,22 @@
         <v>36</v>
       </c>
       <c r="D91" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E91" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F91" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G91" t="n">
         <v>2.0</v>
       </c>
       <c r="H91" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I91" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J91" t="s">
         <v>34</v>
@@ -15450,10 +15450,10 @@
         <v>36</v>
       </c>
       <c r="D92" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E92" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F92" t="s">
         <v>34</v>
@@ -15462,10 +15462,10 @@
         <v>1.0</v>
       </c>
       <c r="H92" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I92" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J92" t="s">
         <v>34</v>
@@ -15518,10 +15518,10 @@
         <v>36</v>
       </c>
       <c r="D93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F93" t="s">
         <v>34</v>
@@ -15530,10 +15530,10 @@
         <v>3.0</v>
       </c>
       <c r="H93" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I93" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J93" t="s">
         <v>34</v>
@@ -15586,10 +15586,10 @@
         <v>36</v>
       </c>
       <c r="D94" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E94" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F94" t="s">
         <v>34</v>
@@ -15598,10 +15598,10 @@
         <v>1.0</v>
       </c>
       <c r="H94" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I94" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J94" t="s">
         <v>34</v>
@@ -15660,16 +15660,16 @@
         <v>436</v>
       </c>
       <c r="F95" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G95" t="n">
         <v>1.0</v>
       </c>
       <c r="H95" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I95" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J95" t="s">
         <v>34</v>
@@ -15725,7 +15725,7 @@
         <v>439</v>
       </c>
       <c r="E96" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F96" t="s">
         <v>34</v>
@@ -15734,10 +15734,10 @@
         <v>2.0</v>
       </c>
       <c r="H96" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I96" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J96" t="s">
         <v>34</v>
@@ -15793,7 +15793,7 @@
         <v>442</v>
       </c>
       <c r="E97" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F97" t="s">
         <v>34</v>
@@ -15802,10 +15802,10 @@
         <v>3.0</v>
       </c>
       <c r="H97" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I97" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J97" t="s">
         <v>34</v>
@@ -15858,13 +15858,13 @@
         <v>36</v>
       </c>
       <c r="D98" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E98" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F98" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G98" t="n">
         <v>2.0</v>
@@ -15873,7 +15873,7 @@
         <v>296</v>
       </c>
       <c r="I98" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J98" t="s">
         <v>34</v>
@@ -15926,10 +15926,10 @@
         <v>36</v>
       </c>
       <c r="D99" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E99" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F99" t="s">
         <v>34</v>
@@ -15938,10 +15938,10 @@
         <v>3.0</v>
       </c>
       <c r="H99" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I99" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J99" t="s">
         <v>34</v>
@@ -15997,7 +15997,7 @@
         <v>449</v>
       </c>
       <c r="E100" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F100" t="s">
         <v>34</v>
@@ -16006,10 +16006,10 @@
         <v>3.0</v>
       </c>
       <c r="H100" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I100" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J100" t="s">
         <v>34</v>
@@ -16062,7 +16062,7 @@
         <v>36</v>
       </c>
       <c r="D101" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E101" t="s">
         <v>452</v>
@@ -16074,10 +16074,10 @@
         <v>2.0</v>
       </c>
       <c r="H101" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I101" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J101" t="s">
         <v>34</v>
@@ -16130,10 +16130,10 @@
         <v>36</v>
       </c>
       <c r="D102" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F102" t="s">
         <v>34</v>
@@ -16142,10 +16142,10 @@
         <v>1.0</v>
       </c>
       <c r="H102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I102" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J102" t="s">
         <v>34</v>
@@ -16198,22 +16198,22 @@
         <v>36</v>
       </c>
       <c r="D103" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E103" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F103" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G103" t="n">
         <v>3.0</v>
       </c>
       <c r="H103" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I103" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J103" t="s">
         <v>34</v>
@@ -16266,10 +16266,10 @@
         <v>36</v>
       </c>
       <c r="D104" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E104" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F104" t="s">
         <v>34</v>
@@ -16278,10 +16278,10 @@
         <v>1.0</v>
       </c>
       <c r="H104" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I104" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J104" t="s">
         <v>34</v>
@@ -16334,22 +16334,22 @@
         <v>36</v>
       </c>
       <c r="D105" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E105" t="s">
         <v>461</v>
       </c>
       <c r="F105" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G105" t="n">
         <v>1.0</v>
       </c>
       <c r="H105" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I105" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J105" t="s">
         <v>34</v>
@@ -16405,19 +16405,19 @@
         <v>340</v>
       </c>
       <c r="E106" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F106" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G106" t="n">
         <v>1.0</v>
       </c>
       <c r="H106" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I106" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J106" t="s">
         <v>34</v>
@@ -16470,10 +16470,10 @@
         <v>36</v>
       </c>
       <c r="D107" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E107" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F107" t="s">
         <v>34</v>
@@ -16482,10 +16482,10 @@
         <v>2.0</v>
       </c>
       <c r="H107" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I107" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J107" t="s">
         <v>34</v>
@@ -16541,7 +16541,7 @@
         <v>468</v>
       </c>
       <c r="E108" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F108" t="s">
         <v>34</v>
@@ -16550,10 +16550,10 @@
         <v>1.0</v>
       </c>
       <c r="H108" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I108" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J108" t="s">
         <v>34</v>
@@ -16606,22 +16606,22 @@
         <v>36</v>
       </c>
       <c r="D109" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E109" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F109" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G109" t="n">
         <v>1.0</v>
       </c>
       <c r="H109" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I109" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J109" t="s">
         <v>34</v>
@@ -16756,7 +16756,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>47</v>
@@ -16820,8 +16820,8 @@
       <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
-        <v>55</v>
+      <c r="C3" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="D3" t="s">
         <v>34</v>
@@ -16874,7 +16874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>34</v>
@@ -16933,7 +16933,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>34</v>
@@ -16992,7 +16992,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>34</v>
@@ -17051,7 +17051,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -17110,7 +17110,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>34</v>
@@ -17169,7 +17169,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>34</v>
@@ -17228,7 +17228,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>34</v>
@@ -17287,7 +17287,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>34</v>
@@ -17346,7 +17346,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -17560,7 +17560,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
@@ -17619,7 +17619,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -17678,7 +17678,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
@@ -17737,7 +17737,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -17796,7 +17796,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -17855,7 +17855,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -17914,7 +17914,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>34</v>
@@ -17973,7 +17973,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
@@ -18032,7 +18032,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -18091,7 +18091,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -18150,7 +18150,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -18209,7 +18209,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -18268,7 +18268,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -18327,7 +18327,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -18386,7 +18386,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -18445,7 +18445,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -18504,7 +18504,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -18563,7 +18563,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -18622,7 +18622,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -18681,7 +18681,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -18740,7 +18740,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
@@ -18799,7 +18799,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -18858,7 +18858,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -18917,7 +18917,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -18976,7 +18976,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -19035,7 +19035,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -19094,7 +19094,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
@@ -19153,7 +19153,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
@@ -19212,7 +19212,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -19271,7 +19271,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
@@ -19330,7 +19330,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
@@ -19389,7 +19389,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B34" t="s">
         <v>34</v>
@@ -19448,7 +19448,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
@@ -19507,7 +19507,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
@@ -19566,7 +19566,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
@@ -19625,7 +19625,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
         <v>34</v>
@@ -19684,7 +19684,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>34</v>
@@ -19743,7 +19743,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>34</v>
@@ -19802,7 +19802,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
         <v>34</v>
@@ -19861,7 +19861,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
@@ -19920,7 +19920,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
         <v>34</v>
@@ -19979,7 +19979,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B44" t="s">
         <v>34</v>
@@ -20038,13 +20038,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B45" t="s">
         <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>266</v>
       </c>
       <c r="D45" t="s">
         <v>34</v>
@@ -20097,7 +20097,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
         <v>34</v>
@@ -20156,7 +20156,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
         <v>34</v>
@@ -20215,7 +20215,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
         <v>34</v>
@@ -20274,7 +20274,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
         <v>34</v>
@@ -20333,7 +20333,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s">
         <v>34</v>
@@ -20392,7 +20392,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B51" t="s">
         <v>34</v>
@@ -20451,7 +20451,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B52" t="s">
         <v>34</v>
@@ -20510,7 +20510,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
         <v>34</v>
@@ -20569,7 +20569,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B54" t="s">
         <v>34</v>
@@ -20628,7 +20628,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B55" t="s">
         <v>34</v>
@@ -20687,7 +20687,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B56" t="s">
         <v>34</v>
@@ -20746,7 +20746,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B57" t="s">
         <v>34</v>
@@ -20805,7 +20805,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B58" t="s">
         <v>34</v>
@@ -20864,7 +20864,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B59" t="s">
         <v>34</v>
@@ -20923,7 +20923,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B60" t="s">
         <v>34</v>
@@ -20982,7 +20982,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B61" t="s">
         <v>34</v>
@@ -21041,7 +21041,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B62" t="s">
         <v>34</v>
@@ -21100,7 +21100,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s">
         <v>34</v>
@@ -21159,7 +21159,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B64" t="s">
         <v>34</v>
@@ -21218,7 +21218,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B65" t="s">
         <v>34</v>
@@ -21277,7 +21277,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B66" t="s">
         <v>34</v>
@@ -21336,7 +21336,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B67" t="s">
         <v>34</v>
@@ -21395,7 +21395,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B68" t="s">
         <v>34</v>
@@ -21454,7 +21454,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B69" t="s">
         <v>34</v>
@@ -21513,7 +21513,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B70" t="s">
         <v>34</v>
@@ -21572,7 +21572,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B71" t="s">
         <v>34</v>
@@ -21631,7 +21631,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B72" t="s">
         <v>34</v>
@@ -21690,7 +21690,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>34</v>
@@ -21749,7 +21749,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B74" t="s">
         <v>34</v>
@@ -21822,7 +21822,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.71875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="15.82421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -21963,11 +21963,11 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>266</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -21988,11 +21988,11 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B4"/>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>266</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -20,8 +20,83 @@
 </workbook>
 </file>
 
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S028: Securing scalable Hibernate
+  Chad Poe
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S028: Securing scalable Hibernate
+  Chad Poe
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C45" authorId="0">
+      <text>
+        <t>S028: Securing scalable Hibernate
+  Chad Poe
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S028: Securing scalable Hibernate
+  Chad Poe
+  PINNED BY USER</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0">
+      <text>
+        <t>S028: Securing scalable Hibernate
+  Chad Poe
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6300" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6351" uniqueCount="479">
   <si>
     <t>Conference name</t>
   </si>
@@ -1770,6 +1845,9 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -1916,26 +1994,60 @@
       <c r="A3" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
+      <c r="D3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -1945,6 +2057,7 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -16707,6 +16820,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -17466,11 +17582,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -21869,11 +21989,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -22020,51 +22144,119 @@
       <c r="A3" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
+      <c r="D3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="C4" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
+      <c r="D4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -22074,11 +22266,15 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6619" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6619" uniqueCount="522">
   <si>
     <t>Conference name</t>
   </si>
@@ -311,367 +311,370 @@
     <t>End</t>
   </si>
   <si>
+    <t>Talk types</t>
+  </si>
+  <si>
+    <t>Tags</t>
+  </si>
+  <si>
+    <t>Mon 2018-10-01</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>Lab</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>Breakout</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>Tue 2018-10-02</t>
+  </si>
+  <si>
+    <t>Wed 2018-10-03</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>10:15-12:15</t>
+  </si>
+  <si>
+    <t>10:15-11:00</t>
+  </si>
+  <si>
+    <t>11:30-12:15</t>
+  </si>
+  <si>
+    <t>13:00-15:00</t>
+  </si>
+  <si>
+    <t>15:30-16:15</t>
+  </si>
+  <si>
+    <t>16:30-17:15</t>
+  </si>
+  <si>
+    <t>R 1</t>
+  </si>
+  <si>
+    <t>Large, Recorded</t>
+  </si>
+  <si>
+    <t>R 2</t>
+  </si>
+  <si>
+    <t>R 3</t>
+  </si>
+  <si>
+    <t>Recorded</t>
+  </si>
+  <si>
+    <t>R 4</t>
+  </si>
+  <si>
+    <t>R 5</t>
+  </si>
+  <si>
+    <t>Lab_room, Large, Recorded</t>
+  </si>
+  <si>
+    <t>R 6</t>
+  </si>
+  <si>
+    <t>R 7</t>
+  </si>
+  <si>
+    <t>R 8</t>
+  </si>
+  <si>
+    <t>R 9</t>
+  </si>
+  <si>
+    <t>R 10</t>
+  </si>
+  <si>
+    <t>Lab_room</t>
+  </si>
+  <si>
+    <t>Required timeslot tags</t>
+  </si>
+  <si>
+    <t>Preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Required room tags</t>
+  </si>
+  <si>
+    <t>Preferred room tags</t>
+  </si>
+  <si>
+    <t>Prohibited room tags</t>
+  </si>
+  <si>
+    <t>Undesired room tags</t>
+  </si>
+  <si>
+    <t>Amy Cole</t>
+  </si>
+  <si>
+    <t>Beth Fox</t>
+  </si>
+  <si>
+    <t>Chad Green</t>
+  </si>
+  <si>
+    <t>Dan Jones</t>
+  </si>
+  <si>
+    <t>Elsa King</t>
+  </si>
+  <si>
+    <t>Flo Li</t>
+  </si>
+  <si>
+    <t>Gus Poe</t>
+  </si>
+  <si>
+    <t>Hugo Rye</t>
+  </si>
+  <si>
+    <t>Ivy Smith</t>
+  </si>
+  <si>
+    <t>Jay Watt</t>
+  </si>
+  <si>
+    <t>Amy Fox</t>
+  </si>
+  <si>
+    <t>Beth Green</t>
+  </si>
+  <si>
+    <t>Chad Jones</t>
+  </si>
+  <si>
+    <t>Dan King</t>
+  </si>
+  <si>
+    <t>Elsa Li</t>
+  </si>
+  <si>
+    <t>Flo Poe</t>
+  </si>
+  <si>
+    <t>Gus Rye</t>
+  </si>
+  <si>
+    <t>Hugo Smith</t>
+  </si>
+  <si>
+    <t>Ivy Watt</t>
+  </si>
+  <si>
+    <t>Jay Cole</t>
+  </si>
+  <si>
+    <t>Amy Green</t>
+  </si>
+  <si>
+    <t>Beth Jones</t>
+  </si>
+  <si>
+    <t>Chad King</t>
+  </si>
+  <si>
+    <t>Dan Li</t>
+  </si>
+  <si>
+    <t>Elsa Poe</t>
+  </si>
+  <si>
+    <t>Flo Rye</t>
+  </si>
+  <si>
+    <t>Gus Smith</t>
+  </si>
+  <si>
+    <t>Hugo Watt</t>
+  </si>
+  <si>
+    <t>Ivy Cole</t>
+  </si>
+  <si>
+    <t>Jay Fox</t>
+  </si>
+  <si>
+    <t>Amy Jones</t>
+  </si>
+  <si>
+    <t>Beth King</t>
+  </si>
+  <si>
+    <t>Chad Li</t>
+  </si>
+  <si>
+    <t>Dan Poe</t>
+  </si>
+  <si>
+    <t>Elsa Rye</t>
+  </si>
+  <si>
+    <t>Flo Smith</t>
+  </si>
+  <si>
+    <t>Gus Watt</t>
+  </si>
+  <si>
+    <t>Hugo Cole</t>
+  </si>
+  <si>
+    <t>Ivy Fox</t>
+  </si>
+  <si>
+    <t>Jay Green</t>
+  </si>
+  <si>
+    <t>Amy King</t>
+  </si>
+  <si>
+    <t>Beth Li</t>
+  </si>
+  <si>
+    <t>Chad Poe</t>
+  </si>
+  <si>
+    <t>Dan Rye</t>
+  </si>
+  <si>
+    <t>Elsa Smith</t>
+  </si>
+  <si>
+    <t>Flo Watt</t>
+  </si>
+  <si>
+    <t>Gus Cole</t>
+  </si>
+  <si>
+    <t>Hugo Fox</t>
+  </si>
+  <si>
+    <t>Ivy Green</t>
+  </si>
+  <si>
+    <t>Jay Jones</t>
+  </si>
+  <si>
+    <t>Amy Li</t>
+  </si>
+  <si>
+    <t>Beth Poe</t>
+  </si>
+  <si>
+    <t>Chad Rye</t>
+  </si>
+  <si>
+    <t>Dan Smith</t>
+  </si>
+  <si>
+    <t>Elsa Watt</t>
+  </si>
+  <si>
+    <t>Flo Cole</t>
+  </si>
+  <si>
+    <t>Gus Fox</t>
+  </si>
+  <si>
+    <t>Hugo Green</t>
+  </si>
+  <si>
+    <t>Ivy Jones</t>
+  </si>
+  <si>
+    <t>Jay King</t>
+  </si>
+  <si>
+    <t>Amy Poe</t>
+  </si>
+  <si>
+    <t>Beth Rye</t>
+  </si>
+  <si>
+    <t>Chad Smith</t>
+  </si>
+  <si>
+    <t>Dan Watt</t>
+  </si>
+  <si>
+    <t>Elsa Cole</t>
+  </si>
+  <si>
+    <t>Flo Fox</t>
+  </si>
+  <si>
+    <t>Gus Green</t>
+  </si>
+  <si>
+    <t>Hugo Jones</t>
+  </si>
+  <si>
+    <t>Ivy King</t>
+  </si>
+  <si>
+    <t>Jay Li</t>
+  </si>
+  <si>
+    <t>Amy Rye</t>
+  </si>
+  <si>
+    <t>Beth Smith</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
     <t>Talk type</t>
-  </si>
-  <si>
-    <t>Tags</t>
-  </si>
-  <si>
-    <t>Mon 2018-10-01</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>Lab</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>Breakout</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>Tue 2018-10-02</t>
-  </si>
-  <si>
-    <t>Wed 2018-10-03</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>10:15-12:15</t>
-  </si>
-  <si>
-    <t>10:15-11:00</t>
-  </si>
-  <si>
-    <t>11:30-12:15</t>
-  </si>
-  <si>
-    <t>13:00-15:00</t>
-  </si>
-  <si>
-    <t>15:30-16:15</t>
-  </si>
-  <si>
-    <t>16:30-17:15</t>
-  </si>
-  <si>
-    <t>R 1</t>
-  </si>
-  <si>
-    <t>Large, Recorded</t>
-  </si>
-  <si>
-    <t>R 2</t>
-  </si>
-  <si>
-    <t>R 3</t>
-  </si>
-  <si>
-    <t>Recorded</t>
-  </si>
-  <si>
-    <t>R 4</t>
-  </si>
-  <si>
-    <t>R 5</t>
-  </si>
-  <si>
-    <t>Lab_room, Large, Recorded</t>
-  </si>
-  <si>
-    <t>R 6</t>
-  </si>
-  <si>
-    <t>R 7</t>
-  </si>
-  <si>
-    <t>R 8</t>
-  </si>
-  <si>
-    <t>R 9</t>
-  </si>
-  <si>
-    <t>R 10</t>
-  </si>
-  <si>
-    <t>Lab_room</t>
-  </si>
-  <si>
-    <t>Required timeslot tags</t>
-  </si>
-  <si>
-    <t>Preferred timeslot tags</t>
-  </si>
-  <si>
-    <t>Prohibited timeslot tags</t>
-  </si>
-  <si>
-    <t>Undesired timeslot tags</t>
-  </si>
-  <si>
-    <t>Required room tags</t>
-  </si>
-  <si>
-    <t>Preferred room tags</t>
-  </si>
-  <si>
-    <t>Prohibited room tags</t>
-  </si>
-  <si>
-    <t>Undesired room tags</t>
-  </si>
-  <si>
-    <t>Amy Cole</t>
-  </si>
-  <si>
-    <t>Beth Fox</t>
-  </si>
-  <si>
-    <t>Chad Green</t>
-  </si>
-  <si>
-    <t>Dan Jones</t>
-  </si>
-  <si>
-    <t>Elsa King</t>
-  </si>
-  <si>
-    <t>Flo Li</t>
-  </si>
-  <si>
-    <t>Gus Poe</t>
-  </si>
-  <si>
-    <t>Hugo Rye</t>
-  </si>
-  <si>
-    <t>Ivy Smith</t>
-  </si>
-  <si>
-    <t>Jay Watt</t>
-  </si>
-  <si>
-    <t>Amy Fox</t>
-  </si>
-  <si>
-    <t>Beth Green</t>
-  </si>
-  <si>
-    <t>Chad Jones</t>
-  </si>
-  <si>
-    <t>Dan King</t>
-  </si>
-  <si>
-    <t>Elsa Li</t>
-  </si>
-  <si>
-    <t>Flo Poe</t>
-  </si>
-  <si>
-    <t>Gus Rye</t>
-  </si>
-  <si>
-    <t>Hugo Smith</t>
-  </si>
-  <si>
-    <t>Ivy Watt</t>
-  </si>
-  <si>
-    <t>Jay Cole</t>
-  </si>
-  <si>
-    <t>Amy Green</t>
-  </si>
-  <si>
-    <t>Beth Jones</t>
-  </si>
-  <si>
-    <t>Chad King</t>
-  </si>
-  <si>
-    <t>Dan Li</t>
-  </si>
-  <si>
-    <t>Elsa Poe</t>
-  </si>
-  <si>
-    <t>Flo Rye</t>
-  </si>
-  <si>
-    <t>Gus Smith</t>
-  </si>
-  <si>
-    <t>Hugo Watt</t>
-  </si>
-  <si>
-    <t>Ivy Cole</t>
-  </si>
-  <si>
-    <t>Jay Fox</t>
-  </si>
-  <si>
-    <t>Amy Jones</t>
-  </si>
-  <si>
-    <t>Beth King</t>
-  </si>
-  <si>
-    <t>Chad Li</t>
-  </si>
-  <si>
-    <t>Dan Poe</t>
-  </si>
-  <si>
-    <t>Elsa Rye</t>
-  </si>
-  <si>
-    <t>Flo Smith</t>
-  </si>
-  <si>
-    <t>Gus Watt</t>
-  </si>
-  <si>
-    <t>Hugo Cole</t>
-  </si>
-  <si>
-    <t>Ivy Fox</t>
-  </si>
-  <si>
-    <t>Jay Green</t>
-  </si>
-  <si>
-    <t>Amy King</t>
-  </si>
-  <si>
-    <t>Beth Li</t>
-  </si>
-  <si>
-    <t>Chad Poe</t>
-  </si>
-  <si>
-    <t>Dan Rye</t>
-  </si>
-  <si>
-    <t>Elsa Smith</t>
-  </si>
-  <si>
-    <t>Flo Watt</t>
-  </si>
-  <si>
-    <t>Gus Cole</t>
-  </si>
-  <si>
-    <t>Hugo Fox</t>
-  </si>
-  <si>
-    <t>Ivy Green</t>
-  </si>
-  <si>
-    <t>Jay Jones</t>
-  </si>
-  <si>
-    <t>Amy Li</t>
-  </si>
-  <si>
-    <t>Beth Poe</t>
-  </si>
-  <si>
-    <t>Chad Rye</t>
-  </si>
-  <si>
-    <t>Dan Smith</t>
-  </si>
-  <si>
-    <t>Elsa Watt</t>
-  </si>
-  <si>
-    <t>Flo Cole</t>
-  </si>
-  <si>
-    <t>Gus Fox</t>
-  </si>
-  <si>
-    <t>Hugo Green</t>
-  </si>
-  <si>
-    <t>Ivy Jones</t>
-  </si>
-  <si>
-    <t>Jay King</t>
-  </si>
-  <si>
-    <t>Amy Poe</t>
-  </si>
-  <si>
-    <t>Beth Rye</t>
-  </si>
-  <si>
-    <t>Chad Smith</t>
-  </si>
-  <si>
-    <t>Dan Watt</t>
-  </si>
-  <si>
-    <t>Elsa Cole</t>
-  </si>
-  <si>
-    <t>Flo Fox</t>
-  </si>
-  <si>
-    <t>Gus Green</t>
-  </si>
-  <si>
-    <t>Hugo Jones</t>
-  </si>
-  <si>
-    <t>Ivy King</t>
-  </si>
-  <si>
-    <t>Jay Li</t>
-  </si>
-  <si>
-    <t>Amy Rye</t>
-  </si>
-  <si>
-    <t>Beth Smith</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Title</t>
   </si>
   <si>
     <t>Speakers</t>
@@ -2281,7 +2284,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -2340,13 +2343,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2499,7 +2502,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -2558,13 +2561,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2717,7 +2720,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -2776,13 +2779,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2853,7 +2856,7 @@
     <col min="1" max="1" width="16.0078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="6.0859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="6.0859375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="9.41796875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.29296875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="5.1484375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -10193,28 +10196,28 @@
         <v>179</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>98</v>
@@ -10241,10 +10244,10 @@
         <v>105</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>57</v>
@@ -10253,39 +10256,39 @@
         <v>58</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>65</v>
@@ -10329,34 +10332,34 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>65</v>
@@ -10400,34 +10403,34 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>65</v>
@@ -10471,10 +10474,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>64</v>
@@ -10483,22 +10486,22 @@
         <v>112</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>65</v>
@@ -10542,10 +10545,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>64</v>
@@ -10554,22 +10557,22 @@
         <v>113</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>65</v>
@@ -10613,10 +10616,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>64</v>
@@ -10625,22 +10628,22 @@
         <v>114</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>65</v>
@@ -10684,34 +10687,34 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>65</v>
@@ -10755,10 +10758,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>64</v>
@@ -10767,22 +10770,22 @@
         <v>117</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>65</v>
@@ -10826,10 +10829,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>64</v>
@@ -10838,22 +10841,22 @@
         <v>118</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>65</v>
@@ -10897,10 +10900,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>64</v>
@@ -10909,22 +10912,22 @@
         <v>119</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>65</v>
@@ -10968,34 +10971,34 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>65</v>
@@ -11039,10 +11042,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>64</v>
@@ -11051,22 +11054,22 @@
         <v>122</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>65</v>
@@ -11110,34 +11113,34 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>65</v>
@@ -11181,10 +11184,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>67</v>
@@ -11193,22 +11196,22 @@
         <v>125</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>65</v>
@@ -11252,10 +11255,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>67</v>
@@ -11264,22 +11267,22 @@
         <v>126</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>65</v>
@@ -11323,10 +11326,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>67</v>
@@ -11335,22 +11338,22 @@
         <v>127</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>65</v>
@@ -11394,34 +11397,34 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -11465,10 +11468,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>67</v>
@@ -11477,22 +11480,22 @@
         <v>130</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>65</v>
@@ -11536,10 +11539,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>67</v>
@@ -11548,22 +11551,22 @@
         <v>131</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>65</v>
@@ -11607,10 +11610,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>67</v>
@@ -11619,22 +11622,22 @@
         <v>132</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>65</v>
@@ -11678,10 +11681,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>67</v>
@@ -11690,22 +11693,22 @@
         <v>133</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>65</v>
@@ -11749,10 +11752,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>67</v>
@@ -11761,22 +11764,22 @@
         <v>134</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>65</v>
@@ -11820,34 +11823,34 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>65</v>
@@ -11891,10 +11894,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>67</v>
@@ -11903,22 +11906,22 @@
         <v>137</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>65</v>
@@ -11962,34 +11965,34 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>65</v>
@@ -12033,10 +12036,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>67</v>
@@ -12045,22 +12048,22 @@
         <v>140</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>65</v>
@@ -12104,10 +12107,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>67</v>
@@ -12116,22 +12119,22 @@
         <v>141</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>65</v>
@@ -12175,34 +12178,34 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>65</v>
@@ -12246,34 +12249,34 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>65</v>
@@ -12317,10 +12320,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>67</v>
@@ -12329,22 +12332,22 @@
         <v>146</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>65</v>
@@ -12388,10 +12391,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>67</v>
@@ -12400,22 +12403,22 @@
         <v>147</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>65</v>
@@ -12459,10 +12462,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>67</v>
@@ -12471,22 +12474,22 @@
         <v>148</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>65</v>
@@ -12530,10 +12533,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>67</v>
@@ -12542,22 +12545,22 @@
         <v>149</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>65</v>
@@ -12601,10 +12604,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>67</v>
@@ -12613,22 +12616,22 @@
         <v>150</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>65</v>
@@ -12672,34 +12675,34 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>65</v>
@@ -12743,10 +12746,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>67</v>
@@ -12755,22 +12758,22 @@
         <v>153</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>65</v>
@@ -12814,34 +12817,34 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>65</v>
@@ -12885,34 +12888,34 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>65</v>
@@ -12956,10 +12959,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>67</v>
@@ -12968,22 +12971,22 @@
         <v>158</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>65</v>
@@ -13027,34 +13030,34 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>65</v>
@@ -13098,10 +13101,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>67</v>
@@ -13110,22 +13113,22 @@
         <v>161</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>65</v>
@@ -13169,34 +13172,34 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>65</v>
@@ -13240,10 +13243,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>67</v>
@@ -13252,22 +13255,22 @@
         <v>166</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>65</v>
@@ -13311,10 +13314,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>67</v>
@@ -13323,22 +13326,22 @@
         <v>167</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>65</v>
@@ -13382,10 +13385,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>67</v>
@@ -13394,22 +13397,22 @@
         <v>168</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>65</v>
@@ -13453,10 +13456,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>67</v>
@@ -13465,22 +13468,22 @@
         <v>169</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>65</v>
@@ -13524,10 +13527,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>67</v>
@@ -13536,22 +13539,22 @@
         <v>170</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>65</v>
@@ -13595,10 +13598,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>67</v>
@@ -13607,22 +13610,22 @@
         <v>171</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>65</v>
@@ -13666,34 +13669,34 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>65</v>
@@ -13737,10 +13740,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>67</v>
@@ -13749,22 +13752,22 @@
         <v>174</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>65</v>
@@ -13808,34 +13811,34 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>65</v>
@@ -13879,34 +13882,34 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>65</v>
@@ -13950,34 +13953,34 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>65</v>
@@ -14021,10 +14024,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>67</v>
@@ -14033,22 +14036,22 @@
         <v>109</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>65</v>
@@ -14092,10 +14095,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>67</v>
@@ -14104,22 +14107,22 @@
         <v>110</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>65</v>
@@ -14163,34 +14166,34 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>65</v>
@@ -14234,34 +14237,34 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>65</v>
@@ -14305,10 +14308,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>67</v>
@@ -14317,22 +14320,22 @@
         <v>115</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>65</v>
@@ -14376,34 +14379,34 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>65</v>
@@ -14447,10 +14450,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>67</v>
@@ -14459,22 +14462,22 @@
         <v>118</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>65</v>
@@ -14518,34 +14521,34 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>65</v>
@@ -14589,10 +14592,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>67</v>
@@ -14601,22 +14604,22 @@
         <v>121</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>65</v>
@@ -14660,10 +14663,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>67</v>
@@ -14672,22 +14675,22 @@
         <v>122</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>65</v>
@@ -14731,10 +14734,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>67</v>
@@ -14743,22 +14746,22 @@
         <v>123</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>65</v>
@@ -14802,34 +14805,34 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>65</v>
@@ -14873,10 +14876,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>67</v>
@@ -14885,22 +14888,22 @@
         <v>126</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>65</v>
@@ -14944,34 +14947,34 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>65</v>
@@ -15015,10 +15018,10 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>67</v>
@@ -15027,22 +15030,22 @@
         <v>129</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>65</v>
@@ -15086,10 +15089,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>67</v>
@@ -15098,22 +15101,22 @@
         <v>130</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>65</v>
@@ -15157,34 +15160,34 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>65</v>
@@ -15228,34 +15231,34 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>65</v>
@@ -15299,10 +15302,10 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>67</v>
@@ -15311,22 +15314,22 @@
         <v>135</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>65</v>
@@ -15370,10 +15373,10 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>67</v>
@@ -15382,22 +15385,22 @@
         <v>136</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>65</v>
@@ -15441,10 +15444,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>67</v>
@@ -15453,22 +15456,22 @@
         <v>137</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>65</v>
@@ -15512,10 +15515,10 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>67</v>
@@ -15524,22 +15527,22 @@
         <v>138</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>65</v>
@@ -15583,10 +15586,10 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>67</v>
@@ -15595,22 +15598,22 @@
         <v>139</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>65</v>
@@ -15654,10 +15657,10 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>67</v>
@@ -15666,22 +15669,22 @@
         <v>140</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>65</v>
@@ -15725,34 +15728,34 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>65</v>
@@ -15796,34 +15799,34 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>65</v>
@@ -15867,10 +15870,10 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>67</v>
@@ -15879,22 +15882,22 @@
         <v>145</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>65</v>
@@ -15938,34 +15941,34 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>65</v>
@@ -16009,10 +16012,10 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>67</v>
@@ -16021,22 +16024,22 @@
         <v>148</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>65</v>
@@ -16080,10 +16083,10 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>67</v>
@@ -16092,22 +16095,22 @@
         <v>149</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>65</v>
@@ -16151,34 +16154,34 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>65</v>
@@ -16222,34 +16225,34 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>65</v>
@@ -16293,34 +16296,34 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>65</v>
@@ -16364,34 +16367,34 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>65</v>
@@ -16435,10 +16438,10 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>67</v>
@@ -16447,22 +16450,22 @@
         <v>159</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>65</v>
@@ -16506,10 +16509,10 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>67</v>
@@ -16518,22 +16521,22 @@
         <v>160</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>65</v>
@@ -16577,34 +16580,34 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>65</v>
@@ -16648,10 +16651,10 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>67</v>
@@ -16660,22 +16663,22 @@
         <v>164</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>65</v>
@@ -16719,34 +16722,34 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>65</v>
@@ -16790,10 +16793,10 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>67</v>
@@ -16802,22 +16805,22 @@
         <v>167</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>65</v>
@@ -16861,34 +16864,34 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>65</v>
@@ -16932,34 +16935,34 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>65</v>
@@ -17003,10 +17006,10 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>67</v>
@@ -17015,22 +17018,22 @@
         <v>172</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K97" s="2" t="s">
         <v>65</v>
@@ -17074,34 +17077,34 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>65</v>
@@ -17145,34 +17148,34 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K99" s="2" t="s">
         <v>65</v>
@@ -17216,10 +17219,10 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>67</v>
@@ -17228,22 +17231,22 @@
         <v>177</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>65</v>
@@ -17287,10 +17290,10 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>67</v>
@@ -17299,22 +17302,22 @@
         <v>106</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K101" s="2" t="s">
         <v>65</v>
@@ -17358,34 +17361,34 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>65</v>
@@ -17429,10 +17432,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>67</v>
@@ -17441,22 +17444,22 @@
         <v>109</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K103" s="2" t="s">
         <v>65</v>
@@ -17500,10 +17503,10 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>67</v>
@@ -17512,22 +17515,22 @@
         <v>110</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>65</v>
@@ -17571,34 +17574,34 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K105" s="2" t="s">
         <v>65</v>
@@ -17642,10 +17645,10 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>67</v>
@@ -17654,22 +17657,22 @@
         <v>113</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>65</v>
@@ -17713,34 +17716,34 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H107" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>65</v>
@@ -17784,10 +17787,10 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>67</v>
@@ -17796,22 +17799,22 @@
         <v>116</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>65</v>
@@ -17855,10 +17858,10 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>67</v>
@@ -17867,22 +17870,22 @@
         <v>117</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K109" s="2" t="s">
         <v>65</v>
@@ -18039,7 +18042,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -18104,7 +18107,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -18788,7 +18791,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -20682,7 +20685,7 @@
         <v>65</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>65</v>
@@ -23195,7 +23198,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -23254,13 +23257,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -23313,13 +23316,13 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>65</v>
@@ -23472,7 +23475,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -11,32 +11,16 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Rooms view" r:id="rId8" sheetId="6"/>
-    <sheet name="Speakers view" r:id="rId9" sheetId="7"/>
-    <sheet name="Theme tracks view" r:id="rId10" sheetId="8"/>
-    <sheet name="Sectors view" r:id="rId11" sheetId="9"/>
-    <sheet name="Audience type view" r:id="rId12" sheetId="10"/>
-    <sheet name="Audience level view" r:id="rId13" sheetId="11"/>
-    <sheet name="Contents view" r:id="rId14" sheetId="12"/>
+    <sheet name="Score view" r:id="rId8" sheetId="6"/>
+    <sheet name="Rooms view" r:id="rId9" sheetId="7"/>
+    <sheet name="Speakers view" r:id="rId10" sheetId="8"/>
+    <sheet name="Theme tracks view" r:id="rId11" sheetId="9"/>
+    <sheet name="Sectors view" r:id="rId12" sheetId="10"/>
+    <sheet name="Audience type view" r:id="rId13" sheetId="11"/>
+    <sheet name="Audience level view" r:id="rId14" sheetId="12"/>
+    <sheet name="Contents view" r:id="rId15" sheetId="13"/>
   </sheets>
 </workbook>
-</file>
-
-<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment ref="C3" authorId="0">
-      <text>
-        <t>S073: Grok distributed Tensorflow
-  Beth King
-  PINNED BY USER</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -73,7 +57,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
@@ -96,6 +80,23 @@
     <author/>
   </authors>
   <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t>S073: Grok distributed Tensorflow
+  Beth King
+  PINNED BY USER</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
     <comment ref="C34" authorId="0">
       <text>
         <t>S073: Grok distributed Tensorflow
@@ -107,7 +108,7 @@
 </comments>
 </file>
 
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
@@ -132,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6619" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6640" uniqueCount="526">
   <si>
     <t>Conference name</t>
   </si>
@@ -407,9 +408,6 @@
     <t>R 5</t>
   </si>
   <si>
-    <t>Lab_room, Large, Recorded</t>
-  </si>
-  <si>
     <t>R 6</t>
   </si>
   <si>
@@ -425,9 +423,6 @@
     <t>R 10</t>
   </si>
   <si>
-    <t>Lab_room</t>
-  </si>
-  <si>
     <t>Required timeslot tags</t>
   </si>
   <si>
@@ -1674,6 +1669,24 @@
   </si>
   <si>
     <t>Building deep learning Angular</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>-214init</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Usable timeslots</t>
+  </si>
+  <si>
+    <t>Usable rooms</t>
+  </si>
+  <si>
+    <t>Usable sessions</t>
   </si>
   <si>
     <t>S073: Grok distributed Tensorflow
@@ -1806,6 +1819,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
@@ -2202,6 +2219,164 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
+    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
     <col min="1" max="1" width="14.1953125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -2284,7 +2459,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -2343,13 +2518,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2412,7 +2587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -2502,7 +2677,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -2561,13 +2736,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2630,7 +2805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -2720,7 +2895,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -2779,13 +2954,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -3195,8 +3370,8 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="6.48828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="25.6328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="10.29296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.51171875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
@@ -3214,6 +3389,7 @@
     <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="11.86328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3224,11 +3400,11 @@
         <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="E1" s="1" t="s">
         <v>65</v>
       </c>
@@ -3242,11 +3418,11 @@
         <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="K1" s="1" t="s">
         <v>65</v>
       </c>
@@ -3260,11 +3436,11 @@
         <v>65</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="Q1" s="1" t="s">
         <v>65</v>
       </c>
@@ -3275,6 +3451,9 @@
         <v>65</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3283,60 +3462,63 @@
         <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3345,60 +3527,63 @@
         <v>84</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="I3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M3" s="2" t="s">
+      <c r="L3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P3" s="2" t="s">
+      <c r="O3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="S3" s="2" t="s">
+      <c r="R3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3407,60 +3592,63 @@
         <v>86</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="I4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M4" s="2" t="s">
+      <c r="L4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P4" s="2" t="s">
+      <c r="O4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="S4" s="2" t="s">
+      <c r="R4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3469,60 +3657,63 @@
         <v>87</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="I5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M5" s="2" t="s">
+      <c r="L5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P5" s="2" t="s">
+      <c r="O5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="S5" s="2" t="s">
+      <c r="R5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U5" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3531,60 +3722,63 @@
         <v>89</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="I6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M6" s="2" t="s">
+      <c r="L6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P6" s="2" t="s">
+      <c r="O6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="S6" s="2" t="s">
+      <c r="R6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3593,378 +3787,396 @@
         <v>90</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="I7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7" s="3" t="s">
+      <c r="L7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="P7" s="3" t="s">
+      <c r="O7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="S7" s="3" t="s">
+      <c r="R7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="S7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="U7" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" s="2" t="s">
+      <c r="L8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P8" s="2" t="s">
+      <c r="O8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="S8" s="2" t="s">
+      <c r="R8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U8" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M9" s="2" t="s">
+      <c r="L9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P9" s="2" t="s">
+      <c r="O9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="S9" s="2" t="s">
+      <c r="R9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U9" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" s="2" t="s">
+      <c r="L10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P10" s="2" t="s">
+      <c r="O10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="S10" s="2" t="s">
+      <c r="R10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U10" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="2" t="s">
+      <c r="I11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="2" t="s">
+      <c r="L11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P11" s="2" t="s">
+      <c r="O11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="S11" s="2" t="s">
+      <c r="R11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="T11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U11" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="F12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" s="3" t="s">
+      <c r="I12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" s="3" t="s">
+      <c r="L12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="O12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="P12" s="3" t="s">
+      <c r="O12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="R12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="S12" s="3" t="s">
+      <c r="R12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="S12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="U12" s="3" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="P1:U1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
@@ -4093,28 +4305,28 @@
         <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>78</v>
@@ -4173,7 +4385,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>65</v>
@@ -4256,7 +4468,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>65</v>
@@ -4339,7 +4551,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>65</v>
@@ -4422,7 +4634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>65</v>
@@ -4505,7 +4717,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>65</v>
@@ -4588,7 +4800,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>65</v>
@@ -4671,7 +4883,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -4754,7 +4966,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -4837,7 +5049,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>65</v>
@@ -4920,7 +5132,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>65</v>
@@ -5003,7 +5215,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>65</v>
@@ -5086,7 +5298,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>65</v>
@@ -5169,7 +5381,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>65</v>
@@ -5252,7 +5464,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>65</v>
@@ -5335,7 +5547,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>65</v>
@@ -5418,7 +5630,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>65</v>
@@ -5501,7 +5713,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>65</v>
@@ -5584,7 +5796,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>65</v>
@@ -5667,7 +5879,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>65</v>
@@ -5750,7 +5962,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>65</v>
@@ -5833,7 +6045,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>65</v>
@@ -5916,7 +6128,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>65</v>
@@ -5999,7 +6211,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>65</v>
@@ -6082,7 +6294,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>65</v>
@@ -6165,7 +6377,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>65</v>
@@ -6248,7 +6460,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>65</v>
@@ -6331,7 +6543,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>65</v>
@@ -6414,7 +6626,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>65</v>
@@ -6497,7 +6709,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>65</v>
@@ -6580,7 +6792,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>65</v>
@@ -6663,7 +6875,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>65</v>
@@ -6746,7 +6958,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>65</v>
@@ -6829,7 +7041,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>65</v>
@@ -6912,7 +7124,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>65</v>
@@ -6995,7 +7207,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>65</v>
@@ -7078,7 +7290,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>65</v>
@@ -7161,7 +7373,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>65</v>
@@ -7244,7 +7456,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>65</v>
@@ -7327,7 +7539,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>65</v>
@@ -7410,7 +7622,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>65</v>
@@ -7493,7 +7705,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>65</v>
@@ -7576,7 +7788,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>65</v>
@@ -7659,7 +7871,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>65</v>
@@ -7742,7 +7954,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>65</v>
@@ -7825,7 +8037,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>65</v>
@@ -7908,7 +8120,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>65</v>
@@ -7991,7 +8203,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>65</v>
@@ -8074,7 +8286,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>65</v>
@@ -8157,7 +8369,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>65</v>
@@ -8240,7 +8452,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>65</v>
@@ -8323,7 +8535,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>65</v>
@@ -8406,7 +8618,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>65</v>
@@ -8489,7 +8701,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>65</v>
@@ -8572,7 +8784,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>65</v>
@@ -8655,7 +8867,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>65</v>
@@ -8738,7 +8950,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>65</v>
@@ -8821,7 +9033,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>65</v>
@@ -8904,7 +9116,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>65</v>
@@ -8987,7 +9199,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>65</v>
@@ -9070,7 +9282,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>65</v>
@@ -9153,7 +9365,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>65</v>
@@ -9236,7 +9448,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>65</v>
@@ -9319,7 +9531,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>65</v>
@@ -9402,7 +9614,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>65</v>
@@ -9485,7 +9697,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>65</v>
@@ -9568,7 +9780,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>65</v>
@@ -9651,7 +9863,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>65</v>
@@ -9734,7 +9946,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>65</v>
@@ -9817,7 +10029,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>65</v>
@@ -9900,7 +10112,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>65</v>
@@ -9983,7 +10195,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>65</v>
@@ -10066,7 +10278,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>65</v>
@@ -10190,64 +10402,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>57</v>
@@ -10256,39 +10468,39 @@
         <v>58</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>65</v>
@@ -10303,7 +10515,7 @@
         <v>65</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>65</v>
@@ -10332,34 +10544,34 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>65</v>
@@ -10374,7 +10586,7 @@
         <v>65</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>65</v>
@@ -10403,34 +10615,34 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>65</v>
@@ -10445,7 +10657,7 @@
         <v>65</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>65</v>
@@ -10474,34 +10686,34 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>65</v>
@@ -10516,7 +10728,7 @@
         <v>65</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>65</v>
@@ -10545,34 +10757,34 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>65</v>
@@ -10587,7 +10799,7 @@
         <v>65</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>65</v>
@@ -10616,34 +10828,34 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>65</v>
@@ -10658,7 +10870,7 @@
         <v>65</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>65</v>
@@ -10687,34 +10899,34 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>65</v>
@@ -10729,7 +10941,7 @@
         <v>65</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>65</v>
@@ -10758,34 +10970,34 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>65</v>
@@ -10800,7 +11012,7 @@
         <v>65</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>65</v>
@@ -10829,34 +11041,34 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>65</v>
@@ -10871,7 +11083,7 @@
         <v>65</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>65</v>
@@ -10900,34 +11112,34 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>65</v>
@@ -10942,7 +11154,7 @@
         <v>65</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>65</v>
@@ -10971,34 +11183,34 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>65</v>
@@ -11013,7 +11225,7 @@
         <v>65</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>65</v>
@@ -11042,34 +11254,34 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>65</v>
@@ -11084,7 +11296,7 @@
         <v>65</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>65</v>
@@ -11113,34 +11325,34 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>65</v>
@@ -11184,34 +11396,34 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>65</v>
@@ -11255,34 +11467,34 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>65</v>
@@ -11326,34 +11538,34 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>65</v>
@@ -11397,34 +11609,34 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="G18" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>65</v>
@@ -11468,34 +11680,34 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>65</v>
@@ -11539,34 +11751,34 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>65</v>
@@ -11610,34 +11822,34 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>65</v>
@@ -11681,34 +11893,34 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>65</v>
@@ -11752,34 +11964,34 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>65</v>
@@ -11823,34 +12035,34 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>65</v>
@@ -11894,34 +12106,34 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>65</v>
@@ -11965,34 +12177,34 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>65</v>
@@ -12036,34 +12248,34 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>65</v>
@@ -12107,34 +12319,34 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>65</v>
@@ -12178,34 +12390,34 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>65</v>
@@ -12249,34 +12461,34 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>65</v>
@@ -12320,34 +12532,34 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>65</v>
@@ -12391,34 +12603,34 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>65</v>
@@ -12462,34 +12674,34 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>65</v>
@@ -12533,34 +12745,34 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>65</v>
@@ -12604,34 +12816,34 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>65</v>
@@ -12675,34 +12887,34 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>65</v>
@@ -12746,34 +12958,34 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>65</v>
@@ -12817,34 +13029,34 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>65</v>
@@ -12888,34 +13100,34 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>65</v>
@@ -12959,34 +13171,34 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>65</v>
@@ -13030,34 +13242,34 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>65</v>
@@ -13101,34 +13313,34 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>65</v>
@@ -13172,34 +13384,34 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>65</v>
@@ -13243,34 +13455,34 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>65</v>
@@ -13314,34 +13526,34 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>65</v>
@@ -13385,34 +13597,34 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>65</v>
@@ -13456,34 +13668,34 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>65</v>
@@ -13527,34 +13739,34 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>65</v>
@@ -13598,34 +13810,34 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>65</v>
@@ -13669,34 +13881,34 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>65</v>
@@ -13740,34 +13952,34 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>65</v>
@@ -13811,34 +14023,34 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>65</v>
@@ -13882,34 +14094,34 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>65</v>
@@ -13953,34 +14165,34 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>65</v>
@@ -14024,34 +14236,34 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>65</v>
@@ -14095,34 +14307,34 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>65</v>
@@ -14166,34 +14378,34 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>65</v>
@@ -14237,34 +14449,34 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>65</v>
@@ -14308,34 +14520,34 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>65</v>
@@ -14379,34 +14591,34 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>65</v>
@@ -14450,34 +14662,34 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>65</v>
@@ -14521,34 +14733,34 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>65</v>
@@ -14592,34 +14804,34 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>65</v>
@@ -14663,34 +14875,34 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>65</v>
@@ -14734,34 +14946,34 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>65</v>
@@ -14805,34 +15017,34 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>65</v>
@@ -14876,34 +15088,34 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>65</v>
@@ -14947,34 +15159,34 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>65</v>
@@ -15018,34 +15230,34 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>65</v>
@@ -15089,34 +15301,34 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>65</v>
@@ -15160,34 +15372,34 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>65</v>
@@ -15231,34 +15443,34 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>65</v>
@@ -15302,34 +15514,34 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>65</v>
@@ -15373,34 +15585,34 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>65</v>
@@ -15444,34 +15656,34 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>65</v>
@@ -15515,34 +15727,34 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>65</v>
@@ -15586,34 +15798,34 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>65</v>
@@ -15657,34 +15869,34 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>65</v>
@@ -15728,34 +15940,34 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>65</v>
@@ -15799,34 +16011,34 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>65</v>
@@ -15870,34 +16082,34 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>65</v>
@@ -15941,34 +16153,34 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>65</v>
@@ -16012,34 +16224,34 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>65</v>
@@ -16083,34 +16295,34 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>65</v>
@@ -16154,34 +16366,34 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>65</v>
@@ -16225,34 +16437,34 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>65</v>
@@ -16296,34 +16508,34 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>65</v>
@@ -16367,34 +16579,34 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>65</v>
@@ -16438,34 +16650,34 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>65</v>
@@ -16509,34 +16721,34 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>65</v>
@@ -16580,34 +16792,34 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>65</v>
@@ -16651,34 +16863,34 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>65</v>
@@ -16722,34 +16934,34 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>65</v>
@@ -16793,34 +17005,34 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>65</v>
@@ -16864,34 +17076,34 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>65</v>
@@ -16935,34 +17147,34 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>65</v>
@@ -17006,34 +17218,34 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K97" s="2" t="s">
         <v>65</v>
@@ -17077,34 +17289,34 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>65</v>
@@ -17148,34 +17360,34 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K99" s="2" t="s">
         <v>65</v>
@@ -17219,34 +17431,34 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>65</v>
@@ -17290,34 +17502,34 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K101" s="2" t="s">
         <v>65</v>
@@ -17361,34 +17573,34 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>65</v>
@@ -17432,34 +17644,34 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K103" s="2" t="s">
         <v>65</v>
@@ -17503,34 +17715,34 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>65</v>
@@ -17574,34 +17786,34 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K105" s="2" t="s">
         <v>65</v>
@@ -17645,34 +17857,34 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>65</v>
@@ -17716,34 +17928,34 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H107" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>65</v>
@@ -17787,34 +17999,34 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>65</v>
@@ -17858,34 +18070,34 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K109" s="2" t="s">
         <v>65</v>
@@ -17934,6 +18146,87 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="9.4453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.95703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.22265625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.59375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="15.30078125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>96.0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>96.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -18042,7 +18335,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -18107,7 +18400,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -18396,7 +18689,7 @@
     </row>
     <row r="8" ht="60.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>65</v>
@@ -18455,7 +18748,7 @@
     </row>
     <row r="9" ht="60.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>65</v>
@@ -18514,7 +18807,7 @@
     </row>
     <row r="10" ht="60.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>65</v>
@@ -18573,7 +18866,7 @@
     </row>
     <row r="11" ht="60.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>65</v>
@@ -18632,7 +18925,7 @@
     </row>
     <row r="12" ht="60.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>65</v>
@@ -18701,7 +18994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -18791,7 +19084,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -18850,7 +19143,7 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
@@ -18909,7 +19202,7 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>65</v>
@@ -18968,7 +19261,7 @@
     </row>
     <row r="5" ht="15.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>65</v>
@@ -19027,7 +19320,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>65</v>
@@ -19086,7 +19379,7 @@
     </row>
     <row r="7" ht="15.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>65</v>
@@ -19145,7 +19438,7 @@
     </row>
     <row r="8" ht="15.0" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>65</v>
@@ -19204,7 +19497,7 @@
     </row>
     <row r="9" ht="15.0" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>65</v>
@@ -19263,7 +19556,7 @@
     </row>
     <row r="10" ht="15.0" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>65</v>
@@ -19322,7 +19615,7 @@
     </row>
     <row r="11" ht="15.0" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>65</v>
@@ -19381,7 +19674,7 @@
     </row>
     <row r="12" ht="15.0" customHeight="true">
       <c r="A12" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>65</v>
@@ -19440,7 +19733,7 @@
     </row>
     <row r="13" ht="15.0" customHeight="true">
       <c r="A13" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>65</v>
@@ -19499,7 +19792,7 @@
     </row>
     <row r="14" ht="15.0" customHeight="true">
       <c r="A14" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>65</v>
@@ -19558,7 +19851,7 @@
     </row>
     <row r="15" ht="15.0" customHeight="true">
       <c r="A15" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>65</v>
@@ -19617,7 +19910,7 @@
     </row>
     <row r="16" ht="15.0" customHeight="true">
       <c r="A16" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>65</v>
@@ -19676,7 +19969,7 @@
     </row>
     <row r="17" ht="15.0" customHeight="true">
       <c r="A17" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>65</v>
@@ -19735,7 +20028,7 @@
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>65</v>
@@ -19794,7 +20087,7 @@
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>65</v>
@@ -19853,7 +20146,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>65</v>
@@ -19912,7 +20205,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>65</v>
@@ -19971,7 +20264,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>65</v>
@@ -20030,7 +20323,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>65</v>
@@ -20089,7 +20382,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>65</v>
@@ -20148,7 +20441,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>65</v>
@@ -20207,7 +20500,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>65</v>
@@ -20266,7 +20559,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="true">
       <c r="A27" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>65</v>
@@ -20325,7 +20618,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="true">
       <c r="A28" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>65</v>
@@ -20384,7 +20677,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="true">
       <c r="A29" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>65</v>
@@ -20443,7 +20736,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="true">
       <c r="A30" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>65</v>
@@ -20502,7 +20795,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="true">
       <c r="A31" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>65</v>
@@ -20561,7 +20854,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="true">
       <c r="A32" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>65</v>
@@ -20620,7 +20913,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="true">
       <c r="A33" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>65</v>
@@ -20679,13 +20972,13 @@
     </row>
     <row r="34" ht="15.0" customHeight="true">
       <c r="A34" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>65</v>
@@ -20738,7 +21031,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="true">
       <c r="A35" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>65</v>
@@ -20797,7 +21090,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="true">
       <c r="A36" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>65</v>
@@ -20856,7 +21149,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="true">
       <c r="A37" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>65</v>
@@ -20915,7 +21208,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="true">
       <c r="A38" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>65</v>
@@ -20974,7 +21267,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="true">
       <c r="A39" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>65</v>
@@ -21033,7 +21326,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="true">
       <c r="A40" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>65</v>
@@ -21092,7 +21385,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="true">
       <c r="A41" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>65</v>
@@ -21151,7 +21444,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="true">
       <c r="A42" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>65</v>
@@ -21210,7 +21503,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="true">
       <c r="A43" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>65</v>
@@ -21269,7 +21562,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="true">
       <c r="A44" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>65</v>
@@ -21328,7 +21621,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="true">
       <c r="A45" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>65</v>
@@ -21387,7 +21680,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="true">
       <c r="A46" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>65</v>
@@ -21446,7 +21739,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="true">
       <c r="A47" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>65</v>
@@ -21505,7 +21798,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="true">
       <c r="A48" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>65</v>
@@ -21564,7 +21857,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="true">
       <c r="A49" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>65</v>
@@ -21623,7 +21916,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="true">
       <c r="A50" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>65</v>
@@ -21682,7 +21975,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="true">
       <c r="A51" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>65</v>
@@ -21741,7 +22034,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="true">
       <c r="A52" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>65</v>
@@ -21800,7 +22093,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="true">
       <c r="A53" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>65</v>
@@ -21859,7 +22152,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="true">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>65</v>
@@ -21918,7 +22211,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="true">
       <c r="A55" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>65</v>
@@ -21977,7 +22270,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="true">
       <c r="A56" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>65</v>
@@ -22036,7 +22329,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="true">
       <c r="A57" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>65</v>
@@ -22095,7 +22388,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="true">
       <c r="A58" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>65</v>
@@ -22154,7 +22447,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="true">
       <c r="A59" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>65</v>
@@ -22213,7 +22506,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="true">
       <c r="A60" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>65</v>
@@ -22272,7 +22565,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="true">
       <c r="A61" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>65</v>
@@ -22331,7 +22624,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="true">
       <c r="A62" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>65</v>
@@ -22390,7 +22683,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="true">
       <c r="A63" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>65</v>
@@ -22449,7 +22742,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="true">
       <c r="A64" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>65</v>
@@ -22508,7 +22801,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="true">
       <c r="A65" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>65</v>
@@ -22567,7 +22860,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="true">
       <c r="A66" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>65</v>
@@ -22626,7 +22919,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="true">
       <c r="A67" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>65</v>
@@ -22685,7 +22978,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="true">
       <c r="A68" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>65</v>
@@ -22744,7 +23037,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="true">
       <c r="A69" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>65</v>
@@ -22803,7 +23096,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="true">
       <c r="A70" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>65</v>
@@ -22862,7 +23155,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="true">
       <c r="A71" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>65</v>
@@ -22921,7 +23214,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="true">
       <c r="A72" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>65</v>
@@ -22980,7 +23273,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="true">
       <c r="A73" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>65</v>
@@ -23039,7 +23332,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="true">
       <c r="A74" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>65</v>
@@ -23108,7 +23401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FCE94F"/>
@@ -23198,7 +23491,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -23257,13 +23550,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -23316,13 +23609,13 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>65</v>
@@ -23383,162 +23676,4 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <tabColor rgb="FCE94F"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="10.23828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:S1"/>
-  </mergeCells>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6640" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6641" uniqueCount="528">
   <si>
     <t>Conference name</t>
   </si>
@@ -681,7 +681,7 @@
     <t>Sector tags</t>
   </si>
   <si>
-    <t>Audience type</t>
+    <t>Audience types</t>
   </si>
   <si>
     <t>Audience level</t>
@@ -1687,6 +1687,9 @@
   </si>
   <si>
     <t>Usable sessions</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
   <si>
     <t>S073: Grok distributed Tensorflow
@@ -1703,6 +1706,9 @@
   </si>
   <si>
     <t>Sector tag</t>
+  </si>
+  <si>
+    <t>Audience type</t>
   </si>
   <si>
     <t>1</t>
@@ -2301,7 +2307,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -2459,7 +2465,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>182</v>
+        <v>524</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -2524,7 +2530,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2736,13 +2742,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -2895,7 +2901,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -2960,7 +2966,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -18218,6 +18224,24 @@
       </c>
       <c r="E5" s="2" t="n">
         <v>96.0</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>108.0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>180.0</v>
       </c>
     </row>
   </sheetData>
@@ -18400,7 +18424,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -19084,7 +19108,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -20978,7 +21002,7 @@
         <v>65</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>65</v>
@@ -23491,7 +23515,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>78</v>
@@ -23556,7 +23580,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
@@ -23615,7 +23639,7 @@
         <v>65</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>65</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -3538,7 +3538,7 @@
       <c r="C3" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -3547,7 +3547,7 @@
       <c r="F3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -3556,7 +3556,7 @@
       <c r="I3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -3565,7 +3565,7 @@
       <c r="L3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N3" s="2" t="s">
@@ -3574,7 +3574,7 @@
       <c r="O3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q3" s="2" t="s">
@@ -3583,7 +3583,7 @@
       <c r="R3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T3" s="2" t="s">
@@ -3603,7 +3603,7 @@
       <c r="C4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -3612,7 +3612,7 @@
       <c r="F4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -3621,7 +3621,7 @@
       <c r="I4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K4" s="2" t="s">
@@ -3630,7 +3630,7 @@
       <c r="L4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N4" s="2" t="s">
@@ -3639,7 +3639,7 @@
       <c r="O4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q4" s="2" t="s">
@@ -3648,7 +3648,7 @@
       <c r="R4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T4" s="2" t="s">
@@ -3668,7 +3668,7 @@
       <c r="C5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -3677,7 +3677,7 @@
       <c r="F5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -3686,7 +3686,7 @@
       <c r="I5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -3695,7 +3695,7 @@
       <c r="L5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N5" s="2" t="s">
@@ -3704,7 +3704,7 @@
       <c r="O5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="P5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q5" s="2" t="s">
@@ -3713,7 +3713,7 @@
       <c r="R5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="S5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T5" s="2" t="s">
@@ -3733,7 +3733,7 @@
       <c r="C6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -3742,7 +3742,7 @@
       <c r="F6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -3751,7 +3751,7 @@
       <c r="I6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -3760,7 +3760,7 @@
       <c r="L6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N6" s="2" t="s">
@@ -3769,7 +3769,7 @@
       <c r="O6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="P6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q6" s="2" t="s">
@@ -3778,7 +3778,7 @@
       <c r="R6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S6" s="3" t="s">
+      <c r="S6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T6" s="2" t="s">
@@ -3801,55 +3801,55 @@
       <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="H7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" s="3" t="s">
+      <c r="K7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O7" s="3" t="s">
+      <c r="N7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Q7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R7" s="3" t="s">
+      <c r="Q7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="T7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="U7" s="3" t="s">
+      <c r="T7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U7" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       <c r="C8" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -3872,7 +3872,7 @@
       <c r="F8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -3881,7 +3881,7 @@
       <c r="I8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K8" s="2" t="s">
@@ -3890,7 +3890,7 @@
       <c r="L8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N8" s="2" t="s">
@@ -3899,7 +3899,7 @@
       <c r="O8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="P8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q8" s="2" t="s">
@@ -3908,7 +3908,7 @@
       <c r="R8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="S8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T8" s="2" t="s">
@@ -3928,7 +3928,7 @@
       <c r="C9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -3937,7 +3937,7 @@
       <c r="F9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -3946,7 +3946,7 @@
       <c r="I9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K9" s="2" t="s">
@@ -3955,7 +3955,7 @@
       <c r="L9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N9" s="2" t="s">
@@ -3964,7 +3964,7 @@
       <c r="O9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="P9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q9" s="2" t="s">
@@ -3973,7 +3973,7 @@
       <c r="R9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="S9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T9" s="2" t="s">
@@ -3993,7 +3993,7 @@
       <c r="C10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -4002,7 +4002,7 @@
       <c r="F10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -4011,7 +4011,7 @@
       <c r="I10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K10" s="2" t="s">
@@ -4020,7 +4020,7 @@
       <c r="L10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="M10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N10" s="2" t="s">
@@ -4029,7 +4029,7 @@
       <c r="O10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="P10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q10" s="2" t="s">
@@ -4038,7 +4038,7 @@
       <c r="R10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="S10" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T10" s="2" t="s">
@@ -4058,7 +4058,7 @@
       <c r="C11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -4067,7 +4067,7 @@
       <c r="F11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H11" s="2" t="s">
@@ -4076,7 +4076,7 @@
       <c r="I11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="K11" s="2" t="s">
@@ -4085,7 +4085,7 @@
       <c r="L11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="M11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="N11" s="2" t="s">
@@ -4094,7 +4094,7 @@
       <c r="O11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="P11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="Q11" s="2" t="s">
@@ -4103,7 +4103,7 @@
       <c r="R11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="S11" s="2" t="s">
         <v>65</v>
       </c>
       <c r="T11" s="2" t="s">
@@ -4126,55 +4126,55 @@
       <c r="D12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="H12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" s="3" t="s">
+      <c r="K12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="O12" s="3" t="s">
+      <c r="N12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="R12" s="3" t="s">
+      <c r="Q12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="U12" s="3" t="s">
+      <c r="T12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U12" s="2" t="s">
         <v>65</v>
       </c>
     </row>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -1918,7 +1918,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
@@ -1940,7 +1940,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -1962,7 +1962,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -1984,7 +1984,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>22</v>
@@ -1995,7 +1995,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>24</v>
@@ -2006,7 +2006,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>22</v>
@@ -2017,7 +2017,7 @@
         <v>26</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>24</v>
@@ -2028,7 +2028,7 @@
         <v>27</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -2039,7 +2039,7 @@
         <v>29</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
@@ -2050,7 +2050,7 @@
         <v>31</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>30</v>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -11,14 +11,16 @@
     <sheet name="Rooms" r:id="rId5" sheetId="3"/>
     <sheet name="Speakers" r:id="rId6" sheetId="4"/>
     <sheet name="Talks" r:id="rId7" sheetId="5"/>
-    <sheet name="Score view" r:id="rId8" sheetId="6"/>
+    <sheet name="Infeasible view" r:id="rId8" sheetId="6"/>
     <sheet name="Rooms view" r:id="rId9" sheetId="7"/>
     <sheet name="Speakers view" r:id="rId10" sheetId="8"/>
     <sheet name="Theme tracks view" r:id="rId11" sheetId="9"/>
     <sheet name="Sectors view" r:id="rId12" sheetId="10"/>
-    <sheet name="Audience type view" r:id="rId13" sheetId="11"/>
-    <sheet name="Audience level view" r:id="rId14" sheetId="12"/>
+    <sheet name="Audience types view" r:id="rId13" sheetId="11"/>
+    <sheet name="Audience levels view" r:id="rId14" sheetId="12"/>
     <sheet name="Contents view" r:id="rId15" sheetId="13"/>
+    <sheet name="Languages view" r:id="rId16" sheetId="14"/>
+    <sheet name="Score view" r:id="rId17" sheetId="15"/>
   </sheets>
 </workbook>
 </file>
@@ -31,9 +33,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S073: Grok distributed Tensorflow
-  Beth King
-  PINNED BY USER</t>
+        <t xml:space="preserve">S073: Grok distributed Tensorflow
+    Beth King
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -48,9 +51,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S073: Grok distributed Tensorflow
-  Beth King
-  PINNED BY USER</t>
+        <t xml:space="preserve">S073: Grok distributed Tensorflow
+    Beth King
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -65,9 +69,28 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S073: Grok distributed Tensorflow
-  Beth King
-  PINNED BY USER</t>
+        <t xml:space="preserve">S073: Grok distributed Tensorflow
+    Beth King
+PINNED BY USER
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <t xml:space="preserve">S073: Grok distributed Tensorflow
+    Beth King
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -82,9 +105,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S073: Grok distributed Tensorflow
-  Beth King
-  PINNED BY USER</t>
+        <t xml:space="preserve">S073: Grok distributed Tensorflow
+    Beth King
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -99,9 +123,10 @@
   <commentList>
     <comment ref="C34" authorId="0">
       <text>
-        <t>S073: Grok distributed Tensorflow
-  Beth King
-  PINNED BY USER</t>
+        <t xml:space="preserve">S073: Grok distributed Tensorflow
+    Beth King
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -116,16 +141,18 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t>S073: Grok distributed Tensorflow
-  Beth King
-  PINNED BY USER</t>
+        <t xml:space="preserve">S073: Grok distributed Tensorflow
+    Beth King
+PINNED BY USER
+</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0">
       <text>
-        <t>S073: Grok distributed Tensorflow
-  Beth King
-  PINNED BY USER</t>
+        <t xml:space="preserve">S073: Grok distributed Tensorflow
+    Beth King
+PINNED BY USER
+</t>
       </text>
     </comment>
   </commentList>
@@ -133,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6641" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6703" uniqueCount="531">
   <si>
     <t>Conference name</t>
   </si>
@@ -1718,6 +1745,15 @@
   </si>
   <si>
     <t>S073 (level 1)</t>
+  </si>
+  <si>
+    <t>Constraint match</t>
+  </si>
+  <si>
+    <t>Match score</t>
+  </si>
+  <si>
+    <t>Total score</t>
   </si>
 </sst>
 </file>
@@ -1829,6 +1865,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
@@ -3026,6 +3070,261 @@
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" ht="15.0" customHeight="true">
+      <c r="A3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="16.8125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="12.296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.08203125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18241,7 +18540,7 @@
         <v>10.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>180.0</v>
+        <v>108.0</v>
       </c>
     </row>
   </sheetData>
@@ -18416,7 +18715,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" ht="60.0" customHeight="true">
+    <row r="3" ht="45.0" customHeight="true">
       <c r="A3" s="2" t="s">
         <v>84</v>
       </c>
@@ -18475,7 +18774,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" ht="60.0" customHeight="true">
+    <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
         <v>86</v>
       </c>
@@ -18534,7 +18833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" ht="60.0" customHeight="true">
+    <row r="5" ht="45.0" customHeight="true">
       <c r="A5" s="2" t="s">
         <v>87</v>
       </c>
@@ -18593,7 +18892,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" ht="60.0" customHeight="true">
+    <row r="6" ht="45.0" customHeight="true">
       <c r="A6" s="2" t="s">
         <v>89</v>
       </c>
@@ -18652,7 +18951,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" ht="60.0" customHeight="true">
+    <row r="7" ht="45.0" customHeight="true">
       <c r="A7" s="2" t="s">
         <v>90</v>
       </c>
@@ -18711,7 +19010,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" ht="60.0" customHeight="true">
+    <row r="8" ht="45.0" customHeight="true">
       <c r="A8" s="2" t="s">
         <v>91</v>
       </c>
@@ -18770,7 +19069,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" ht="60.0" customHeight="true">
+    <row r="9" ht="45.0" customHeight="true">
       <c r="A9" s="2" t="s">
         <v>92</v>
       </c>
@@ -18829,7 +19128,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" ht="60.0" customHeight="true">
+    <row r="10" ht="45.0" customHeight="true">
       <c r="A10" s="2" t="s">
         <v>93</v>
       </c>
@@ -18888,7 +19187,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" ht="60.0" customHeight="true">
+    <row r="11" ht="45.0" customHeight="true">
       <c r="A11" s="2" t="s">
         <v>94</v>
       </c>
@@ -18947,7 +19246,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" ht="60.0" customHeight="true">
+    <row r="12" ht="45.0" customHeight="true">
       <c r="A12" s="2" t="s">
         <v>95</v>
       </c>
@@ -19027,24 +19326,43 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.75390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="11.86328125" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="11.86328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="20.0" customWidth="true"/>
+    <col min="3" max="3" width="20.0" customWidth="true"/>
+    <col min="4" max="4" width="20.0" customWidth="true"/>
+    <col min="5" max="5" width="20.0" customWidth="true"/>
+    <col min="6" max="6" width="20.0" customWidth="true"/>
+    <col min="7" max="7" width="20.0" customWidth="true"/>
+    <col min="8" max="8" width="20.0" customWidth="true"/>
+    <col min="9" max="9" width="20.0" customWidth="true"/>
+    <col min="10" max="10" width="20.0" customWidth="true"/>
+    <col min="11" max="11" width="20.0" customWidth="true"/>
+    <col min="12" max="12" width="20.0" customWidth="true"/>
+    <col min="13" max="13" width="20.0" customWidth="true"/>
+    <col min="14" max="14" width="20.0" customWidth="true"/>
+    <col min="15" max="15" width="20.0" customWidth="true"/>
+    <col min="16" max="16" width="20.0" customWidth="true"/>
+    <col min="17" max="17" width="20.0" customWidth="true"/>
+    <col min="18" max="18" width="20.0" customWidth="true"/>
+    <col min="19" max="19" width="20.0" customWidth="true"/>
+    <col min="20" max="20" width="20.0" customWidth="true"/>
+    <col min="21" max="21" width="20.0" customWidth="true"/>
+    <col min="22" max="22" width="20.0" customWidth="true"/>
+    <col min="23" max="23" width="20.0" customWidth="true"/>
+    <col min="24" max="24" width="20.0" customWidth="true"/>
+    <col min="25" max="25" width="20.0" customWidth="true"/>
+    <col min="26" max="26" width="20.0" customWidth="true"/>
+    <col min="27" max="27" width="20.0" customWidth="true"/>
+    <col min="28" max="28" width="20.0" customWidth="true"/>
+    <col min="29" max="29" width="20.0" customWidth="true"/>
+    <col min="30" max="30" width="20.0" customWidth="true"/>
+    <col min="31" max="31" width="20.0" customWidth="true"/>
+    <col min="32" max="32" width="20.0" customWidth="true"/>
+    <col min="33" max="33" width="20.0" customWidth="true"/>
+    <col min="34" max="34" width="20.0" customWidth="true"/>
+    <col min="35" max="35" width="20.0" customWidth="true"/>
+    <col min="36" max="36" width="20.0" customWidth="true"/>
+    <col min="37" max="37" width="20.0" customWidth="true"/>
+    <col min="38" max="38" width="20.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -225,40 +225,40 @@
     <t>Soft reward per 2 talks that have the same timeslot and a different language</t>
   </si>
   <si>
-    <t>Speaker preferred timeslot tag</t>
+    <t>Speaker preferred timeslot tags</t>
   </si>
   <si>
     <t>Soft penalty per missing preferred tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Speaker undesired timeslot tag</t>
+    <t>Speaker undesired timeslot tags</t>
   </si>
   <si>
     <t>Soft penalty per undesired tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Talk preferred timeslot tag</t>
-  </si>
-  <si>
-    <t>Talk undesired timeslot tag</t>
-  </si>
-  <si>
-    <t>Speaker preferred room tag</t>
+    <t>Talk preferred timeslot tags</t>
+  </si>
+  <si>
+    <t>Talk undesired timeslot tags</t>
+  </si>
+  <si>
+    <t>Speaker preferred room tags</t>
   </si>
   <si>
     <t>Soft penalty per missing preferred tag in a talk's room</t>
   </si>
   <si>
-    <t>Speaker undesired room tag</t>
+    <t>Speaker undesired room tags</t>
   </si>
   <si>
     <t>Soft penalty per undesired tag in a talk's room</t>
   </si>
   <si>
-    <t>Talk preferred room tag</t>
-  </si>
-  <si>
-    <t>Talk undesired room tag</t>
+    <t>Talk preferred room tags</t>
+  </si>
+  <si>
+    <t>Talk undesired room tags</t>
   </si>
   <si>
     <t>Same day talks</t>
@@ -309,43 +309,43 @@
     <t>Hard penalty per pair of talks with the same speaker in overlapping timeslots</t>
   </si>
   <si>
-    <t>Speaker required timeslot tag</t>
+    <t>Speaker required timeslot tags</t>
   </si>
   <si>
     <t>Hard penalty per missing required tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Speaker prohibited timeslot tag</t>
+    <t>Speaker prohibited timeslot tags</t>
   </si>
   <si>
     <t>Hard penalty per prohibited tag in a talk's timeslot</t>
   </si>
   <si>
-    <t>Talk required timeslot tag</t>
-  </si>
-  <si>
-    <t>Talk prohibited timeslot tag</t>
-  </si>
-  <si>
-    <t>Speaker required room tag</t>
+    <t>Talk required timeslot tags</t>
+  </si>
+  <si>
+    <t>Talk prohibited timeslot tags</t>
+  </si>
+  <si>
+    <t>Speaker required room tags</t>
   </si>
   <si>
     <t>Hard penalty per missing required tag in a talk's room</t>
   </si>
   <si>
-    <t>Speaker prohibited room tag</t>
+    <t>Speaker prohibited room tags</t>
   </si>
   <si>
     <t>Hard penalty per prohibited tag in a talk's room</t>
   </si>
   <si>
-    <t>Talk required room tag</t>
-  </si>
-  <si>
-    <t>Talk prohibited room tag</t>
-  </si>
-  <si>
-    <t>Talk mutually-exclusive-talks tag</t>
+    <t>Talk required room tags</t>
+  </si>
+  <si>
+    <t>Talk prohibited room tags</t>
+  </si>
+  <si>
+    <t>Talk mutually-exclusive-talks tags</t>
   </si>
   <si>
     <t>Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -286,7 +286,7 @@
     <t>Popular talks</t>
   </si>
   <si>
-    <t>Soft penalty per 2 talks where the less popular one (has lower number of likes) is assigned a larger room than the more popular talk</t>
+    <t>Soft penalty per 2 talks where the less popular one (has lower favorite count) is assigned a larger room than the more popular talk</t>
   </si>
   <si>
     <t>Crowd control</t>
@@ -778,7 +778,7 @@
     <t>Prerequisite talks codes</t>
   </si>
   <si>
-    <t>Number of likes</t>
+    <t>Favorite count</t>
   </si>
   <si>
     <t>Crowd control risk</t>
@@ -10867,7 +10867,7 @@
     <col min="18" max="18" width="22.84375" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="31.2734375" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="26.23046875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.5390625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="16.25390625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="20.140625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.65234375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.14453125" customWidth="true" bestFit="true"/>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -21,6 +21,9 @@
     <sheet name="Contents view" r:id="rId15" sheetId="13"/>
     <sheet name="Languages view" r:id="rId16" sheetId="14"/>
     <sheet name="Score view" r:id="rId17" sheetId="15"/>
+    <sheet name="Mon 2018-10-01" r:id="rId18" sheetId="16"/>
+    <sheet name="Tue 2018-10-02" r:id="rId19" sheetId="17"/>
+    <sheet name="Wed 2018-10-03" r:id="rId20" sheetId="18"/>
   </sheets>
 </workbook>
 </file>
@@ -33,11 +36,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S098: Program flexible Spring
+        <t xml:space="preserve">S098-Mobile: Program flexible Spring
     Beth Smith, Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -53,11 +55,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S098: Program flexible Spring
+        <t xml:space="preserve">S098-Mobile: Program flexible Spring
     Beth Smith, Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -73,11 +74,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S098: Program flexible Spring
+        <t xml:space="preserve">S098-Mobile: Program flexible Spring
     Beth Smith, Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -93,7 +93,26 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S098: Program flexible Spring
+        <t xml:space="preserve">S098-Mobile: Program flexible Spring
+    Beth Smith, Amy Cole
+PINNED BY USER
+-10soft total
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments16.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0">
+      <text>
+        <t xml:space="preserve">S098-Mobile: Program flexible Spring
     Beth Smith, Amy Cole
 PINNED BY USER
 -10soft total
@@ -113,7 +132,7 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S098: Program flexible Spring
+        <t xml:space="preserve">S098-Mobile: Program flexible Spring
     Beth Smith, Amy Cole
 PINNED BY USER
 -10soft total
@@ -133,21 +152,19 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S098: Program flexible Spring
+        <t xml:space="preserve">S098-Mobile: Program flexible Spring
     Beth Smith, Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
     <comment ref="C74" authorId="0">
       <text>
-        <t xml:space="preserve">S098: Program flexible Spring
+        <t xml:space="preserve">S098-Mobile: Program flexible Spring
     Beth Smith, Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -163,11 +180,10 @@
   <commentList>
     <comment ref="C3" authorId="0">
       <text>
-        <t xml:space="preserve">S098: Program flexible Spring
+        <t xml:space="preserve">S098-Mobile: Program flexible Spring
     Beth Smith, Amy Cole
 PINNED BY USER
 -10soft total
-    -10soft for 1 Crowd controls
 </t>
       </text>
     </comment>
@@ -176,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6909" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6937" uniqueCount="539">
   <si>
     <t>Conference name</t>
   </si>
@@ -295,6 +311,12 @@
     <t>Soft penalty per talks with crowd control risk greater than zero that are not in pairs</t>
   </si>
   <si>
+    <t>Talk mutually-exclusive-talks tags</t>
+  </si>
+  <si>
+    <t>Medium penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
+  </si>
+  <si>
     <t>Talk type of timeslot</t>
   </si>
   <si>
@@ -365,12 +387,6 @@
   </si>
   <si>
     <t>Talk prohibited room tags</t>
-  </si>
-  <si>
-    <t>Talk mutually-exclusive-talks tags</t>
-  </si>
-  <si>
-    <t>Hard penalty per two talks that share the same Mutually exclusive talks tag that are scheduled in overlapping timeslots</t>
   </si>
   <si>
     <t>Talk prerequisite talks</t>
@@ -1791,6 +1807,10 @@
   </si>
   <si>
     <t xml:space="preserve">    S098</t>
+  </si>
+  <si>
+    <t>Program flexible Spring
+Beth Smith, Amy Cole</t>
   </si>
 </sst>
 </file>
@@ -1812,7 +1832,7 @@
       <b val="true"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1847,6 +1867,46 @@
         <fgColor rgb="FCAF3E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="8AE234"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FCE94F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="729FCF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="E9B96E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="73D216"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="EDD400"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="3465A4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="C17D11"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1860,7 +1920,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true">
       <alignment wrapText="true" vertical="center"/>
@@ -1884,6 +1944,33 @@
       <alignment wrapText="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1915,6 +2002,18 @@
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
@@ -1952,7 +2051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.66796875" customWidth="true" bestFit="true"/>
@@ -2195,109 +2294,99 @@
         <v>39</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>10000.0</v>
+        <v>1.0</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>10000.0</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>10000.0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>10.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
@@ -2308,40 +2397,40 @@
         <v>1.0</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
@@ -2352,17 +2441,28 @@
         <v>1.0</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2377,7 +2477,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.94140625" customWidth="true" bestFit="true"/>
@@ -2535,7 +2635,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.99609375" customWidth="true" bestFit="true"/>
@@ -2753,7 +2853,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.3046875" customWidth="true" bestFit="true"/>
@@ -2971,7 +3071,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="13.4609375" customWidth="true" bestFit="true"/>
@@ -3189,7 +3289,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.3046875" customWidth="true" bestFit="true"/>
@@ -3389,12 +3489,6 @@
       <c r="S3" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="T3" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>518</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -3413,44 +3507,231 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.0703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.73828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.15625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>535</v>
-      </c>
-    </row>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="4">
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="17.94140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" ht="45.0" customHeight="true">
+      <c r="A2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" ht="45.0" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="4" ht="45.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" ht="45.0" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" ht="45.0" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" ht="45.0" customHeight="true">
+      <c r="A7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="17.3515625" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" ht="45.0" customHeight="true">
+      <c r="A2" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" ht="45.0" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" ht="45.0" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" ht="45.0" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" ht="45.0" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" ht="45.0" customHeight="true">
+      <c r="A7" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FCE94F"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="18.12890625" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" ht="45.0" customHeight="true">
+      <c r="A2" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" ht="45.0" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" ht="45.0" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" ht="45.0" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" ht="45.0" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" ht="45.0" customHeight="true">
+      <c r="A7" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -3460,7 +3741,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.3828125" customWidth="true" bestFit="true"/>
@@ -3801,7 +4082,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.109375" customWidth="true" bestFit="true"/>
@@ -4657,7 +4938,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AB74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="12.04296875" customWidth="true" bestFit="true"/>
@@ -10844,7 +11125,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="6.34765625" customWidth="true" bestFit="true"/>
@@ -19934,7 +20215,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="10.78515625" customWidth="true" bestFit="true"/>
@@ -20033,7 +20314,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.02734375" customWidth="true" bestFit="true"/>
@@ -20801,7 +21082,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="12.04296875" customWidth="true" bestFit="true"/>
@@ -25227,7 +25508,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.1640625" customWidth="true" bestFit="true"/>

--- a/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
+++ b/optaplanner-examples/data/conferencescheduling/unsolved/108talks-18timeslots-10rooms.xlsx
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7716" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7716" uniqueCount="584">
   <si>
     <t>Conference name</t>
   </si>
@@ -934,9 +934,6 @@
   </si>
   <si>
     <t>en</t>
-  </si>
-  <si>
-    <t>Large, Recorded</t>
   </si>
   <si>
     <t>S001</t>
@@ -2791,7 +2788,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -2949,7 +2946,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -3008,13 +3005,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -3070,7 +3067,7 @@
         <v>232</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>93</v>
@@ -3285,13 +3282,13 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -3344,10 +3341,10 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>93</v>
@@ -3503,7 +3500,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -3562,10 +3559,10 @@
     </row>
     <row r="3" ht="15.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>93</v>
@@ -3621,13 +3618,13 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>93</v>
@@ -3842,10 +3839,10 @@
         <v>234</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -3927,39 +3924,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3972,13 +3969,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="6">
@@ -3986,13 +3983,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7">
@@ -4000,13 +3997,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
@@ -4014,13 +4011,13 @@
         <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="9">
@@ -4028,13 +4025,13 @@
         <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10">
@@ -4042,13 +4039,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11">
@@ -4056,13 +4053,13 @@
         <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12">
@@ -4070,13 +4067,13 @@
         <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13">
@@ -4084,13 +4081,13 @@
         <v>35</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14">
@@ -4098,13 +4095,13 @@
         <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="15">
@@ -4112,13 +4109,13 @@
         <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16">
@@ -4126,13 +4123,13 @@
         <v>40</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17">
@@ -4140,13 +4137,13 @@
         <v>34</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18">
@@ -4154,13 +4151,13 @@
         <v>39</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19">
@@ -4168,13 +4165,13 @@
         <v>33</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="20">
@@ -4182,13 +4179,13 @@
         <v>41</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21">
@@ -4196,13 +4193,13 @@
         <v>62</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="22">
@@ -4210,13 +4207,13 @@
         <v>78</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="23">
@@ -4224,13 +4221,13 @@
         <v>71</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="24">
@@ -4238,13 +4235,13 @@
         <v>80</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="25">
@@ -4252,13 +4249,13 @@
         <v>74</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="26">
@@ -4266,13 +4263,13 @@
         <v>82</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="27">
@@ -4280,13 +4277,13 @@
         <v>76</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28">
@@ -4294,13 +4291,13 @@
         <v>83</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="29">
@@ -4308,13 +4305,13 @@
         <v>77</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C29" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="30">
@@ -4322,13 +4319,13 @@
         <v>60</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="31">
@@ -4336,13 +4333,13 @@
         <v>65</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="32">
@@ -4350,13 +4347,13 @@
         <v>69</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="33">
@@ -4364,13 +4361,13 @@
         <v>44</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="34">
@@ -4378,13 +4375,13 @@
         <v>67</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="35">
@@ -4392,13 +4389,13 @@
         <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="36">
@@ -4406,13 +4403,13 @@
         <v>47</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="37">
@@ -4420,13 +4417,13 @@
         <v>49</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="38">
@@ -4434,13 +4431,13 @@
         <v>58</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="39">
@@ -4448,13 +4445,13 @@
         <v>53</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C39" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40">
@@ -4462,13 +4459,13 @@
         <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="41">
@@ -4476,13 +4473,13 @@
         <v>26</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="42"/>
@@ -4492,13 +4489,13 @@
         <v>58</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="45">
@@ -4506,13 +4503,13 @@
         <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="46">
@@ -4520,13 +4517,13 @@
         <v>56</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="47">
@@ -4534,13 +4531,13 @@
         <v>24</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="48">
@@ -4548,13 +4545,13 @@
         <v>60</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="49">
@@ -4562,13 +4559,13 @@
         <v>62</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="50">
@@ -4576,13 +4573,13 @@
         <v>26</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C50" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="51">
@@ -4590,13 +4587,13 @@
         <v>65</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="52">
@@ -4604,13 +4601,13 @@
         <v>69</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C52" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="53">
@@ -4618,13 +4615,13 @@
         <v>44</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="54">
@@ -4632,13 +4629,13 @@
         <v>41</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="55">
@@ -4646,13 +4643,13 @@
         <v>10</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="56">
@@ -4660,13 +4657,13 @@
         <v>7</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="57">
@@ -4674,13 +4671,13 @@
         <v>67</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="58">
@@ -4688,13 +4685,13 @@
         <v>51</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="59">
@@ -4702,13 +4699,13 @@
         <v>16</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="60">
@@ -4716,13 +4713,13 @@
         <v>78</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="61">
@@ -4730,13 +4727,13 @@
         <v>71</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="62">
@@ -4744,13 +4741,13 @@
         <v>37</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="63">
@@ -4758,13 +4755,13 @@
         <v>31</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="64">
@@ -4772,13 +4769,13 @@
         <v>35</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="65">
@@ -4786,13 +4783,13 @@
         <v>29</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="66">
@@ -4800,13 +4797,13 @@
         <v>13</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="67">
@@ -4814,13 +4811,13 @@
         <v>80</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="68">
@@ -4828,13 +4825,13 @@
         <v>74</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="69">
@@ -4842,13 +4839,13 @@
         <v>21</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="70">
@@ -4856,13 +4853,13 @@
         <v>82</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="71">
@@ -4870,13 +4867,13 @@
         <v>76</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="72">
@@ -4884,13 +4881,13 @@
         <v>19</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="73">
@@ -4898,13 +4895,13 @@
         <v>40</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C73" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="74">
@@ -4912,13 +4909,13 @@
         <v>34</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="75">
@@ -4926,13 +4923,13 @@
         <v>39</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="76">
@@ -4940,13 +4937,13 @@
         <v>33</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="77">
@@ -4954,13 +4951,13 @@
         <v>83</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="78">
@@ -4968,13 +4965,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="79">
@@ -4982,13 +4979,13 @@
         <v>47</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C79" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="80">
@@ -4996,13 +4993,13 @@
         <v>49</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>
@@ -5043,7 +5040,7 @@
         <v>93</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3" ht="45.0" customHeight="true">
@@ -5051,7 +5048,7 @@
         <v>109</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C3" s="2"/>
     </row>
@@ -12775,7 +12772,7 @@
         <v>93</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>93</v>
@@ -12825,31 +12822,31 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>234</v>
@@ -12920,31 +12917,31 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>234</v>
@@ -12965,7 +12962,7 @@
         <v>93</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>93</v>
@@ -13015,10 +13012,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>92</v>
@@ -13027,19 +13024,19 @@
         <v>142</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>234</v>
@@ -13060,7 +13057,7 @@
         <v>93</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>93</v>
@@ -13110,10 +13107,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>92</v>
@@ -13134,7 +13131,7 @@
         <v>3.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>234</v>
@@ -13205,10 +13202,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>92</v>
@@ -13217,7 +13214,7 @@
         <v>144</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -13229,7 +13226,7 @@
         <v>2.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>234</v>
@@ -13250,7 +13247,7 @@
         <v>93</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>93</v>
@@ -13300,10 +13297,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>92</v>
@@ -13312,19 +13309,19 @@
         <v>145</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>234</v>
@@ -13357,7 +13354,7 @@
         <v>93</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>799.0</v>
@@ -13395,10 +13392,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>92</v>
@@ -13407,19 +13404,19 @@
         <v>146</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>234</v>
@@ -13440,7 +13437,7 @@
         <v>93</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>93</v>
@@ -13490,31 +13487,31 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>234</v>
@@ -13585,10 +13582,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>92</v>
@@ -13609,7 +13606,7 @@
         <v>3.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>234</v>
@@ -13680,31 +13677,31 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>234</v>
@@ -13725,7 +13722,7 @@
         <v>93</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>93</v>
@@ -13775,10 +13772,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>92</v>
@@ -13787,19 +13784,19 @@
         <v>152</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>234</v>
@@ -13870,10 +13867,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>95</v>
@@ -13888,13 +13885,13 @@
         <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>234</v>
@@ -13915,7 +13912,7 @@
         <v>93</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>93</v>
@@ -13965,31 +13962,31 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="G15" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>234</v>
@@ -14060,10 +14057,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>95</v>
@@ -14072,19 +14069,19 @@
         <v>156</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>234</v>
@@ -14105,7 +14102,7 @@
         <v>93</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>93</v>
@@ -14155,19 +14152,19 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -14179,7 +14176,7 @@
         <v>1.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>234</v>
@@ -14200,7 +14197,7 @@
         <v>93</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>93</v>
@@ -14250,10 +14247,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>95</v>
@@ -14262,7 +14259,7 @@
         <v>159</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -14274,7 +14271,7 @@
         <v>1.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>234</v>
@@ -14345,10 +14342,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>95</v>
@@ -14357,7 +14354,7 @@
         <v>160</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -14369,7 +14366,7 @@
         <v>2.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>234</v>
@@ -14390,7 +14387,7 @@
         <v>93</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>93</v>
@@ -14440,10 +14437,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>95</v>
@@ -14452,19 +14449,19 @@
         <v>161</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>234</v>
@@ -14535,19 +14532,19 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -14559,7 +14556,7 @@
         <v>3.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>234</v>
@@ -14580,7 +14577,7 @@
         <v>93</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>93</v>
@@ -14630,10 +14627,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>95</v>
@@ -14642,19 +14639,19 @@
         <v>164</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>234</v>
@@ -14725,10 +14722,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>95</v>
@@ -14737,19 +14734,19 @@
         <v>165</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>234</v>
@@ -14770,7 +14767,7 @@
         <v>93</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="2" t="s">
         <v>93</v>
@@ -14820,31 +14817,31 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>234</v>
@@ -14877,7 +14874,7 @@
         <v>93</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="U24" s="2" t="n">
         <v>617.0</v>
@@ -14915,31 +14912,31 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>234</v>
@@ -14960,7 +14957,7 @@
         <v>93</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>93</v>
@@ -15010,10 +15007,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>95</v>
@@ -15022,19 +15019,19 @@
         <v>170</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>234</v>
@@ -15055,7 +15052,7 @@
         <v>93</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q26" s="2" t="s">
         <v>93</v>
@@ -15105,31 +15102,31 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>234</v>
@@ -15150,7 +15147,7 @@
         <v>93</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q27" s="2" t="s">
         <v>93</v>
@@ -15200,31 +15197,31 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>234</v>
@@ -15245,7 +15242,7 @@
         <v>93</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="Q28" s="2" t="s">
         <v>93</v>
@@ -15254,7 +15251,7 @@
         <v>93</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>93</v>
@@ -15295,31 +15292,31 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="G29" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>234</v>
@@ -15340,7 +15337,7 @@
         <v>93</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q29" s="2" t="s">
         <v>93</v>
@@ -15390,10 +15387,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>95</v>
@@ -15402,7 +15399,7 @@
         <v>177</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
@@ -15414,7 +15411,7 @@
         <v>2.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>234</v>
@@ -15435,7 +15432,7 @@
         <v>93</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="Q30" s="2" t="s">
         <v>93</v>
@@ -15485,19 +15482,19 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
@@ -15509,7 +15506,7 @@
         <v>3.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>234</v>
@@ -15530,7 +15527,7 @@
         <v>93</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q31" s="2" t="s">
         <v>93</v>
@@ -15580,31 +15577,31 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>234</v>
@@ -15625,7 +15622,7 @@
         <v>93</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q32" s="2" t="s">
         <v>93</v>
@@ -15675,31 +15672,31 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="F33" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>234</v>
@@ -15732,7 +15729,7 @@
         <v>93</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="U33" s="2" t="n">
         <v>894.0</v>
@@ -15770,10 +15767,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>355</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>95</v>
@@ -15782,7 +15779,7 @@
         <v>185</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>93</v>
@@ -15794,7 +15791,7 @@
         <v>2.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>234</v>
@@ -15865,31 +15862,31 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="G35" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>234</v>
@@ -15960,10 +15957,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>95</v>
@@ -15972,7 +15969,7 @@
         <v>188</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>93</v>
@@ -15984,7 +15981,7 @@
         <v>1.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>234</v>
@@ -16005,7 +16002,7 @@
         <v>93</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q36" s="2" t="s">
         <v>93</v>
@@ -16055,10 +16052,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>95</v>
@@ -16067,19 +16064,19 @@
         <v>189</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>234</v>
@@ -16109,7 +16106,7 @@
         <v>93</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="T37" s="2" t="s">
         <v>93</v>
@@ -16150,10 +16147,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>95</v>
@@ -16162,7 +16159,7 @@
         <v>190</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>93</v>
@@ -16174,7 +16171,7 @@
         <v>2.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>234</v>
@@ -16245,16 +16242,16 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>231</v>
@@ -16269,7 +16266,7 @@
         <v>3.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>234</v>
@@ -16290,7 +16287,7 @@
         <v>93</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q39" s="2" t="s">
         <v>93</v>
@@ -16302,7 +16299,7 @@
         <v>93</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="U39" s="2" t="n">
         <v>591.0</v>
@@ -16340,10 +16337,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>95</v>
@@ -16358,13 +16355,13 @@
         <v>93</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>234</v>
@@ -16435,10 +16432,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>95</v>
@@ -16447,10 +16444,10 @@
         <v>194</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>232</v>
@@ -16459,7 +16456,7 @@
         <v>2.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>234</v>
@@ -16530,10 +16527,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>95</v>
@@ -16548,13 +16545,13 @@
         <v>93</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>234</v>
@@ -16575,7 +16572,7 @@
         <v>93</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c r="Q42" s="2" t="s">
         <v>93</v>
@@ -16625,10 +16622,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>95</v>
@@ -16637,10 +16634,10 @@
         <v>196</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>232</v>
@@ -16649,7 +16646,7 @@
         <v>2.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>234</v>
@@ -16720,10 +16717,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>95</v>
@@ -16732,7 +16729,7 @@
         <v>197</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>93</v>
@@ -16744,7 +16741,7 @@
         <v>3.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>234</v>
@@ -16765,7 +16762,7 @@
         <v>93</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q44" s="2" t="s">
         <v>93</v>
@@ -16815,19 +16812,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>93</v>
@@ -16839,7 +16836,7 @@
         <v>3.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>234</v>
@@ -16910,19 +16907,19 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>93</v>
@@ -16934,7 +16931,7 @@
         <v>1.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>234</v>
@@ -17005,10 +17002,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>95</v>
@@ -17017,19 +17014,19 @@
         <v>202</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>234</v>
@@ -17100,10 +17097,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>95</v>
@@ -17112,19 +17109,19 @@
         <v>203</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>234</v>
@@ -17195,19 +17192,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>93</v>
@@ -17219,7 +17216,7 @@
         <v>2.0</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>234</v>
@@ -17240,7 +17237,7 @@
         <v>93</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="Q49" s="2" t="s">
         <v>93</v>
@@ -17290,10 +17287,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>95</v>
@@ -17302,19 +17299,19 @@
         <v>206</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>234</v>
@@ -17335,7 +17332,7 @@
         <v>93</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="Q50" s="2" t="s">
         <v>93</v>
@@ -17385,10 +17382,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>95</v>
@@ -17397,10 +17394,10 @@
         <v>230</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>232</v>
@@ -17409,7 +17406,7 @@
         <v>3.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>234</v>
@@ -17430,7 +17427,7 @@
         <v>93</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c r="Q51" s="2" t="s">
         <v>93</v>
@@ -17442,7 +17439,7 @@
         <v>93</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="U51" s="2" t="n">
         <v>307.0</v>
@@ -17480,10 +17477,10 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>95</v>
@@ -17492,7 +17489,7 @@
         <v>136</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>93</v>
@@ -17504,7 +17501,7 @@
         <v>3.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>234</v>
@@ -17575,19 +17572,19 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>93</v>
@@ -17599,7 +17596,7 @@
         <v>3.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>234</v>
@@ -17620,7 +17617,7 @@
         <v>93</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q53" s="2" t="s">
         <v>93</v>
@@ -17670,19 +17667,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>93</v>
@@ -17694,7 +17691,7 @@
         <v>1.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>234</v>
@@ -17765,10 +17762,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>95</v>
@@ -17777,19 +17774,19 @@
         <v>143</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>234</v>
@@ -17810,7 +17807,7 @@
         <v>93</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q55" s="2" t="s">
         <v>93</v>
@@ -17860,31 +17857,31 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>231</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>234</v>
@@ -17905,7 +17902,7 @@
         <v>93</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q56" s="2" t="s">
         <v>93</v>
@@ -17955,10 +17952,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>95</v>
@@ -17967,19 +17964,19 @@
         <v>147</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>234</v>
@@ -18000,7 +17997,7 @@
         <v>93</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="Q57" s="2" t="s">
         <v>93</v>
@@ -18050,22 +18047,22 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>232</v>
@@ -18074,7 +18071,7 @@
         <v>3.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>234</v>
@@ -18095,7 +18092,7 @@
         <v>93</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q58" s="2" t="s">
         <v>93</v>
@@ -18145,31 +18142,31 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>234</v>
@@ -18190,7 +18187,7 @@
         <v>93</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q59" s="2" t="s">
         <v>93</v>
@@ -18240,10 +18237,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>95</v>
@@ -18258,13 +18255,13 @@
         <v>93</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>234</v>
@@ -18285,7 +18282,7 @@
         <v>93</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q60" s="2" t="s">
         <v>93</v>
@@ -18294,7 +18291,7 @@
         <v>93</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="T60" s="2" t="s">
         <v>93</v>
@@ -18335,31 +18332,31 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>234</v>
@@ -18430,10 +18427,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>95</v>
@@ -18442,19 +18439,19 @@
         <v>156</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>234</v>
@@ -18475,7 +18472,7 @@
         <v>93</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>93</v>
@@ -18525,31 +18522,31 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E63" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>234</v>
@@ -18620,10 +18617,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>95</v>
@@ -18632,10 +18629,10 @@
         <v>159</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>232</v>
@@ -18644,7 +18641,7 @@
         <v>2.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>234</v>
@@ -18662,7 +18659,7 @@
         <v>93</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>93</v>
@@ -18671,7 +18668,7 @@
         <v>93</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="S64" s="2" t="s">
         <v>93</v>
@@ -18715,31 +18712,31 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>436</v>
-      </c>
       <c r="F65" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>234</v>
@@ -18810,10 +18807,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>95</v>
@@ -18822,7 +18819,7 @@
         <v>162</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>93</v>
@@ -18834,7 +18831,7 @@
         <v>2.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>234</v>
@@ -18855,7 +18852,7 @@
         <v>93</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>93</v>
@@ -18905,31 +18902,31 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>234</v>
@@ -19000,10 +18997,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>95</v>
@@ -19012,19 +19009,19 @@
         <v>165</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>234</v>
@@ -19095,31 +19092,31 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>234</v>
@@ -19140,7 +19137,7 @@
         <v>93</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q69" s="2" t="s">
         <v>93</v>
@@ -19190,10 +19187,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>95</v>
@@ -19202,10 +19199,10 @@
         <v>168</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>232</v>
@@ -19214,7 +19211,7 @@
         <v>3.0</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>234</v>
@@ -19235,7 +19232,7 @@
         <v>93</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q70" s="2" t="s">
         <v>93</v>
@@ -19285,10 +19282,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>95</v>
@@ -19297,7 +19294,7 @@
         <v>169</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>93</v>
@@ -19309,7 +19306,7 @@
         <v>2.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>234</v>
@@ -19330,7 +19327,7 @@
         <v>93</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q71" s="2" t="s">
         <v>93</v>
@@ -19380,10 +19377,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>95</v>
@@ -19392,19 +19389,19 @@
         <v>170</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>234</v>
@@ -19437,7 +19434,7 @@
         <v>93</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U72" s="2" t="n">
         <v>309.0</v>
@@ -19475,10 +19472,10 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>95</v>
@@ -19487,19 +19484,19 @@
         <v>171</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>234</v>
@@ -19520,13 +19517,13 @@
         <v>93</v>
       </c>
       <c r="P73" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q73" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R73" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="Q73" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R73" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>93</v>
@@ -19570,16 +19567,16 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>231</v>
@@ -19594,7 +19591,7 @@
         <v>1.0</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>234</v>
@@ -19615,7 +19612,7 @@
         <v>93</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q74" s="2" t="s">
         <v>93</v>
@@ -19665,10 +19662,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>95</v>
@@ -19677,19 +19674,19 @@
         <v>174</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>234</v>
@@ -19760,31 +19757,31 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>234</v>
@@ -19855,16 +19852,16 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>231</v>
@@ -19873,13 +19870,13 @@
         <v>93</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>234</v>
@@ -19900,7 +19897,7 @@
         <v>93</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q77" s="2" t="s">
         <v>93</v>
@@ -19950,10 +19947,10 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>95</v>
@@ -19962,19 +19959,19 @@
         <v>179</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>234</v>
@@ -19995,7 +19992,7 @@
         <v>93</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q78" s="2" t="s">
         <v>93</v>
@@ -20045,22 +20042,22 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D79" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>471</v>
-      </c>
       <c r="F79" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>232</v>
@@ -20090,7 +20087,7 @@
         <v>93</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="Q79" s="2" t="s">
         <v>93</v>
@@ -20140,10 +20137,10 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>95</v>
@@ -20152,19 +20149,19 @@
         <v>182</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>234</v>
@@ -20235,10 +20232,10 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>95</v>
@@ -20247,19 +20244,19 @@
         <v>183</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>234</v>
@@ -20330,19 +20327,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>93</v>
@@ -20354,7 +20351,7 @@
         <v>3.0</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>234</v>
@@ -20387,7 +20384,7 @@
         <v>93</v>
       </c>
       <c r="T82" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="U82" s="2" t="n">
         <v>947.0</v>
@@ -20425,10 +20422,10 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>95</v>
@@ -20437,19 +20434,19 @@
         <v>186</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>234</v>
@@ -20470,7 +20467,7 @@
         <v>93</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q83" s="2" t="s">
         <v>93</v>
@@ -20520,10 +20517,10 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>95</v>
@@ -20532,7 +20529,7 @@
         <v>187</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>93</v>
@@ -20544,7 +20541,7 @@
         <v>3.0</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>234</v>
@@ -20615,10 +20612,10 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>95</v>
@@ -20627,19 +20624,19 @@
         <v>188</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>234</v>
@@ -20710,10 +20707,10 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>95</v>
@@ -20722,19 +20719,19 @@
         <v>189</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>234</v>
@@ -20755,7 +20752,7 @@
         <v>93</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q86" s="2" t="s">
         <v>93</v>
@@ -20805,10 +20802,10 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>95</v>
@@ -20817,7 +20814,7 @@
         <v>190</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>93</v>
@@ -20829,7 +20826,7 @@
         <v>3.0</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>234</v>
@@ -20850,7 +20847,7 @@
         <v>93</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q87" s="2" t="s">
         <v>93</v>
@@ -20900,10 +20897,10 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>95</v>
@@ -20912,19 +20909,19 @@
         <v>191</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>234</v>
@@ -20945,7 +20942,7 @@
         <v>93</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="Q88" s="2" t="s">
         <v>93</v>
@@ -20995,10 +20992,10 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>95</v>
@@ -21007,7 +21004,7 @@
         <v>192</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>93</v>
@@ -21019,7 +21016,7 @@
         <v>3.0</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>234</v>
@@ -21040,7 +21037,7 @@
         <v>93</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q89" s="2" t="s">
         <v>93</v>
@@ -21090,31 +21087,31 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>234</v>
@@ -21185,31 +21182,31 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D91" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>502</v>
-      </c>
       <c r="F91" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>234</v>
@@ -21230,7 +21227,7 @@
         <v>93</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q91" s="2" t="s">
         <v>93</v>
@@ -21280,10 +21277,10 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>95</v>
@@ -21292,19 +21289,19 @@
         <v>197</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>234</v>
@@ -21375,19 +21372,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>93</v>
@@ -21399,7 +21396,7 @@
         <v>2.0</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>234</v>
@@ -21470,31 +21467,31 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>234</v>
@@ -21565,10 +21562,10 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>95</v>
@@ -21577,19 +21574,19 @@
         <v>202</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>234</v>
@@ -21660,31 +21657,31 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>513</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>234</v>
@@ -21705,7 +21702,7 @@
         <v>93</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q96" s="2" t="s">
         <v>93</v>
@@ -21755,31 +21752,31 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>516</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>234</v>
@@ -21800,7 +21797,7 @@
         <v>93</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c r="Q97" s="2" t="s">
         <v>93</v>
@@ -21850,10 +21847,10 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>95</v>
@@ -21862,19 +21859,19 @@
         <v>134</v>
       </c>
       <c r="E98" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>234</v>
@@ -21895,7 +21892,7 @@
         <v>93</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q98" s="2" t="s">
         <v>93</v>
@@ -21907,7 +21904,7 @@
         <v>93</v>
       </c>
       <c r="T98" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="U98" s="2" t="n">
         <v>947.0</v>
@@ -21945,10 +21942,10 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>95</v>
@@ -21957,19 +21954,19 @@
         <v>135</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>234</v>
@@ -21990,7 +21987,7 @@
         <v>93</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q99" s="2" t="s">
         <v>93</v>
@@ -22040,10 +22037,10 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>95</v>
@@ -22052,19 +22049,19 @@
         <v>136</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>234</v>
@@ -22135,10 +22132,10 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>95</v>
@@ -22147,19 +22144,19 @@
         <v>137</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>234</v>
@@ -22230,10 +22227,10 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>526</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>527</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>95</v>
@@ -22242,19 +22239,19 @@
         <v>138</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>3.0</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>234</v>
@@ -22325,10 +22322,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>95</v>
@@ -22337,7 +22334,7 @@
         <v>139</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>93</v>
@@ -22349,7 +22346,7 @@
         <v>1.0</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>234</v>
@@ -22370,7 +22367,7 @@
         <v>93</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q103" s="2" t="s">
         <v>93</v>
@@ -22420,19 +22417,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>93</v>
@@ -22444,7 +22441,7 @@
         <v>1.0</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>234</v>
@@ -22515,10 +22512,10 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>95</v>
@@ -22527,19 +22524,19 @@
         <v>143</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>234</v>
@@ -22560,7 +22557,7 @@
         <v>93</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q105" s="2" t="s">
         <v>93</v>
@@ -22610,19 +22607,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>93</v>
@@ -22634,7 +22631,7 @@
         <v>3.0</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>234</v>
@@ -22655,7 +22652,7 @@
         <v>93</v>
       </c>
       <c r="P106" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q106" s="2" t="s">
         <v>93</v>
@@ -22705,19 +22702,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>93</v>
@@ -22729,7 +22726,7 @@
         <v>2.0</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>234</v>
@@ -22750,7 +22747,7 @@
         <v>93</v>
       </c>
       <c r="P107" s="2" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c r="Q107" s="2" t="s">
         <v>93</v>
@@ -22800,10 +22797,10 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>95</v>
@@ -22812,19 +22809,19 @@
         <v>148</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>234</v>
@@ -22895,10 +22892,10 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>95</v>
@@ -22907,19 +22904,19 @@
         <v>149</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>234</v>
@@ -22940,7 +22937,7 @@
         <v>93</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="Q109" s="2" t="s">
         <v>93</v>
@@ -23011,10 +23008,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="2"/>
@@ -23023,16 +23020,16 @@
         <v>209</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="4">
@@ -23072,7 +23069,7 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>108.0</v>
@@ -23267,7 +23264,7 @@
         <v>93</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>93</v>
@@ -23500,7 +23497,7 @@
         <v>120</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -23967,7 +23964,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -24504,7 +24501,7 @@
         <v>93</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>93</v>
@@ -24855,7 +24852,7 @@
         <v>149</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -28371,7 +28368,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -28433,7 +28430,7 @@
         <v>231</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>93</v>
@@ -28489,13 +28486,13 @@
     </row>
     <row r="4" ht="15.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>93</v>
